--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -709,22 +709,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="4" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>95497</v>
+        <v>102862</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>9726</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>85771</v>
+        <v>93136</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.08955223880597014</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.1282051282051282</v>
+        <v>0.119047619047619</v>
       </c>
     </row>
     <row r="6">
@@ -774,14 +774,14 @@
     <row r="9" ht="20" customHeight="1">
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>8636</v>
+        <v>1131</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>46174</v>
@@ -796,36 +796,36 @@
     <row r="10" ht="20" customHeight="1">
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>9805</v>
+        <v>6234</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>43443</v>
+        <v>50808</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>21468</v>
+        <v>8636</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>46235</v>
@@ -840,14 +840,14 @@
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>3534</v>
+        <v>9805</v>
       </c>
       <c r="F12" s="18" t="n">
         <v>46266</v>
@@ -862,14 +862,14 @@
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>6040</v>
+        <v>21468</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>46296</v>
@@ -884,14 +884,14 @@
     <row r="14" ht="20" customHeight="1">
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>10144</v>
+        <v>3534</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>46327</v>
@@ -906,14 +906,14 @@
     <row r="15" ht="20" customHeight="1">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1290</v>
+        <v>6040</v>
       </c>
       <c r="F15" s="14" t="n">
         <v>46357</v>
@@ -928,14 +928,14 @@
     <row r="16" ht="20" customHeight="1">
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>16476</v>
+        <v>10144</v>
       </c>
       <c r="F16" s="18" t="n">
         <v>46388</v>
@@ -950,14 +950,14 @@
     <row r="17" ht="20" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>7980</v>
+        <v>1290</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>46419</v>
@@ -972,14 +972,14 @@
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>9012</v>
+        <v>16476</v>
       </c>
       <c r="F18" s="18" t="n">
         <v>46447</v>
@@ -994,13 +994,39 @@
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>9012</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
           <t>22-06-2026</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D21" s="13" t="n">
         <v>1112</v>
       </c>
     </row>
@@ -1361,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1467,38 +1493,38 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>#1143</t>
+          <t>#1148</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>Nandhini V</t>
+          <t>Amirtha Varshini</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - M</t>
+          <t>Plum Pinstripe - L</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" s="19" t="inlineStr">
@@ -1518,17 +1544,17 @@
       </c>
       <c r="L2" s="20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>'631601</t>
+          <t>'627007</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -1545,38 +1571,38 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>#1142</t>
+          <t>#1147</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Sunanda P</t>
+          <t>Vishalini Priya</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
+          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G3" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" s="23" t="inlineStr">
@@ -1596,17 +1622,17 @@
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>'560011</t>
+          <t>'600117</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
@@ -1623,24 +1649,24 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>#1141</t>
+          <t>#1146</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Priya Kathiravan</t>
+          <t>Astin</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Geometric Glam - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>1211</v>
+        <v>2243</v>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
@@ -1674,17 +1700,17 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Sathyamoorthy Nagar</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>'614804</t>
+          <t>'613007</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -1701,38 +1727,38 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>#1139</t>
+          <t>#1144</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Keerthana C</t>
+          <t>Deepak Raj</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Rose Charm Top - S</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1112</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -1757,12 +1783,12 @@
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>'600091</t>
+          <t>'600045</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR PICKUP</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -1779,38 +1805,38 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>#1138</t>
+          <t>#1143</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Preeti Niranjan</t>
+          <t>Nandhini V</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - S</t>
+          <t>Wine Blossom Top - M</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
         <v>46207</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -1830,17 +1856,17 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Karwar Uttar Kannada</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>'581400</t>
+          <t>'631601</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -1857,24 +1883,24 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>#1137</t>
+          <t>#1142</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Sasi Gouru</t>
+          <t>Sunanda P</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
         <v>46207</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1211</v>
+        <v>2779</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
@@ -1908,12 +1934,12 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>'500090</t>
+          <t>'560011</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -1935,38 +1961,38 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>#1136</t>
+          <t>#1141</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Bala Murali</t>
+          <t>Priya Kathiravan</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1290</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -1986,17 +2012,17 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram District</t>
+          <t>Sathyamoorthy Nagar</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>'623707</t>
+          <t>'614804</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -2013,21 +2039,21 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>#1135</t>
+          <t>#1139</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Anusha Bekkanti</t>
+          <t>Keerthana C</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>1112</v>
@@ -2064,17 +2090,17 @@
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Harlur Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>'560102</t>
+          <t>'600091</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -2091,24 +2117,24 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>#1134</t>
+          <t>#1138</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Kaylash Pinkky</t>
+          <t>Preeti Niranjan</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Wine Blossom Top - S</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
@@ -2142,12 +2168,12 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Karwar Uttar Kannada</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>'500010</t>
+          <t>'581400</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
@@ -2169,24 +2195,24 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>#1133</t>
+          <t>#1137</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Deva E</t>
+          <t>Sasi Gouru</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>3096</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
@@ -2220,17 +2246,17 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>'600056</t>
+          <t>'500090</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -2247,38 +2273,38 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>#1132</t>
+          <t>#1136</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Sudha Manikandan</t>
+          <t>Bala Murali</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
         <v>46206</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -2298,17 +2324,17 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Paramakudi , Ramanathapuram District</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>'625016</t>
+          <t>'623707</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -2325,38 +2351,38 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>#1131</t>
+          <t>#1135</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Sindhuri Kalidindi</t>
+          <t>Anusha Bekkanti</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
         <v>46206</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -2376,12 +2402,12 @@
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Harlur Bengaluru</t>
         </is>
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>'146024</t>
+          <t>'560102</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
@@ -2403,38 +2429,38 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>#1130</t>
+          <t>#1134</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Sudha G</t>
+          <t>Kaylash Pinkky</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3336</v>
+        <v>1131</v>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -2454,12 +2480,12 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>'639001</t>
+          <t>'500010</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
@@ -2481,24 +2507,24 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>#1129</t>
+          <t>#1133</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Mamillapalli Sivakumari</t>
+          <t>Deva E</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>1112</v>
+        <v>3096</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -2532,17 +2558,17 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Thiruvallur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>'601204</t>
+          <t>'600056</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -2559,24 +2585,24 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>#1128</t>
+          <t>#1132</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Shanmuga Priya Priya</t>
+          <t>Sudha Manikandan</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - M</t>
+          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1032</v>
+        <v>2144</v>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
@@ -2605,17 +2631,17 @@
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>Seller Initiated Delay</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>'632009</t>
+          <t>'625016</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
@@ -2637,24 +2663,24 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>#1127</t>
+          <t>#1131</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Rajani Reddy</t>
+          <t>Sindhuri Kalidindi</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - M</t>
+          <t>Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
@@ -2688,17 +2714,17 @@
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>'560076</t>
+          <t>'146024</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -2715,24 +2741,24 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>#1126</t>
+          <t>#1130</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Sulochana N</t>
+          <t>Sudha G</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Rosy Mist - M</t>
+          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1890</v>
+        <v>3336</v>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
@@ -2766,17 +2792,17 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>'515002</t>
+          <t>'639001</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -2793,24 +2819,24 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>#1125</t>
+          <t>#1129</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Subha A.R</t>
+          <t>Mamillapalli Sivakumari</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - S</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>2680</v>
+        <v>1112</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -2839,22 +2865,22 @@
       </c>
       <c r="K19" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>Chennai 600107</t>
+          <t>Thiruvallur</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>'600107</t>
+          <t>'601204</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -2871,24 +2897,24 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>#1124</t>
+          <t>#1128</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Anusha Madhukar</t>
+          <t>Shanmuga Priya Priya</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
@@ -2917,17 +2943,17 @@
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Seller Initiated Delay</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>'500035</t>
+          <t>'632009</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
@@ -2949,38 +2975,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>#1123</t>
+          <t>#1127</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Ujwala Gajula</t>
+          <t>Rajani Reddy</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
+          <t>Sunset Petal - M</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>2064</v>
+        <v>1112</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -3000,17 +3026,17 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>'500019</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -3027,38 +3053,38 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>#1122</t>
+          <t>#1126</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Suganya Suganyasridhar</t>
+          <t>Sulochana N</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - XL, Purple Panache - XL</t>
+          <t>Rosy Mist - M</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2064</v>
+        <v>1890</v>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -3078,12 +3104,12 @@
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Anantapur</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>'606902</t>
+          <t>'515002</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
@@ -3105,24 +3131,24 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>#1121</t>
+          <t>#1125</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Salla Mahesh</t>
+          <t>Subha A.R</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
+          <t>Sunset Petal - L, Teal Tempo - S</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>2144</v>
+        <v>2680</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -3151,22 +3177,22 @@
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>Godavarikhani</t>
+          <t>Chennai 600107</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>'505210</t>
+          <t>'600107</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -3183,43 +3209,43 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>#1120</t>
+          <t>#1124</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Nisha J</t>
+          <t>Anusha Madhukar</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J24" s="19" t="inlineStr">
@@ -3234,17 +3260,17 @@
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>Chengalpattu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>'603002</t>
+          <t>'500035</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>CANCELED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -3261,38 +3287,38 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>#1119</t>
+          <t>#1123</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Vijayasri S Narendran</t>
+          <t>Ujwala Gajula</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Blossom Taupe Chic Set - 2XL</t>
+          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>1890</v>
+        <v>2064</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -3307,22 +3333,22 @@
       </c>
       <c r="K25" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Avadi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>'600062</t>
+          <t>'500019</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -3339,38 +3365,38 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>#1118</t>
+          <t>#1122</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Aswathy P</t>
+          <t>Suganya Suganyasridhar</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - M</t>
+          <t>Bold Basil - XL, Purple Panache - XL</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1032</v>
+        <v>2064</v>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -3390,17 +3416,17 @@
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>'682030</t>
+          <t>'606902</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -3417,38 +3443,38 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>#1117</t>
+          <t>#1121</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Dr Jovin Jose</t>
+          <t>Salla Mahesh</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - M</t>
+          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -3468,17 +3494,17 @@
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>Kanhangad</t>
+          <t>Godavarikhani</t>
         </is>
       </c>
       <c r="M27" s="26" t="inlineStr">
         <is>
-          <t>'671326</t>
+          <t>'505210</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -3495,43 +3521,43 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>#1115</t>
+          <t>#1120</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Vidya Jothi</t>
+          <t>Nisha J</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Dainty Dots Teal - 2XL</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1390</v>
+        <v>1032</v>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
@@ -3541,22 +3567,22 @@
       </c>
       <c r="K28" s="20" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chengalpattu</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>'641062</t>
+          <t>'603002</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -3573,38 +3599,38 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>#1114</t>
+          <t>#1119</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Kruthika Vignesh</t>
+          <t>Vijayasri S Narendran</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Blossom Taupe Chic Set - 2XL</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>1112</v>
+        <v>1890</v>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -3619,22 +3645,22 @@
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Avadi</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>'600078</t>
+          <t>'600062</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -3651,21 +3677,21 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>#1113</t>
+          <t>#1118</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Maha Jayaraman</t>
+          <t>Aswathy P</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - XL</t>
+          <t>Urban Ruby - M</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>1032</v>
@@ -3697,22 +3723,22 @@
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
-          <t>Unabletocontactrecipient Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>'605008</t>
+          <t>'682030</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -3729,21 +3755,21 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>#1112</t>
+          <t>#1117</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Perikala Vivekananda</t>
+          <t>Dr Jovin Jose</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - S</t>
+          <t>Daisy Dusk Yellow - M</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>1112</v>
@@ -3780,17 +3806,17 @@
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>Tenali</t>
+          <t>Kanhangad</t>
         </is>
       </c>
       <c r="M31" s="26" t="inlineStr">
         <is>
-          <t>'522201</t>
+          <t>'671326</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -3807,24 +3833,24 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>#1111</t>
+          <t>#1115</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Jeeva Ramprabu</t>
+          <t>Vidya Jothi</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>2784</v>
+        <v>1390</v>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
@@ -3853,27 +3879,27 @@
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customerunavailable Deliveryattempted</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>'626707</t>
+          <t>'641062</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P32" s="19" t="inlineStr">
@@ -3885,24 +3911,24 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>#1110</t>
+          <t>#1114</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Sharanyaa K</t>
+          <t>Kruthika Vignesh</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - M, Sunset Petal - M</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>2144</v>
+        <v>1112</v>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
@@ -3936,22 +3962,22 @@
       </c>
       <c r="L33" s="24" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M33" s="26" t="inlineStr">
         <is>
-          <t>'605011</t>
+          <t>'600078</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P33" s="23" t="inlineStr">
@@ -3963,38 +3989,38 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>#1109</t>
+          <t>#1113</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Anusha Anusha</t>
+          <t>Maha Jayaraman</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - 3XL</t>
+          <t>Dainty Dots Teal - XL</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>1032</v>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -4009,27 +4035,27 @@
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unabletocontactrecipient Deliveryattempted</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
-          <t>Hyderbad</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>'500086</t>
+          <t>'605008</t>
         </is>
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P34" s="19" t="inlineStr">
@@ -4041,38 +4067,38 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>#1108</t>
+          <t>#1112</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>Bharathi Dinesh</t>
+          <t>Perikala Vivekananda</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - S</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -4092,17 +4118,17 @@
       </c>
       <c r="L35" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Tenali</t>
         </is>
       </c>
       <c r="M35" s="26" t="inlineStr">
         <is>
-          <t>'600077</t>
+          <t>'522201</t>
         </is>
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -4119,24 +4145,24 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>#1107</t>
+          <t>#1111</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Meghana R</t>
+          <t>Jeeva Ramprabu</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Aranya Grace Anarkali Dress - XL</t>
+          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>2680</v>
+        <v>2784</v>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
@@ -4155,37 +4181,37 @@
       </c>
       <c r="I36" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Customer Cancelled Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
-          <t>Kolar</t>
+          <t>Paramakudi , Ramanathapuram</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
         <is>
-          <t>'563102</t>
+          <t>'626707</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P36" s="19" t="inlineStr">
@@ -4197,17 +4223,17 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>#1105</t>
+          <t>#1110</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Akila Senthil</t>
+          <t>Sharanyaa K</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
+          <t>Moss Majesty - M, Sunset Petal - M</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
@@ -4218,52 +4244,52 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K37" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L37" s="24" t="inlineStr">
         <is>
-          <t>Salem</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="M37" s="26" t="inlineStr">
         <is>
-          <t>'636005</t>
+          <t>'605011</t>
         </is>
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P37" s="23" t="inlineStr">
@@ -4275,24 +4301,24 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>#1104</t>
+          <t>#1109</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Gopal Kowsi</t>
+          <t>Anusha Anusha</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Purple Panache - 3XL</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
         <v>46202</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
@@ -4326,12 +4352,12 @@
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
-          <t>Vanavasi</t>
+          <t>Hyderbad</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
         <is>
-          <t>'636457</t>
+          <t>'500086</t>
         </is>
       </c>
       <c r="N38" s="19" t="inlineStr">
@@ -4353,24 +4379,24 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>#1103</t>
+          <t>#1108</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Praveena Manoharan</t>
+          <t>Bharathi Dinesh</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - XL</t>
+          <t>Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D39" s="11" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
@@ -4409,17 +4435,17 @@
       </c>
       <c r="M39" s="26" t="inlineStr">
         <is>
-          <t>'600100</t>
+          <t>'600077</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O39" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P39" s="23" t="inlineStr">
@@ -4431,24 +4457,24 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>#1102</t>
+          <t>#1107</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Smitha Ag</t>
+          <t>Meghana R</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L</t>
+          <t>Aranya Grace Anarkali Dress - XL</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>1032</v>
+        <v>2680</v>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
@@ -4467,32 +4493,32 @@
       </c>
       <c r="I40" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J40" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K40" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Cancelled Otp Verified</t>
         </is>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
-          <t>Muvattupuzha</t>
+          <t>Kolar</t>
         </is>
       </c>
       <c r="M40" s="22" t="inlineStr">
         <is>
-          <t>'686661</t>
+          <t>'563102</t>
         </is>
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr">
@@ -4509,73 +4535,73 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>#1101</t>
+          <t>#1105</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Apsara Reddy</t>
+          <t>Akila Senthil</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
+          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>3176</v>
+        <v>2144</v>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K41" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L41" s="24" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Salem</t>
         </is>
       </c>
       <c r="M41" s="26" t="inlineStr">
         <is>
-          <t>'518003</t>
+          <t>'636005</t>
         </is>
       </c>
       <c r="N41" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P41" s="23" t="inlineStr">
@@ -4587,24 +4613,24 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>#1100</t>
+          <t>#1104</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Shailu Reddy</t>
+          <t>Gopal Kowsi</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - 2XL</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>1290</v>
+        <v>1112</v>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
@@ -4638,12 +4664,12 @@
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Vanavasi</t>
         </is>
       </c>
       <c r="M42" s="22" t="inlineStr">
         <is>
-          <t>'506002</t>
+          <t>'636457</t>
         </is>
       </c>
       <c r="N42" s="19" t="inlineStr">
@@ -4665,38 +4691,38 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>#1099</t>
+          <t>#1103</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>Durai Kannan</t>
+          <t>Praveena Manoharan</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - L</t>
+          <t>Purple Panache - XL</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>1032</v>
+        <v>1290</v>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I43" s="23" t="inlineStr">
@@ -4716,12 +4742,12 @@
       </c>
       <c r="L43" s="24" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M43" s="26" t="inlineStr">
         <is>
-          <t>'641008</t>
+          <t>'600100</t>
         </is>
       </c>
       <c r="N43" s="23" t="inlineStr">
@@ -4743,17 +4769,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>#1098</t>
+          <t>#1102</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>B Padmapriya</t>
+          <t>Smitha Ag</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - L</t>
+          <t>Mystic Mist Red - L</t>
         </is>
       </c>
       <c r="D44" s="15" t="n">
@@ -4794,22 +4820,22 @@
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Muvattupuzha</t>
         </is>
       </c>
       <c r="M44" s="22" t="inlineStr">
         <is>
-          <t>'500017</t>
+          <t>'686661</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P44" s="19" t="inlineStr">
@@ -4821,24 +4847,24 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>#1097</t>
+          <t>#1101</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Apsara Reddy</t>
         </is>
       </c>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>Grape Leaf Glam - M</t>
+          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>1112</v>
+        <v>3176</v>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
@@ -4872,12 +4898,12 @@
       </c>
       <c r="L45" s="24" t="inlineStr">
         <is>
-          <t>Guntur</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="M45" s="26" t="inlineStr">
         <is>
-          <t>'522007</t>
+          <t>'518003</t>
         </is>
       </c>
       <c r="N45" s="23" t="inlineStr">
@@ -4899,38 +4925,38 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>#1096</t>
+          <t>#1100</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Indu Rekha</t>
+          <t>Shailu Reddy</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
+          <t>Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D46" s="15" t="n">
         <v>46200</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>2224</v>
+        <v>1290</v>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I46" s="19" t="inlineStr">
@@ -4950,12 +4976,12 @@
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
-          <t>Anantapur Urban</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="M46" s="22" t="inlineStr">
         <is>
-          <t>'515001</t>
+          <t>'506002</t>
         </is>
       </c>
       <c r="N46" s="19" t="inlineStr">
@@ -4977,38 +5003,38 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>#1095</t>
+          <t>#1099</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Priya Dharshini Pd</t>
+          <t>Durai Kannan</t>
         </is>
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - 2XL</t>
+          <t>Moss Majesty - L</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I47" s="23" t="inlineStr">
@@ -5028,12 +5054,12 @@
       </c>
       <c r="L47" s="24" t="inlineStr">
         <is>
-          <t>Villupuram</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M47" s="26" t="inlineStr">
         <is>
-          <t>'604204</t>
+          <t>'641008</t>
         </is>
       </c>
       <c r="N47" s="23" t="inlineStr">
@@ -5055,17 +5081,17 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>#1094</t>
+          <t>#1098</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Usha .R</t>
+          <t>B Padmapriya</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 3XL</t>
+          <t>Bold Basil - L</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
@@ -5076,17 +5102,17 @@
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I48" s="19" t="inlineStr">
@@ -5106,12 +5132,12 @@
       </c>
       <c r="L48" s="20" t="inlineStr">
         <is>
-          <t>Hosur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M48" s="22" t="inlineStr">
         <is>
-          <t>'635109</t>
+          <t>'500017</t>
         </is>
       </c>
       <c r="N48" s="19" t="inlineStr">
@@ -5133,38 +5159,38 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>#1093</t>
+          <t>#1097</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Ramya Gowda</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Grape Leaf Glam - M</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I49" s="23" t="inlineStr">
@@ -5179,27 +5205,27 @@
       </c>
       <c r="K49" s="24" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L49" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Guntur</t>
         </is>
       </c>
       <c r="M49" s="26" t="inlineStr">
         <is>
-          <t>'560091</t>
+          <t>'522007</t>
         </is>
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O49" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P49" s="23" t="inlineStr">
@@ -5211,73 +5237,73 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>#1092</t>
+          <t>#1096</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Kowsalya</t>
+          <t>Indu Rekha</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - S</t>
+          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
         </is>
       </c>
       <c r="D50" s="15" t="n">
         <v>46200</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>1290</v>
+        <v>2224</v>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K50" s="20" t="inlineStr">
         <is>
-          <t>Customer Not Available X Office Or Residence Closed</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L50" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Anantapur Urban</t>
         </is>
       </c>
       <c r="M50" s="22" t="inlineStr">
         <is>
-          <t>'600096</t>
+          <t>'515001</t>
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O50" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P50" s="19" t="inlineStr">
@@ -5289,17 +5315,17 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>#1091</t>
+          <t>#1095</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Vijay Aadarsh Adarsh</t>
+          <t>Priya Dharshini Pd</t>
         </is>
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Wine Blossom Top - 2XL</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
@@ -5335,27 +5361,27 @@
       </c>
       <c r="K51" s="24" t="inlineStr">
         <is>
-          <t>Receiver Requested Delivery On Another Date (Cir)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L51" s="24" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Villupuram</t>
         </is>
       </c>
       <c r="M51" s="26" t="inlineStr">
         <is>
-          <t>'641107</t>
+          <t>'604204</t>
         </is>
       </c>
       <c r="N51" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O51" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P51" s="23" t="inlineStr">
@@ -5367,38 +5393,38 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>#1090</t>
+          <t>#1094</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Kamal Thiyagarajan</t>
+          <t>Usha .R</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Vanya Bloom Top - S</t>
+          <t>Dainty Dots Teal - 3XL</t>
         </is>
       </c>
       <c r="D52" s="15" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F52" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
@@ -5418,12 +5444,12 @@
       </c>
       <c r="L52" s="20" t="inlineStr">
         <is>
-          <t>Tirupur</t>
+          <t>Hosur</t>
         </is>
       </c>
       <c r="M52" s="22" t="inlineStr">
         <is>
-          <t>'641606</t>
+          <t>'635109</t>
         </is>
       </c>
       <c r="N52" s="19" t="inlineStr">
@@ -5445,24 +5471,24 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>#1089</t>
+          <t>#1093</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Divya Divya</t>
+          <t>Ramya Gowda</t>
         </is>
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - L</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
@@ -5491,27 +5517,27 @@
       </c>
       <c r="K53" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customerunavailable Deliveryattempted</t>
         </is>
       </c>
       <c r="L53" s="24" t="inlineStr">
         <is>
-          <t>Kuppatti</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M53" s="26" t="inlineStr">
         <is>
-          <t>'635118</t>
+          <t>'560091</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED-3RD ATTEMPT</t>
         </is>
       </c>
       <c r="O53" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P53" s="23" t="inlineStr">
@@ -5523,68 +5549,68 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>#1088</t>
+          <t>#1092</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Nutan Manerkar</t>
+          <t>Kowsalya</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - 2XL</t>
+          <t>Moss Majesty - S</t>
         </is>
       </c>
       <c r="D54" s="15" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>1112</v>
+        <v>1290</v>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Available X Office Or Residence Closed</t>
         </is>
       </c>
       <c r="L54" s="20" t="inlineStr">
         <is>
-          <t>Margao</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M54" s="22" t="inlineStr">
         <is>
-          <t>'403601</t>
+          <t>'600096</t>
         </is>
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O54" s="19" t="inlineStr">
@@ -5601,24 +5627,24 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>#1087</t>
+          <t>#1091</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>Devi Rv</t>
+          <t>Vijay Aadarsh Adarsh</t>
         </is>
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>1290</v>
+        <v>1112</v>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
@@ -5647,22 +5673,22 @@
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
-          <t>Customer Not Contactable</t>
+          <t>Receiver Requested Delivery On Another Date (Cir)</t>
         </is>
       </c>
       <c r="L55" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M55" s="26" t="inlineStr">
         <is>
-          <t>'600110</t>
+          <t>'641107</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O55" s="23" t="inlineStr">
@@ -5679,24 +5705,24 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>#1086</t>
+          <t>#1090</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>D Keerthi</t>
+          <t>Kamal Thiyagarajan</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 3XL</t>
+          <t>Vanya Bloom Top - S</t>
         </is>
       </c>
       <c r="D56" s="15" t="n">
         <v>46198</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F56" s="19" t="inlineStr">
         <is>
@@ -5730,12 +5756,12 @@
       </c>
       <c r="L56" s="20" t="inlineStr">
         <is>
-          <t>Chittoor</t>
+          <t>Tirupur</t>
         </is>
       </c>
       <c r="M56" s="22" t="inlineStr">
         <is>
-          <t>'517234</t>
+          <t>'641606</t>
         </is>
       </c>
       <c r="N56" s="19" t="inlineStr">
@@ -5757,24 +5783,24 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>#1085</t>
+          <t>#1089</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Mohanakrishnan Devanathan</t>
+          <t>Divya Divya</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - M</t>
+          <t>Moss Majesty - L</t>
         </is>
       </c>
       <c r="D57" s="11" t="n">
         <v>46198</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>1032</v>
+        <v>1290</v>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
@@ -5808,12 +5834,12 @@
       </c>
       <c r="L57" s="24" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Kuppatti</t>
         </is>
       </c>
       <c r="M57" s="26" t="inlineStr">
         <is>
-          <t>'605006</t>
+          <t>'635118</t>
         </is>
       </c>
       <c r="N57" s="23" t="inlineStr">
@@ -5835,17 +5861,17 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>#1084</t>
+          <t>#1088</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Gowri R</t>
+          <t>Nutan Manerkar</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Wine Blossom Top - 2XL</t>
         </is>
       </c>
       <c r="D58" s="15" t="n">
@@ -5886,22 +5912,22 @@
       </c>
       <c r="L58" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Margao</t>
         </is>
       </c>
       <c r="M58" s="22" t="inlineStr">
         <is>
-          <t>'600096</t>
+          <t>'403601</t>
         </is>
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P58" s="19" t="inlineStr">
@@ -5913,24 +5939,24 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>#1083</t>
+          <t>#1087</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Sukanya R</t>
+          <t>Devi Rv</t>
         </is>
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>Coral Bloom Top - M, Purple Panache - M</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
@@ -5959,7 +5985,7 @@
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Contactable</t>
         </is>
       </c>
       <c r="L59" s="24" t="inlineStr">
@@ -5969,12 +5995,12 @@
       </c>
       <c r="M59" s="26" t="inlineStr">
         <is>
-          <t>'600095</t>
+          <t>'600110</t>
         </is>
       </c>
       <c r="N59" s="23" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>UNDELIVERED-3RD ATTEMPT</t>
         </is>
       </c>
       <c r="O59" s="23" t="inlineStr">
@@ -5991,24 +6017,24 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>#1082</t>
+          <t>#1086</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Harshini Rajendran</t>
+          <t>D Keerthi</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - XL</t>
+          <t>Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D60" s="15" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
@@ -6027,37 +6053,37 @@
       </c>
       <c r="I60" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J60" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K60" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L60" s="20" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Chittoor</t>
         </is>
       </c>
       <c r="M60" s="22" t="inlineStr">
         <is>
-          <t>'630003</t>
+          <t>'517234</t>
         </is>
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O60" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P60" s="19" t="inlineStr">
@@ -6069,24 +6095,24 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>#1081</t>
+          <t>#1085</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>Harshini Rajendran</t>
+          <t>Mohanakrishnan Devanathan</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - S</t>
+          <t>Purple Panache - M</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
@@ -6105,37 +6131,37 @@
       </c>
       <c r="I61" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J61" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L61" s="24" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="M61" s="26" t="inlineStr">
         <is>
-          <t>'630003</t>
+          <t>'605006</t>
         </is>
       </c>
       <c r="N61" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O61" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P61" s="23" t="inlineStr">
@@ -6147,24 +6173,24 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>#1080</t>
+          <t>#1084</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Chandraelectro Corporation</t>
+          <t>Gowri R</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D62" s="15" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>3176</v>
+        <v>1112</v>
       </c>
       <c r="F62" s="19" t="inlineStr">
         <is>
@@ -6198,12 +6224,12 @@
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M62" s="22" t="inlineStr">
         <is>
-          <t>'625001</t>
+          <t>'600096</t>
         </is>
       </c>
       <c r="N62" s="19" t="inlineStr">
@@ -6225,38 +6251,38 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>#1078</t>
+          <t>#1083</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Gomathi Dhanapal</t>
+          <t>Sukanya R</t>
         </is>
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Coral Bloom Top - M, Purple Panache - M</t>
         </is>
       </c>
       <c r="D63" s="11" t="n">
         <v>46197</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H63" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I63" s="23" t="inlineStr">
@@ -6281,17 +6307,17 @@
       </c>
       <c r="M63" s="26" t="inlineStr">
         <is>
-          <t>'600073</t>
+          <t>'600095</t>
         </is>
       </c>
       <c r="N63" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O63" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P63" s="23" t="inlineStr">
@@ -6303,112 +6329,424 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="19" t="inlineStr">
         <is>
+          <t>#1082</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="inlineStr">
+        <is>
+          <t>Urban Ruby - XL</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K64" s="20" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept   Otp Verified</t>
+        </is>
+      </c>
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M64" s="22" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N64" s="19" t="inlineStr">
+        <is>
+          <t>RTO IN TRANSIT</t>
+        </is>
+      </c>
+      <c r="O64" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P64" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>#1081</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - S</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H65" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I65" s="23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K65" s="24" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept   Otp Verified</t>
+        </is>
+      </c>
+      <c r="L65" s="24" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M65" s="26" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N65" s="23" t="inlineStr">
+        <is>
+          <t>RTO IN TRANSIT</t>
+        </is>
+      </c>
+      <c r="O65" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P65" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>#1080</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Chandraelectro Corporation</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="inlineStr">
+        <is>
+          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K66" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="M66" s="22" t="inlineStr">
+        <is>
+          <t>'625001</t>
+        </is>
+      </c>
+      <c r="N66" s="19" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O66" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P66" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>#1078</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>Gomathi Dhanapal</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I67" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K67" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="24" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M67" s="26" t="inlineStr">
+        <is>
+          <t>'600073</t>
+        </is>
+      </c>
+      <c r="N67" s="23" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O67" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P67" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
           <t>#1071</t>
         </is>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>Soumya Shetty</t>
         </is>
       </c>
-      <c r="C64" s="21" t="inlineStr">
+      <c r="C68" s="21" t="inlineStr">
         <is>
           <t>Sapphire Charm Top - M</t>
         </is>
       </c>
-      <c r="D64" s="15" t="n">
+      <c r="D68" s="15" t="n">
         <v>46195</v>
       </c>
-      <c r="E64" s="17" t="n">
+      <c r="E68" s="17" t="n">
         <v>1112</v>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>Prepaid (Razorpay)</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I68" s="19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K64" s="20" t="inlineStr">
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L64" s="20" t="inlineStr">
+      <c r="L68" s="20" t="inlineStr">
         <is>
           <t>Bijapur</t>
         </is>
       </c>
-      <c r="M64" s="22" t="inlineStr">
+      <c r="M68" s="22" t="inlineStr">
         <is>
           <t>'586101</t>
         </is>
       </c>
-      <c r="N64" s="19" t="inlineStr">
+      <c r="N68" s="19" t="inlineStr">
         <is>
           <t>DELIVERED</t>
         </is>
       </c>
-      <c r="O64" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P64" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
+      <c r="O68" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B65" s="28">
-        <f>COUNTA(A2:A64)</f>
+      <c r="B69" s="28">
+        <f>COUNTA(A2:A68)</f>
         <v/>
       </c>
-      <c r="C65" s="27" t="n"/>
-      <c r="D65" s="29" t="inlineStr">
+      <c r="C69" s="27" t="n"/>
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E65" s="30">
-        <f>SUM(E2:E64)</f>
+      <c r="E69" s="30">
+        <f>SUM(E2:E68)</f>
         <v/>
       </c>
-      <c r="F65" s="27" t="n"/>
-      <c r="G65" s="27" t="n"/>
-      <c r="H65" s="27" t="n"/>
-      <c r="I65" s="27" t="n"/>
-      <c r="J65" s="27" t="n"/>
-      <c r="K65" s="27" t="n"/>
-      <c r="L65" s="27" t="n"/>
-      <c r="M65" s="27" t="n"/>
-      <c r="N65" s="27" t="n"/>
-      <c r="O65" s="27" t="n"/>
-      <c r="P65" s="27" t="n"/>
+      <c r="F69" s="27" t="n"/>
+      <c r="G69" s="27" t="n"/>
+      <c r="H69" s="27" t="n"/>
+      <c r="I69" s="27" t="n"/>
+      <c r="J69" s="27" t="n"/>
+      <c r="K69" s="27" t="n"/>
+      <c r="L69" s="27" t="n"/>
+      <c r="M69" s="27" t="n"/>
+      <c r="N69" s="27" t="n"/>
+      <c r="O69" s="27" t="n"/>
+      <c r="P69" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9375,7 +9713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9481,38 +9819,38 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>#1143</t>
+          <t>#1148</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>Nandhini V</t>
+          <t>Amirtha Varshini</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - M</t>
+          <t>Plum Pinstripe - L</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" s="19" t="inlineStr">
@@ -9532,17 +9870,17 @@
       </c>
       <c r="L2" s="20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>'631601</t>
+          <t>'627007</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -9559,38 +9897,38 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>#1142</t>
+          <t>#1147</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Sunanda P</t>
+          <t>Vishalini Priya</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
+          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G3" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" s="23" t="inlineStr">
@@ -9610,17 +9948,17 @@
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>'560011</t>
+          <t>'600117</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
@@ -9637,24 +9975,24 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>#1141</t>
+          <t>#1146</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Priya Kathiravan</t>
+          <t>Astin</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Geometric Glam - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>1211</v>
+        <v>2243</v>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
@@ -9688,17 +10026,17 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Sathyamoorthy Nagar</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>'614804</t>
+          <t>'613007</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -9715,38 +10053,38 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>#1139</t>
+          <t>#1144</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Keerthana C</t>
+          <t>Deepak Raj</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Rose Charm Top - S</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1112</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -9771,12 +10109,12 @@
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>'600091</t>
+          <t>'600045</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR PICKUP</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -9793,38 +10131,38 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>#1138</t>
+          <t>#1143</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Preeti Niranjan</t>
+          <t>Nandhini V</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - S</t>
+          <t>Wine Blossom Top - M</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
         <v>46207</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -9844,17 +10182,17 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Karwar Uttar Kannada</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>'581400</t>
+          <t>'631601</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -9871,24 +10209,24 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>#1137</t>
+          <t>#1142</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Sasi Gouru</t>
+          <t>Sunanda P</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
         <v>46207</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1211</v>
+        <v>2779</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
@@ -9922,12 +10260,12 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>'500090</t>
+          <t>'560011</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
@@ -9949,38 +10287,38 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>#1136</t>
+          <t>#1141</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Bala Murali</t>
+          <t>Priya Kathiravan</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1290</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -10000,17 +10338,17 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram District</t>
+          <t>Sathyamoorthy Nagar</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>'623707</t>
+          <t>'614804</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -10027,21 +10365,21 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>#1135</t>
+          <t>#1139</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Anusha Bekkanti</t>
+          <t>Keerthana C</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>1112</v>
@@ -10078,17 +10416,17 @@
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Harlur Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>'560102</t>
+          <t>'600091</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -10105,24 +10443,24 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>#1134</t>
+          <t>#1138</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Kaylash Pinkky</t>
+          <t>Preeti Niranjan</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Wine Blossom Top - S</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
@@ -10156,12 +10494,12 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Karwar Uttar Kannada</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>'500010</t>
+          <t>'581400</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
@@ -10183,24 +10521,24 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>#1133</t>
+          <t>#1137</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Deva E</t>
+          <t>Sasi Gouru</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>3096</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
@@ -10234,17 +10572,17 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>'600056</t>
+          <t>'500090</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -10261,38 +10599,38 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>#1132</t>
+          <t>#1136</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Sudha Manikandan</t>
+          <t>Bala Murali</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
         <v>46206</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -10312,17 +10650,17 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Paramakudi , Ramanathapuram District</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>'625016</t>
+          <t>'623707</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -10339,38 +10677,38 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>#1131</t>
+          <t>#1135</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Sindhuri Kalidindi</t>
+          <t>Anusha Bekkanti</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
         <v>46206</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -10390,12 +10728,12 @@
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Harlur Bengaluru</t>
         </is>
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>'146024</t>
+          <t>'560102</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
@@ -10417,38 +10755,38 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>#1130</t>
+          <t>#1134</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Sudha G</t>
+          <t>Kaylash Pinkky</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3336</v>
+        <v>1131</v>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -10468,12 +10806,12 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>'639001</t>
+          <t>'500010</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
@@ -10495,24 +10833,24 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>#1129</t>
+          <t>#1133</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Mamillapalli Sivakumari</t>
+          <t>Deva E</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>1112</v>
+        <v>3096</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -10546,17 +10884,17 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Thiruvallur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>'601204</t>
+          <t>'600056</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -10573,24 +10911,24 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>#1128</t>
+          <t>#1132</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Shanmuga Priya Priya</t>
+          <t>Sudha Manikandan</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - M</t>
+          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1032</v>
+        <v>2144</v>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
@@ -10619,17 +10957,17 @@
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>Seller Initiated Delay</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>'632009</t>
+          <t>'625016</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
@@ -10651,24 +10989,24 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>#1127</t>
+          <t>#1131</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Rajani Reddy</t>
+          <t>Sindhuri Kalidindi</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - M</t>
+          <t>Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
@@ -10702,17 +11040,17 @@
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>'560076</t>
+          <t>'146024</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -10729,24 +11067,24 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>#1126</t>
+          <t>#1130</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Sulochana N</t>
+          <t>Sudha G</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Rosy Mist - M</t>
+          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1890</v>
+        <v>3336</v>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
@@ -10780,17 +11118,17 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>'515002</t>
+          <t>'639001</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -10807,24 +11145,24 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>#1125</t>
+          <t>#1129</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Subha A.R</t>
+          <t>Mamillapalli Sivakumari</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - S</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>2680</v>
+        <v>1112</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -10853,22 +11191,22 @@
       </c>
       <c r="K19" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>Chennai 600107</t>
+          <t>Thiruvallur</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>'600107</t>
+          <t>'601204</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -10885,24 +11223,24 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>#1124</t>
+          <t>#1128</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Anusha Madhukar</t>
+          <t>Shanmuga Priya Priya</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
@@ -10931,17 +11269,17 @@
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Seller Initiated Delay</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>'500035</t>
+          <t>'632009</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
@@ -10963,38 +11301,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>#1123</t>
+          <t>#1127</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Ujwala Gajula</t>
+          <t>Rajani Reddy</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
+          <t>Sunset Petal - M</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>2064</v>
+        <v>1112</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -11014,17 +11352,17 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>'500019</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -11041,38 +11379,38 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>#1122</t>
+          <t>#1126</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Suganya Suganyasridhar</t>
+          <t>Sulochana N</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - XL, Purple Panache - XL</t>
+          <t>Rosy Mist - M</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2064</v>
+        <v>1890</v>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -11092,12 +11430,12 @@
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Anantapur</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>'606902</t>
+          <t>'515002</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
@@ -11119,24 +11457,24 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>#1121</t>
+          <t>#1125</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Salla Mahesh</t>
+          <t>Subha A.R</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
+          <t>Sunset Petal - L, Teal Tempo - S</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>2144</v>
+        <v>2680</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -11165,22 +11503,22 @@
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>Godavarikhani</t>
+          <t>Chennai 600107</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>'505210</t>
+          <t>'600107</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -11197,43 +11535,43 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>#1120</t>
+          <t>#1124</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Nisha J</t>
+          <t>Anusha Madhukar</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J24" s="19" t="inlineStr">
@@ -11248,17 +11586,17 @@
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>Chengalpattu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>'603002</t>
+          <t>'500035</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>CANCELED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -11275,38 +11613,38 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>#1119</t>
+          <t>#1123</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Vijayasri S Narendran</t>
+          <t>Ujwala Gajula</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Blossom Taupe Chic Set - 2XL</t>
+          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>1890</v>
+        <v>2064</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -11321,22 +11659,22 @@
       </c>
       <c r="K25" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Avadi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>'600062</t>
+          <t>'500019</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -11353,38 +11691,38 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>#1118</t>
+          <t>#1122</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Aswathy P</t>
+          <t>Suganya Suganyasridhar</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - M</t>
+          <t>Bold Basil - XL, Purple Panache - XL</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1032</v>
+        <v>2064</v>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -11404,17 +11742,17 @@
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>'682030</t>
+          <t>'606902</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -11431,38 +11769,38 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>#1117</t>
+          <t>#1121</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Dr Jovin Jose</t>
+          <t>Salla Mahesh</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - M</t>
+          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -11482,17 +11820,17 @@
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>Kanhangad</t>
+          <t>Godavarikhani</t>
         </is>
       </c>
       <c r="M27" s="26" t="inlineStr">
         <is>
-          <t>'671326</t>
+          <t>'505210</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -11509,112 +11847,424 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
+          <t>#1120</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Nisha J</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>Chengalpattu</t>
+        </is>
+      </c>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>'603002</t>
+        </is>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O28" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P28" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>#1119</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Vijayasri S Narendran</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>Blossom Taupe Chic Set - 2XL</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>Pickup Not Attempted</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>Avadi</t>
+        </is>
+      </c>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>'600062</t>
+        </is>
+      </c>
+      <c r="N29" s="23" t="inlineStr">
+        <is>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
+        </is>
+      </c>
+      <c r="O29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>#1118</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Aswathy P</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Urban Ruby - M</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>Ernakulam</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>'682030</t>
+        </is>
+      </c>
+      <c r="N30" s="19" t="inlineStr">
+        <is>
+          <t>PICKUP EXCEPTION</t>
+        </is>
+      </c>
+      <c r="O30" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P30" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>#1117</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Dr Jovin Jose</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - M</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="inlineStr">
+        <is>
+          <t>Kanhangad</t>
+        </is>
+      </c>
+      <c r="M31" s="26" t="inlineStr">
+        <is>
+          <t>'671326</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>PICKUP EXCEPTION</t>
+        </is>
+      </c>
+      <c r="O31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
           <t>#1115</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Vidya Jothi</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D32" s="15" t="n">
         <v>46204</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E32" s="17" t="n">
         <v>1390</v>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr">
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>Customerunavailable Deliveryattempted</t>
         </is>
       </c>
-      <c r="L28" s="20" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="M28" s="22" t="inlineStr">
+      <c r="M32" s="22" t="inlineStr">
         <is>
           <t>'641062</t>
         </is>
       </c>
-      <c r="N28" s="19" t="inlineStr">
+      <c r="N32" s="19" t="inlineStr">
         <is>
           <t>UNDELIVERED</t>
         </is>
       </c>
-      <c r="O28" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P28" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="O32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B29" s="28">
-        <f>COUNTA(A2:A28)</f>
+      <c r="B33" s="28">
+        <f>COUNTA(A2:A32)</f>
         <v/>
       </c>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E29" s="30">
-        <f>SUM(E2:E28)</f>
+      <c r="E33" s="30">
+        <f>SUM(E2:E32)</f>
         <v/>
       </c>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="27" t="n"/>
+      <c r="J33" s="27" t="n"/>
+      <c r="K33" s="27" t="n"/>
+      <c r="L33" s="27" t="n"/>
+      <c r="M33" s="27" t="n"/>
+      <c r="N33" s="27" t="n"/>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>Seller Initiated Delay</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P22" s="19" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>Deliveryattempted Unabletocontactrecipient</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>Unabletocontactrecipient Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P34" s="19" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P35" s="23" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="N41" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O64" s="19" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="N65" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O65" s="23" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t>Unabletocontactrecipient Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L3" s="24" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P4" s="19" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -9726,7 +9726,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="41" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="33" customWidth="1" min="14" max="14"/>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>Seller Initiated Delay</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -11440,12 +11440,12 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P22" s="19" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>Deliveryattempted Unabletocontactrecipient</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -5854,7 +5854,7 @@
       </c>
       <c r="P57" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O63" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P63" s="23" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P32" s="19" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1064,6 +1064,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1145,6 +1147,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1178,6 +1190,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1259,6 +1273,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1292,6 +1316,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1373,6 +1399,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1406,6 +1442,8 @@
     <col width="33" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1489,6 +1527,16 @@
           <t>Feedback Received (Yes/No)</t>
         </is>
       </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
@@ -1567,6 +1615,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q2" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R2" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
@@ -1645,6 +1703,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q3" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
@@ -1723,6 +1791,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -1801,6 +1879,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>SF3158681570SPF</t>
+        </is>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -1879,6 +1967,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q6" s="19" t="inlineStr">
+        <is>
+          <t>19041933834995</t>
+        </is>
+      </c>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933834995</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
@@ -1957,6 +2055,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>19041933767110</t>
+        </is>
+      </c>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933767110</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -2035,6 +2143,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q8" s="19" t="inlineStr">
+        <is>
+          <t>SF3158681535SPF</t>
+        </is>
+      </c>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
@@ -2113,6 +2231,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>7D125041276</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D125041276</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -2191,6 +2319,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q10" s="19" t="inlineStr">
+        <is>
+          <t>143263608413636</t>
+        </is>
+      </c>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/143263608413636</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
@@ -2269,6 +2407,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q11" s="23" t="inlineStr">
+        <is>
+          <t>SF3622719795KR</t>
+        </is>
+      </c>
+      <c r="R11" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -2347,6 +2495,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q12" s="19" t="inlineStr">
+        <is>
+          <t>19041933357982</t>
+        </is>
+      </c>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933357982</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -2425,6 +2583,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>19041933358111</t>
+        </is>
+      </c>
+      <c r="R13" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933358111</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -2503,6 +2671,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q14" s="19" t="inlineStr">
+        <is>
+          <t>19041933375224</t>
+        </is>
+      </c>
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933375224</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
@@ -2581,6 +2759,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>143263612093343</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/143263612093343</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -2659,6 +2847,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q16" s="19" t="inlineStr">
+        <is>
+          <t>370577344761</t>
+        </is>
+      </c>
+      <c r="R16" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370577344761</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -2737,6 +2935,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q17" s="23" t="inlineStr">
+        <is>
+          <t>14112362996290</t>
+        </is>
+      </c>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362996290</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -2815,6 +3023,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q18" s="19" t="inlineStr">
+        <is>
+          <t>143263608436527</t>
+        </is>
+      </c>
+      <c r="R18" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/143263608436527</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
@@ -2893,6 +3111,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q19" s="23" t="inlineStr">
+        <is>
+          <t>370574614355</t>
+        </is>
+      </c>
+      <c r="R19" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370574614355</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -2971,6 +3199,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q20" s="19" t="inlineStr">
+        <is>
+          <t>SF3158680701SPF</t>
+        </is>
+      </c>
+      <c r="R20" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -3049,6 +3287,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q21" s="23" t="inlineStr">
+        <is>
+          <t>370554649599</t>
+        </is>
+      </c>
+      <c r="R21" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370554649599</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
@@ -3127,6 +3375,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q22" s="19" t="inlineStr">
+        <is>
+          <t>370552365989</t>
+        </is>
+      </c>
+      <c r="R22" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370552365989</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
@@ -3205,6 +3463,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q23" s="23" t="inlineStr">
+        <is>
+          <t>1091393193440</t>
+        </is>
+      </c>
+      <c r="R23" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393193440</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
@@ -3283,6 +3551,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q24" s="19" t="inlineStr">
+        <is>
+          <t>SF3158680814SPF</t>
+        </is>
+      </c>
+      <c r="R24" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -3361,6 +3639,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q25" s="23" t="inlineStr">
+        <is>
+          <t>7D131505337</t>
+        </is>
+      </c>
+      <c r="R25" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131505337</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
@@ -3439,6 +3727,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q26" s="19" t="inlineStr">
+        <is>
+          <t>370553698802</t>
+        </is>
+      </c>
+      <c r="R26" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370553698802</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
@@ -3517,6 +3815,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q27" s="23" t="inlineStr">
+        <is>
+          <t>370550963576</t>
+        </is>
+      </c>
+      <c r="R27" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370550963576</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -3595,6 +3903,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q28" s="19" t="inlineStr">
+        <is>
+          <t>14112362403829</t>
+        </is>
+      </c>
+      <c r="R28" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
@@ -3673,6 +3991,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q29" s="23" t="inlineStr">
+        <is>
+          <t>1091393138630</t>
+        </is>
+      </c>
+      <c r="R29" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -3751,6 +4079,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q30" s="19" t="inlineStr">
+        <is>
+          <t>7D131502192</t>
+        </is>
+      </c>
+      <c r="R30" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
@@ -3829,6 +4167,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q31" s="23" t="inlineStr">
+        <is>
+          <t>7D131501705</t>
+        </is>
+      </c>
+      <c r="R31" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -3907,6 +4255,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q32" s="19" t="inlineStr">
+        <is>
+          <t>370526573181</t>
+        </is>
+      </c>
+      <c r="R32" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370526573181</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
@@ -3985,6 +4343,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q33" s="23" t="inlineStr">
+        <is>
+          <t>14112365216334</t>
+        </is>
+      </c>
+      <c r="R33" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
@@ -4063,6 +4431,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q34" s="19" t="inlineStr">
+        <is>
+          <t>370503334064</t>
+        </is>
+      </c>
+      <c r="R34" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503334064</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
@@ -4141,6 +4519,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q35" s="23" t="inlineStr">
+        <is>
+          <t>370503560906</t>
+        </is>
+      </c>
+      <c r="R35" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503560906</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -4219,6 +4607,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q36" s="19" t="inlineStr">
+        <is>
+          <t>19041932647740</t>
+        </is>
+      </c>
+      <c r="R36" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
@@ -4297,6 +4695,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q37" s="23" t="inlineStr">
+        <is>
+          <t>370494726459</t>
+        </is>
+      </c>
+      <c r="R37" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370494726459</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
@@ -4375,6 +4783,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q38" s="19" t="inlineStr">
+        <is>
+          <t>7D131169474</t>
+        </is>
+      </c>
+      <c r="R38" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
@@ -4453,6 +4871,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q39" s="23" t="inlineStr">
+        <is>
+          <t>SRSC0319007800</t>
+        </is>
+      </c>
+      <c r="R39" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
@@ -4531,6 +4959,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q40" s="19" t="inlineStr">
+        <is>
+          <t>SF3593208175KR</t>
+        </is>
+      </c>
+      <c r="R40" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
@@ -4609,6 +5047,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q41" s="23" t="inlineStr">
+        <is>
+          <t>14112364415189</t>
+        </is>
+      </c>
+      <c r="R41" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
@@ -4687,6 +5135,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q42" s="19" t="inlineStr">
+        <is>
+          <t>SRSC9436482183</t>
+        </is>
+      </c>
+      <c r="R42" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
@@ -4765,6 +5223,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q43" s="23" t="inlineStr">
+        <is>
+          <t>SF3158678399SPF</t>
+        </is>
+      </c>
+      <c r="R43" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
@@ -4843,6 +5311,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q44" s="19" t="inlineStr">
+        <is>
+          <t>14112363521699</t>
+        </is>
+      </c>
+      <c r="R44" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
@@ -4921,6 +5399,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q45" s="23" t="inlineStr">
+        <is>
+          <t>14112364314371</t>
+        </is>
+      </c>
+      <c r="R45" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="19" t="inlineStr">
@@ -4999,6 +5487,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q46" s="19" t="inlineStr">
+        <is>
+          <t>14112363687734</t>
+        </is>
+      </c>
+      <c r="R46" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
@@ -5077,6 +5575,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q47" s="23" t="inlineStr">
+        <is>
+          <t>370430051263</t>
+        </is>
+      </c>
+      <c r="R47" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370430051263</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="19" t="inlineStr">
@@ -5155,6 +5663,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q48" s="19" t="inlineStr">
+        <is>
+          <t>14112367080297</t>
+        </is>
+      </c>
+      <c r="R48" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
@@ -5233,6 +5751,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q49" s="23" t="inlineStr">
+        <is>
+          <t>370429882984</t>
+        </is>
+      </c>
+      <c r="R49" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429882984</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="19" t="inlineStr">
@@ -5311,6 +5839,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q50" s="19" t="inlineStr">
+        <is>
+          <t>14112365054938</t>
+        </is>
+      </c>
+      <c r="R50" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
@@ -5389,6 +5927,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q51" s="23" t="inlineStr">
+        <is>
+          <t>SF3586915332KR</t>
+        </is>
+      </c>
+      <c r="R51" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="19" t="inlineStr">
@@ -5467,6 +6015,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q52" s="19" t="inlineStr">
+        <is>
+          <t>14112362848987</t>
+        </is>
+      </c>
+      <c r="R52" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
@@ -5545,6 +6103,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q53" s="23" t="inlineStr">
+        <is>
+          <t>370429573110</t>
+        </is>
+      </c>
+      <c r="R53" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429573110</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
@@ -5623,6 +6191,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q54" s="19" t="inlineStr">
+        <is>
+          <t>14112363585911</t>
+        </is>
+      </c>
+      <c r="R54" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
@@ -5701,6 +6279,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q55" s="23" t="inlineStr">
+        <is>
+          <t>7D131457369</t>
+        </is>
+      </c>
+      <c r="R55" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="19" t="inlineStr">
@@ -5779,6 +6367,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q56" s="19" t="inlineStr">
+        <is>
+          <t>370395354997</t>
+        </is>
+      </c>
+      <c r="R56" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370395354997</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
@@ -5857,6 +6455,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q57" s="23" t="inlineStr">
+        <is>
+          <t>SRSC9946388102</t>
+        </is>
+      </c>
+      <c r="R57" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="19" t="inlineStr">
@@ -5935,6 +6543,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q58" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
@@ -6013,6 +6631,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q59" s="23" t="inlineStr">
+        <is>
+          <t>SF3576445793KR</t>
+        </is>
+      </c>
+      <c r="R59" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="19" t="inlineStr">
@@ -6091,6 +6719,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q60" s="19" t="inlineStr">
+        <is>
+          <t>SRSC3884345902</t>
+        </is>
+      </c>
+      <c r="R60" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
@@ -6169,6 +6807,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q61" s="23" t="inlineStr">
+        <is>
+          <t>370384504495</t>
+        </is>
+      </c>
+      <c r="R61" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370384504495</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="19" t="inlineStr">
@@ -6247,6 +6895,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q62" s="19" t="inlineStr">
+        <is>
+          <t>SRSP2020476035</t>
+        </is>
+      </c>
+      <c r="R62" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
@@ -6325,6 +6983,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q63" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="19" t="inlineStr">
@@ -6403,6 +7071,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q64" s="19" t="inlineStr">
+        <is>
+          <t>1319460341769</t>
+        </is>
+      </c>
+      <c r="R64" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="23" t="inlineStr">
@@ -6481,6 +7159,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q65" s="23" t="inlineStr">
+        <is>
+          <t>1319460341773</t>
+        </is>
+      </c>
+      <c r="R65" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="19" t="inlineStr">
@@ -6559,6 +7247,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q66" s="19" t="inlineStr">
+        <is>
+          <t>14112362553816</t>
+        </is>
+      </c>
+      <c r="R66" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
@@ -6637,6 +7335,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q67" s="23" t="inlineStr">
+        <is>
+          <t>SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="R67" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="19" t="inlineStr">
@@ -6713,6 +7421,16 @@
       <c r="P68" s="19" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="Q68" s="19" t="inlineStr">
+        <is>
+          <t>14112363889759</t>
+        </is>
+      </c>
+      <c r="R68" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363889759</t>
         </is>
       </c>
     </row>
@@ -6747,6 +7465,8 @@
       <c r="N69" s="27" t="n"/>
       <c r="O69" s="27" t="n"/>
       <c r="P69" s="27" t="n"/>
+      <c r="Q69" s="27" t="n"/>
+      <c r="R69" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6759,7 +7479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6778,6 +7498,8 @@
     <col width="27" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6861,6 +7583,16 @@
           <t>Feedback Received (Yes/No)</t>
         </is>
       </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
@@ -6939,6 +7671,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q2" s="19" t="inlineStr">
+        <is>
+          <t>14112365216334</t>
+        </is>
+      </c>
+      <c r="R2" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
@@ -7017,6 +7759,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q3" s="23" t="inlineStr">
+        <is>
+          <t>370503334064</t>
+        </is>
+      </c>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503334064</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
@@ -7095,6 +7847,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>370503560906</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503560906</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -7173,6 +7935,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>19041932647740</t>
+        </is>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -7251,6 +8023,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q6" s="19" t="inlineStr">
+        <is>
+          <t>370494726459</t>
+        </is>
+      </c>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370494726459</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
@@ -7329,6 +8111,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>7D131169474</t>
+        </is>
+      </c>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -7407,6 +8199,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q8" s="19" t="inlineStr">
+        <is>
+          <t>SRSC0319007800</t>
+        </is>
+      </c>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
@@ -7485,6 +8287,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>SF3593208175KR</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -7563,6 +8375,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q10" s="19" t="inlineStr">
+        <is>
+          <t>14112364415189</t>
+        </is>
+      </c>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
@@ -7641,6 +8463,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q11" s="23" t="inlineStr">
+        <is>
+          <t>SRSC9436482183</t>
+        </is>
+      </c>
+      <c r="R11" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -7719,6 +8551,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q12" s="19" t="inlineStr">
+        <is>
+          <t>SF3158678399SPF</t>
+        </is>
+      </c>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -7797,6 +8639,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>14112363521699</t>
+        </is>
+      </c>
+      <c r="R13" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -7875,6 +8727,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q14" s="19" t="inlineStr">
+        <is>
+          <t>14112364314371</t>
+        </is>
+      </c>
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
@@ -7953,6 +8815,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>14112363687734</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -8031,6 +8903,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q16" s="19" t="inlineStr">
+        <is>
+          <t>370430051263</t>
+        </is>
+      </c>
+      <c r="R16" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370430051263</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -8109,6 +8991,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q17" s="23" t="inlineStr">
+        <is>
+          <t>14112367080297</t>
+        </is>
+      </c>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -8187,6 +9079,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q18" s="19" t="inlineStr">
+        <is>
+          <t>370429882984</t>
+        </is>
+      </c>
+      <c r="R18" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429882984</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
@@ -8265,6 +9167,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q19" s="23" t="inlineStr">
+        <is>
+          <t>14112365054938</t>
+        </is>
+      </c>
+      <c r="R19" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -8343,6 +9255,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q20" s="19" t="inlineStr">
+        <is>
+          <t>SF3586915332KR</t>
+        </is>
+      </c>
+      <c r="R20" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -8421,6 +9343,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q21" s="23" t="inlineStr">
+        <is>
+          <t>14112362848987</t>
+        </is>
+      </c>
+      <c r="R21" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
@@ -8499,6 +9431,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q22" s="19" t="inlineStr">
+        <is>
+          <t>370429573110</t>
+        </is>
+      </c>
+      <c r="R22" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429573110</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
@@ -8577,6 +9519,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q23" s="23" t="inlineStr">
+        <is>
+          <t>14112363585911</t>
+        </is>
+      </c>
+      <c r="R23" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
@@ -8655,6 +9607,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q24" s="19" t="inlineStr">
+        <is>
+          <t>7D131457369</t>
+        </is>
+      </c>
+      <c r="R24" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -8733,6 +9695,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q25" s="23" t="inlineStr">
+        <is>
+          <t>370395354997</t>
+        </is>
+      </c>
+      <c r="R25" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370395354997</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
@@ -8811,6 +9783,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Q26" s="19" t="inlineStr">
+        <is>
+          <t>SRSC9946388102</t>
+        </is>
+      </c>
+      <c r="R26" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
@@ -8889,6 +9871,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q27" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -8967,6 +9959,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q28" s="19" t="inlineStr">
+        <is>
+          <t>SF3576445793KR</t>
+        </is>
+      </c>
+      <c r="R28" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
@@ -9045,6 +10047,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q29" s="23" t="inlineStr">
+        <is>
+          <t>SRSC3884345902</t>
+        </is>
+      </c>
+      <c r="R29" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -9123,6 +10135,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q30" s="19" t="inlineStr">
+        <is>
+          <t>370384504495</t>
+        </is>
+      </c>
+      <c r="R30" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370384504495</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
@@ -9201,6 +10223,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q31" s="23" t="inlineStr">
+        <is>
+          <t>SRSP2020476035</t>
+        </is>
+      </c>
+      <c r="R31" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -9279,6 +10311,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q32" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
@@ -9357,6 +10399,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q33" s="23" t="inlineStr">
+        <is>
+          <t>1319460341769</t>
+        </is>
+      </c>
+      <c r="R33" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
@@ -9435,6 +10487,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q34" s="19" t="inlineStr">
+        <is>
+          <t>1319460341773</t>
+        </is>
+      </c>
+      <c r="R34" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
@@ -9513,6 +10575,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q35" s="23" t="inlineStr">
+        <is>
+          <t>14112362553816</t>
+        </is>
+      </c>
+      <c r="R35" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -9591,6 +10663,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q36" s="19" t="inlineStr">
+        <is>
+          <t>SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="R36" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
@@ -9667,6 +10749,16 @@
       <c r="P37" s="23" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" s="23" t="inlineStr">
+        <is>
+          <t>14112363889759</t>
+        </is>
+      </c>
+      <c r="R37" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363889759</t>
         </is>
       </c>
     </row>
@@ -9701,6 +10793,8 @@
       <c r="N38" s="27" t="n"/>
       <c r="O38" s="27" t="n"/>
       <c r="P38" s="27" t="n"/>
+      <c r="Q38" s="27" t="n"/>
+      <c r="R38" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9713,7 +10807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9732,6 +10826,8 @@
     <col width="33" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9815,6 +10911,16 @@
           <t>Feedback Received (Yes/No)</t>
         </is>
       </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
@@ -9893,6 +10999,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q2" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R2" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
@@ -9971,6 +11087,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q3" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
@@ -10049,6 +11175,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -10127,6 +11263,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>SF3158681570SPF</t>
+        </is>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -10205,6 +11351,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q6" s="19" t="inlineStr">
+        <is>
+          <t>19041933834995</t>
+        </is>
+      </c>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933834995</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
@@ -10283,6 +11439,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>19041933767110</t>
+        </is>
+      </c>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933767110</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -10361,6 +11527,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q8" s="19" t="inlineStr">
+        <is>
+          <t>SF3158681535SPF</t>
+        </is>
+      </c>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
@@ -10439,6 +11615,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>7D125041276</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D125041276</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -10517,6 +11703,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q10" s="19" t="inlineStr">
+        <is>
+          <t>143263608413636</t>
+        </is>
+      </c>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/143263608413636</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
@@ -10595,6 +11791,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q11" s="23" t="inlineStr">
+        <is>
+          <t>SF3622719795KR</t>
+        </is>
+      </c>
+      <c r="R11" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -10673,6 +11879,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q12" s="19" t="inlineStr">
+        <is>
+          <t>19041933357982</t>
+        </is>
+      </c>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933357982</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -10751,6 +11967,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>19041933358111</t>
+        </is>
+      </c>
+      <c r="R13" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933358111</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -10829,6 +12055,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q14" s="19" t="inlineStr">
+        <is>
+          <t>19041933375224</t>
+        </is>
+      </c>
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041933375224</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
@@ -10907,6 +12143,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>143263612093343</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/143263612093343</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -10985,6 +12231,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q16" s="19" t="inlineStr">
+        <is>
+          <t>370577344761</t>
+        </is>
+      </c>
+      <c r="R16" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370577344761</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -11063,6 +12319,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q17" s="23" t="inlineStr">
+        <is>
+          <t>14112362996290</t>
+        </is>
+      </c>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362996290</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -11141,6 +12407,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q18" s="19" t="inlineStr">
+        <is>
+          <t>143263608436527</t>
+        </is>
+      </c>
+      <c r="R18" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/143263608436527</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
@@ -11219,6 +12495,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q19" s="23" t="inlineStr">
+        <is>
+          <t>370574614355</t>
+        </is>
+      </c>
+      <c r="R19" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370574614355</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -11297,6 +12583,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q20" s="19" t="inlineStr">
+        <is>
+          <t>SF3158680701SPF</t>
+        </is>
+      </c>
+      <c r="R20" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -11375,6 +12671,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q21" s="23" t="inlineStr">
+        <is>
+          <t>370554649599</t>
+        </is>
+      </c>
+      <c r="R21" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370554649599</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
@@ -11453,6 +12759,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q22" s="19" t="inlineStr">
+        <is>
+          <t>370552365989</t>
+        </is>
+      </c>
+      <c r="R22" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370552365989</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
@@ -11531,6 +12847,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q23" s="23" t="inlineStr">
+        <is>
+          <t>1091393193440</t>
+        </is>
+      </c>
+      <c r="R23" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393193440</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
@@ -11609,6 +12935,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q24" s="19" t="inlineStr">
+        <is>
+          <t>SF3158680814SPF</t>
+        </is>
+      </c>
+      <c r="R24" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -11687,6 +13023,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q25" s="23" t="inlineStr">
+        <is>
+          <t>7D131505337</t>
+        </is>
+      </c>
+      <c r="R25" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131505337</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
@@ -11765,6 +13111,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q26" s="19" t="inlineStr">
+        <is>
+          <t>370553698802</t>
+        </is>
+      </c>
+      <c r="R26" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370553698802</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
@@ -11843,6 +13199,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q27" s="23" t="inlineStr">
+        <is>
+          <t>370550963576</t>
+        </is>
+      </c>
+      <c r="R27" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370550963576</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -11921,6 +13287,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q28" s="19" t="inlineStr">
+        <is>
+          <t>14112362403829</t>
+        </is>
+      </c>
+      <c r="R28" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
@@ -11999,6 +13375,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q29" s="23" t="inlineStr">
+        <is>
+          <t>1091393138630</t>
+        </is>
+      </c>
+      <c r="R29" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -12077,6 +13463,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q30" s="19" t="inlineStr">
+        <is>
+          <t>7D131502192</t>
+        </is>
+      </c>
+      <c r="R30" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
@@ -12155,6 +13551,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Q31" s="23" t="inlineStr">
+        <is>
+          <t>7D131501705</t>
+        </is>
+      </c>
+      <c r="R31" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -12231,6 +13637,16 @@
       <c r="P32" s="19" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="Q32" s="19" t="inlineStr">
+        <is>
+          <t>370526573181</t>
+        </is>
+      </c>
+      <c r="R32" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370526573181</t>
         </is>
       </c>
     </row>
@@ -12265,6 +13681,8 @@
       <c r="N33" s="27" t="n"/>
       <c r="O33" s="27" t="n"/>
       <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12277,7 +13695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12296,6 +13714,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12377,6 +13797,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -12391,7 +13821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12410,6 +13840,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12491,6 +13923,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -12505,7 +13947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12524,6 +13966,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12605,6 +14049,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -12619,7 +14073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12638,6 +14092,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12719,6 +14175,16 @@
       <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Feedback Received (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
         </is>
       </c>
     </row>
@@ -12733,7 +14199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12752,6 +14218,8 @@
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12835,6 +14303,16 @@
           <t>Feedback Received (Yes/No)</t>
         </is>
       </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>AWB Code</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>Tracking Link</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -709,22 +709,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>102862</v>
+        <v>107964</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9726</v>
+        <v>1032</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>93136</v>
+        <v>106932</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.01408450704225352</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.119047619047619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -774,14 +774,14 @@
     <row r="9" ht="20" customHeight="1">
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>46174</v>
@@ -796,36 +796,36 @@
     <row r="10" ht="20" customHeight="1">
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>6234</v>
+        <v>5022</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>50808</v>
+        <v>55910</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>8636</v>
+        <v>6234</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>46235</v>
@@ -840,14 +840,14 @@
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
         <v>6</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>9805</v>
+        <v>8636</v>
       </c>
       <c r="F12" s="18" t="n">
         <v>46266</v>
@@ -862,14 +862,14 @@
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>21468</v>
+        <v>9805</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>46296</v>
@@ -884,14 +884,14 @@
     <row r="14" ht="20" customHeight="1">
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>3534</v>
+        <v>21468</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>46327</v>
@@ -906,14 +906,14 @@
     <row r="15" ht="20" customHeight="1">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>6040</v>
+        <v>3534</v>
       </c>
       <c r="F15" s="14" t="n">
         <v>46357</v>
@@ -928,14 +928,14 @@
     <row r="16" ht="20" customHeight="1">
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>10144</v>
+        <v>6040</v>
       </c>
       <c r="F16" s="18" t="n">
         <v>46388</v>
@@ -950,14 +950,14 @@
     <row r="17" ht="20" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1290</v>
+        <v>10144</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>46419</v>
@@ -972,14 +972,14 @@
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>16476</v>
+        <v>1290</v>
       </c>
       <c r="F18" s="18" t="n">
         <v>46447</v>
@@ -994,39 +994,52 @@
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>7980</v>
+        <v>16476</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>9012</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
         <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>9012</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
           <t>22-06-2026</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D22" s="17" t="n">
         <v>1112</v>
       </c>
     </row>
@@ -1423,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1436,14 +1449,14 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1541,24 +1554,24 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>#1148</t>
+          <t>#1152</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>Amirtha Varshini</t>
+          <t>Pooja Akiwate</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - L</t>
+          <t>Daisy Dusk Yellow - XXL</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
@@ -1592,12 +1605,12 @@
       </c>
       <c r="L2" s="20" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Shirol</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>'627007</t>
+          <t>'416122</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
@@ -1629,24 +1642,24 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>#1147</t>
+          <t>#1151</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Vishalini Priya</t>
+          <t>Subha Chandrasekar</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
+          <t>Cocoa Elegance Top - XL</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2780</v>
+        <v>1390</v>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
@@ -1680,12 +1693,12 @@
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>'600117</t>
+          <t>'600083</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
@@ -1717,24 +1730,24 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>#1146</t>
+          <t>#1150</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Astin</t>
+          <t>Kavitha Sharma</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Geometric Glam - L, Purple Panache - L</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>2243</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
@@ -1768,12 +1781,12 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Vizianagaram District</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>'613007</t>
+          <t>'535558</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
@@ -1805,38 +1818,38 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>#1144</t>
+          <t>#1149</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Deepak Raj</t>
+          <t>Princy Raj</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Rose Charm Top - S</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1211</v>
+        <v>1290</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -1856,17 +1869,17 @@
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>'600045</t>
+          <t>'613204</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -1881,50 +1894,50 @@
       </c>
       <c r="Q5" s="23" t="inlineStr">
         <is>
-          <t>SF3158681570SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>#1143</t>
+          <t>#1148</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Nandhini V</t>
+          <t>Amirtha Varshini</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - M</t>
+          <t>Plum Pinstripe - L</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -1944,17 +1957,17 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>'631601</t>
+          <t>'627007</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -1969,50 +1982,50 @@
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>19041933834995</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933834995</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>#1142</t>
+          <t>#1147</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Sunanda P</t>
+          <t>Vishalini Priya</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
+          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -2032,17 +2045,17 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>'560011</t>
+          <t>'600117</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -2057,36 +2070,36 @@
       </c>
       <c r="Q7" s="23" t="inlineStr">
         <is>
-          <t>19041933767110</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933767110</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>#1141</t>
+          <t>#1146</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Priya Kathiravan</t>
+          <t>Astin</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Geometric Glam - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1211</v>
+        <v>2243</v>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
@@ -2120,17 +2133,17 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Sathyamoorthy Nagar</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>'614804</t>
+          <t>'613007</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -2145,50 +2158,50 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>SF3158681535SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>#1139</t>
+          <t>#1144</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Keerthana C</t>
+          <t>Deepak Raj</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Rose Charm Top - S</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1112</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -2213,12 +2226,12 @@
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>'600091</t>
+          <t>'600045</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR PICKUP</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -2233,50 +2246,50 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>7D125041276</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D125041276</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>#1138</t>
+          <t>#1143</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Preeti Niranjan</t>
+          <t>Nandhini V</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - S</t>
+          <t>Wine Blossom Top - M</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
         <v>46207</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -2296,17 +2309,17 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>Karwar Uttar Kannada</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>'581400</t>
+          <t>'631601</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -2321,36 +2334,36 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>143263608413636</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608413636</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>#1137</t>
+          <t>#1142</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Sasi Gouru</t>
+          <t>Sunanda P</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
         <v>46207</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1211</v>
+        <v>2779</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
@@ -2384,17 +2397,17 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>'500090</t>
+          <t>'560011</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -2409,50 +2422,50 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>SF3622719795KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>#1136</t>
+          <t>#1141</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Bala Murali</t>
+          <t>Priya Kathiravan</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1290</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -2472,17 +2485,17 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram District</t>
+          <t>Sathyamoorthy Nagar</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>'623707</t>
+          <t>'614804</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -2497,33 +2510,33 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>19041933357982</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933357982</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>#1135</t>
+          <t>#1139</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Anusha Bekkanti</t>
+          <t>Keerthana C</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>1112</v>
@@ -2560,17 +2573,17 @@
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Harlur Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>'560102</t>
+          <t>'600091</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -2585,36 +2598,36 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>19041933358111</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933358111</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>#1134</t>
+          <t>#1138</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Kaylash Pinkky</t>
+          <t>Preeti Niranjan</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Wine Blossom Top - S</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
@@ -2648,17 +2661,17 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Karwar Uttar Kannada</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>'500010</t>
+          <t>'581400</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -2673,36 +2686,36 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>19041933375224</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933375224</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>#1133</t>
+          <t>#1137</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Deva E</t>
+          <t>Sasi Gouru</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>3096</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -2736,17 +2749,17 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>'600056</t>
+          <t>'500090</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -2761,50 +2774,50 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>143263612093343</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263612093343</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>#1132</t>
+          <t>#1136</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Sudha Manikandan</t>
+          <t>Bala Murali</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
         <v>46206</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -2824,17 +2837,17 @@
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Paramakudi , Ramanathapuram District</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>'625016</t>
+          <t>'623707</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -2849,50 +2862,50 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>370577344761</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370577344761</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>#1131</t>
+          <t>#1135</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Sindhuri Kalidindi</t>
+          <t>Anusha Bekkanti</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
         <v>46206</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -2912,17 +2925,17 @@
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Harlur Bengaluru</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>'146024</t>
+          <t>'560102</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -2937,50 +2950,50 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>14112362996290</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362996290</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>#1130</t>
+          <t>#1134</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Sudha G</t>
+          <t>Kaylash Pinkky</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>3336</v>
+        <v>1131</v>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
@@ -3000,17 +3013,17 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>'639001</t>
+          <t>'500010</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -3025,36 +3038,36 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>143263608436527</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608436527</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>#1129</t>
+          <t>#1133</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Mamillapalli Sivakumari</t>
+          <t>Deva E</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>1112</v>
+        <v>3096</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -3088,17 +3101,17 @@
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>Thiruvallur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>'601204</t>
+          <t>'600056</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -3113,36 +3126,36 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>370574614355</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370574614355</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>#1128</t>
+          <t>#1132</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Shanmuga Priya Priya</t>
+          <t>Sudha Manikandan</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - M</t>
+          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>1032</v>
+        <v>2144</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
@@ -3176,22 +3189,22 @@
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>'632009</t>
+          <t>'625016</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -3201,36 +3214,36 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>SF3158680701SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>#1127</t>
+          <t>#1131</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Rajani Reddy</t>
+          <t>Sindhuri Kalidindi</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - M</t>
+          <t>Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
@@ -3264,17 +3277,17 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>'560076</t>
+          <t>'146024</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -3289,36 +3302,36 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>370554649599</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370554649599</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>#1126</t>
+          <t>#1130</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Sulochana N</t>
+          <t>Sudha G</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Rosy Mist - M</t>
+          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>1890</v>
+        <v>3336</v>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
@@ -3352,22 +3365,22 @@
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>'515002</t>
+          <t>'639001</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P22" s="19" t="inlineStr">
@@ -3377,36 +3390,36 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>370552365989</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370552365989</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>#1125</t>
+          <t>#1129</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Subha A.R</t>
+          <t>Mamillapalli Sivakumari</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - S</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>2680</v>
+        <v>1112</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -3435,22 +3448,22 @@
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>Chennai 600107</t>
+          <t>Thiruvallur</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>'600107</t>
+          <t>'601204</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -3465,36 +3478,36 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>1091393193440</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393193440</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>#1124</t>
+          <t>#1128</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Anusha Madhukar</t>
+          <t>Shanmuga Priya Priya</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
@@ -3528,17 +3541,17 @@
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>'500035</t>
+          <t>'632009</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -3553,50 +3566,50 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>SF3158680814SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>#1123</t>
+          <t>#1127</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Ujwala Gajula</t>
+          <t>Rajani Reddy</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
+          <t>Sunset Petal - M</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>2064</v>
+        <v>1112</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -3616,17 +3629,17 @@
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>'500019</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -3641,50 +3654,50 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>7D131505337</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131505337</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>#1122</t>
+          <t>#1126</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Suganya Suganyasridhar</t>
+          <t>Sulochana N</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - XL, Purple Panache - XL</t>
+          <t>Rosy Mist - M</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>2064</v>
+        <v>1890</v>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -3704,22 +3717,22 @@
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Anantapur</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>'606902</t>
+          <t>'515002</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P26" s="19" t="inlineStr">
@@ -3729,36 +3742,36 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>370553698802</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370553698802</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>#1121</t>
+          <t>#1125</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Salla Mahesh</t>
+          <t>Subha A.R</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
+          <t>Sunset Petal - L, Teal Tempo - S</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2144</v>
+        <v>2680</v>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
@@ -3792,17 +3805,17 @@
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>Godavarikhani</t>
+          <t>Chennai 600107</t>
         </is>
       </c>
       <c r="M27" s="26" t="inlineStr">
         <is>
-          <t>'505210</t>
+          <t>'600107</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -3817,55 +3830,55 @@
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
-          <t>370550963576</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370550963576</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>#1120</t>
+          <t>#1124</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Nisha J</t>
+          <t>Anusha Madhukar</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
@@ -3880,17 +3893,17 @@
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
-          <t>Chengalpattu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>'603002</t>
+          <t>'500035</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>CANCELED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -3905,50 +3918,50 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>14112362403829</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362403829</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>#1119</t>
+          <t>#1123</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Vijayasri S Narendran</t>
+          <t>Ujwala Gajula</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Blossom Taupe Chic Set - 2XL</t>
+          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>1890</v>
+        <v>2064</v>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -3963,22 +3976,22 @@
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>Avadi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>'600062</t>
+          <t>'500019</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -3993,50 +4006,50 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>1091393138630</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393138630</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>#1118</t>
+          <t>#1122</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Aswathy P</t>
+          <t>Suganya Suganyasridhar</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - M</t>
+          <t>Bold Basil - XL, Purple Panache - XL</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>1032</v>
+        <v>2064</v>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -4056,17 +4069,17 @@
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>'682030</t>
+          <t>'606902</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -4081,50 +4094,50 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>7D131502192</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131502192</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>#1117</t>
+          <t>#1121</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Dr Jovin Jose</t>
+          <t>Salla Mahesh</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - M</t>
+          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -4144,17 +4157,17 @@
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>Kanhangad</t>
+          <t>Godavarikhani</t>
         </is>
       </c>
       <c r="M31" s="26" t="inlineStr">
         <is>
-          <t>'671326</t>
+          <t>'505210</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -4169,55 +4182,55 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>7D131501705</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131501705</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>#1115</t>
+          <t>#1120</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Vidya Jothi</t>
+          <t>Nisha J</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Dainty Dots Teal - 2XL</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1390</v>
+        <v>1032</v>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J32" s="19" t="inlineStr">
@@ -4227,22 +4240,22 @@
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
-          <t>Deliveryattempted Unabletocontactrecipient</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chengalpattu</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>'641062</t>
+          <t>'603002</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
@@ -4257,50 +4270,50 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>370526573181</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370526573181</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>#1114</t>
+          <t>#1119</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Kruthika Vignesh</t>
+          <t>Vijayasri S Narendran</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Blossom Taupe Chic Set - 2XL</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>1112</v>
+        <v>1890</v>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -4320,17 +4333,17 @@
       </c>
       <c r="L33" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Avadi</t>
         </is>
       </c>
       <c r="M33" s="26" t="inlineStr">
         <is>
-          <t>'600078</t>
+          <t>'600062</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -4345,33 +4358,33 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>14112365216334</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112365216334</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>#1113</t>
+          <t>#1118</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Maha Jayaraman</t>
+          <t>Aswathy P</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - XL</t>
+          <t>Urban Ruby - M</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>1032</v>
@@ -4408,22 +4421,22 @@
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>'605008</t>
+          <t>'682030</t>
         </is>
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P34" s="19" t="inlineStr">
@@ -4433,33 +4446,33 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>370503334064</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370503334064</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>#1112</t>
+          <t>#1117</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>Perikala Vivekananda</t>
+          <t>Dr Jovin Jose</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - S</t>
+          <t>Daisy Dusk Yellow - M</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>1112</v>
@@ -4496,22 +4509,22 @@
       </c>
       <c r="L35" s="24" t="inlineStr">
         <is>
-          <t>Tenali</t>
+          <t>Kanhangad</t>
         </is>
       </c>
       <c r="M35" s="26" t="inlineStr">
         <is>
-          <t>'522201</t>
+          <t>'671326</t>
         </is>
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P35" s="23" t="inlineStr">
@@ -4521,36 +4534,36 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>370503560906</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370503560906</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>#1111</t>
+          <t>#1115</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Jeeva Ramprabu</t>
+          <t>Vidya Jothi</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>2784</v>
+        <v>1390</v>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
@@ -4584,22 +4597,22 @@
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
         <is>
-          <t>'626707</t>
+          <t>'641062</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P36" s="19" t="inlineStr">
@@ -4609,36 +4622,36 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>19041932647740</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041932647740</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>#1110</t>
+          <t>#1114</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Sharanyaa K</t>
+          <t>Kruthika Vignesh</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - M, Sunset Petal - M</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>2144</v>
+        <v>1112</v>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
@@ -4672,22 +4685,22 @@
       </c>
       <c r="L37" s="24" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M37" s="26" t="inlineStr">
         <is>
-          <t>'605011</t>
+          <t>'600078</t>
         </is>
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P37" s="23" t="inlineStr">
@@ -4697,50 +4710,50 @@
       </c>
       <c r="Q37" s="23" t="inlineStr">
         <is>
-          <t>370494726459</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370494726459</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>#1109</t>
+          <t>#1113</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Anusha Anusha</t>
+          <t>Maha Jayaraman</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - 3XL</t>
+          <t>Dainty Dots Teal - XL</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>1032</v>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I38" s="19" t="inlineStr">
@@ -4760,22 +4773,22 @@
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
-          <t>Hyderbad</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
         <is>
-          <t>'500086</t>
+          <t>'605008</t>
         </is>
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P38" s="19" t="inlineStr">
@@ -4785,50 +4798,50 @@
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>
-          <t>7D131169474</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R38" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131169474</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>#1108</t>
+          <t>#1112</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Bharathi Dinesh</t>
+          <t>Perikala Vivekananda</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - S</t>
         </is>
       </c>
       <c r="D39" s="11" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I39" s="23" t="inlineStr">
@@ -4848,22 +4861,22 @@
       </c>
       <c r="L39" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Tenali</t>
         </is>
       </c>
       <c r="M39" s="26" t="inlineStr">
         <is>
-          <t>'600077</t>
+          <t>'522201</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O39" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P39" s="23" t="inlineStr">
@@ -4873,36 +4886,36 @@
       </c>
       <c r="Q39" s="23" t="inlineStr">
         <is>
-          <t>SRSC0319007800</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>#1107</t>
+          <t>#1111</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Meghana R</t>
+          <t>Jeeva Ramprabu</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Aranya Grace Anarkali Dress - XL</t>
+          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>2680</v>
+        <v>2784</v>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
@@ -4921,32 +4934,32 @@
       </c>
       <c r="I40" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J40" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K40" s="20" t="inlineStr">
         <is>
-          <t>Customer Cancelled Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
-          <t>Kolar</t>
+          <t>Paramakudi , Ramanathapuram</t>
         </is>
       </c>
       <c r="M40" s="22" t="inlineStr">
         <is>
-          <t>'563102</t>
+          <t>'626707</t>
         </is>
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr">
@@ -4961,29 +4974,29 @@
       </c>
       <c r="Q40" s="19" t="inlineStr">
         <is>
-          <t>SF3593208175KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R40" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>#1105</t>
+          <t>#1110</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Akila Senthil</t>
+          <t>Sharanyaa K</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
+          <t>Moss Majesty - M, Sunset Petal - M</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
@@ -4994,47 +5007,47 @@
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K41" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L41" s="24" t="inlineStr">
         <is>
-          <t>Salem</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="M41" s="26" t="inlineStr">
         <is>
-          <t>'636005</t>
+          <t>'605011</t>
         </is>
       </c>
       <c r="N41" s="23" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
@@ -5049,36 +5062,36 @@
       </c>
       <c r="Q41" s="23" t="inlineStr">
         <is>
-          <t>14112364415189</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112364415189</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>#1104</t>
+          <t>#1109</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Gopal Kowsi</t>
+          <t>Anusha Anusha</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Purple Panache - 3XL</t>
         </is>
       </c>
       <c r="D42" s="15" t="n">
         <v>46202</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
@@ -5112,17 +5125,17 @@
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>Vanavasi</t>
+          <t>Hyderbad</t>
         </is>
       </c>
       <c r="M42" s="22" t="inlineStr">
         <is>
-          <t>'636457</t>
+          <t>'500086</t>
         </is>
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O42" s="19" t="inlineStr">
@@ -5137,36 +5150,36 @@
       </c>
       <c r="Q42" s="19" t="inlineStr">
         <is>
-          <t>SRSC9436482183</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R42" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>#1103</t>
+          <t>#1108</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>Praveena Manoharan</t>
+          <t>Bharathi Dinesh</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - XL</t>
+          <t>Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
@@ -5205,17 +5218,17 @@
       </c>
       <c r="M43" s="26" t="inlineStr">
         <is>
-          <t>'600100</t>
+          <t>'600077</t>
         </is>
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O43" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P43" s="23" t="inlineStr">
@@ -5225,36 +5238,36 @@
       </c>
       <c r="Q43" s="23" t="inlineStr">
         <is>
-          <t>SF3158678399SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>#1102</t>
+          <t>#1107</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Smitha Ag</t>
+          <t>Meghana R</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L</t>
+          <t>Aranya Grace Anarkali Dress - XL</t>
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>1032</v>
+        <v>2680</v>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
@@ -5288,17 +5301,17 @@
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>Muvattupuzha</t>
+          <t>Kolar</t>
         </is>
       </c>
       <c r="M44" s="22" t="inlineStr">
         <is>
-          <t>'686661</t>
+          <t>'563102</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr">
@@ -5313,50 +5326,50 @@
       </c>
       <c r="Q44" s="19" t="inlineStr">
         <is>
-          <t>14112363521699</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R44" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363521699</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>#1101</t>
+          <t>#1105</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>Apsara Reddy</t>
+          <t>Akila Senthil</t>
         </is>
       </c>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
+          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>3176</v>
+        <v>2144</v>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I45" s="23" t="inlineStr">
@@ -5376,22 +5389,22 @@
       </c>
       <c r="L45" s="24" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Salem</t>
         </is>
       </c>
       <c r="M45" s="26" t="inlineStr">
         <is>
-          <t>'518003</t>
+          <t>'636005</t>
         </is>
       </c>
       <c r="N45" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O45" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P45" s="23" t="inlineStr">
@@ -5401,36 +5414,36 @@
       </c>
       <c r="Q45" s="23" t="inlineStr">
         <is>
-          <t>14112364314371</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112364314371</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>#1100</t>
+          <t>#1104</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Shailu Reddy</t>
+          <t>Gopal Kowsi</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - 2XL</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D46" s="15" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>1290</v>
+        <v>1112</v>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
@@ -5464,17 +5477,17 @@
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Vanavasi</t>
         </is>
       </c>
       <c r="M46" s="22" t="inlineStr">
         <is>
-          <t>'506002</t>
+          <t>'636457</t>
         </is>
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O46" s="19" t="inlineStr">
@@ -5489,50 +5502,50 @@
       </c>
       <c r="Q46" s="19" t="inlineStr">
         <is>
-          <t>14112363687734</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363687734</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>#1099</t>
+          <t>#1103</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Durai Kannan</t>
+          <t>Praveena Manoharan</t>
         </is>
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - L</t>
+          <t>Purple Panache - XL</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>1032</v>
+        <v>1290</v>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I47" s="23" t="inlineStr">
@@ -5552,17 +5565,17 @@
       </c>
       <c r="L47" s="24" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M47" s="26" t="inlineStr">
         <is>
-          <t>'641008</t>
+          <t>'600100</t>
         </is>
       </c>
       <c r="N47" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O47" s="23" t="inlineStr">
@@ -5577,29 +5590,29 @@
       </c>
       <c r="Q47" s="23" t="inlineStr">
         <is>
-          <t>370430051263</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370430051263</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>#1098</t>
+          <t>#1102</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>B Padmapriya</t>
+          <t>Smitha Ag</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - L</t>
+          <t>Mystic Mist Red - L</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
@@ -5640,22 +5653,22 @@
       </c>
       <c r="L48" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Muvattupuzha</t>
         </is>
       </c>
       <c r="M48" s="22" t="inlineStr">
         <is>
-          <t>'500017</t>
+          <t>'686661</t>
         </is>
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O48" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P48" s="19" t="inlineStr">
@@ -5665,36 +5678,36 @@
       </c>
       <c r="Q48" s="19" t="inlineStr">
         <is>
-          <t>14112367080297</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R48" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112367080297</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>#1097</t>
+          <t>#1101</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Apsara Reddy</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>Grape Leaf Glam - M</t>
+          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>1112</v>
+        <v>3176</v>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
@@ -5728,17 +5741,17 @@
       </c>
       <c r="L49" s="24" t="inlineStr">
         <is>
-          <t>Guntur</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="M49" s="26" t="inlineStr">
         <is>
-          <t>'522007</t>
+          <t>'518003</t>
         </is>
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O49" s="23" t="inlineStr">
@@ -5753,50 +5766,50 @@
       </c>
       <c r="Q49" s="23" t="inlineStr">
         <is>
-          <t>370429882984</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370429882984</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>#1096</t>
+          <t>#1100</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Indu Rekha</t>
+          <t>Shailu Reddy</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
+          <t>Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D50" s="15" t="n">
         <v>46200</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>2224</v>
+        <v>1290</v>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr">
@@ -5816,17 +5829,17 @@
       </c>
       <c r="L50" s="20" t="inlineStr">
         <is>
-          <t>Anantapur Urban</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="M50" s="22" t="inlineStr">
         <is>
-          <t>'515001</t>
+          <t>'506002</t>
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O50" s="19" t="inlineStr">
@@ -5841,50 +5854,50 @@
       </c>
       <c r="Q50" s="19" t="inlineStr">
         <is>
-          <t>14112365054938</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R50" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112365054938</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>#1095</t>
+          <t>#1099</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Priya Dharshini Pd</t>
+          <t>Durai Kannan</t>
         </is>
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - 2XL</t>
+          <t>Moss Majesty - L</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I51" s="23" t="inlineStr">
@@ -5904,17 +5917,17 @@
       </c>
       <c r="L51" s="24" t="inlineStr">
         <is>
-          <t>Villupuram</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M51" s="26" t="inlineStr">
         <is>
-          <t>'604204</t>
+          <t>'641008</t>
         </is>
       </c>
       <c r="N51" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O51" s="23" t="inlineStr">
@@ -5929,29 +5942,29 @@
       </c>
       <c r="Q51" s="23" t="inlineStr">
         <is>
-          <t>SF3586915332KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>#1094</t>
+          <t>#1098</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Usha .R</t>
+          <t>B Padmapriya</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 3XL</t>
+          <t>Bold Basil - L</t>
         </is>
       </c>
       <c r="D52" s="15" t="n">
@@ -5962,17 +5975,17 @@
       </c>
       <c r="F52" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
@@ -5992,22 +6005,22 @@
       </c>
       <c r="L52" s="20" t="inlineStr">
         <is>
-          <t>Hosur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M52" s="22" t="inlineStr">
         <is>
-          <t>'635109</t>
+          <t>'500017</t>
         </is>
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O52" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P52" s="19" t="inlineStr">
@@ -6017,50 +6030,50 @@
       </c>
       <c r="Q52" s="19" t="inlineStr">
         <is>
-          <t>14112362848987</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R52" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362848987</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>#1093</t>
+          <t>#1097</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Ramya Gowda</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Grape Leaf Glam - M</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I53" s="23" t="inlineStr">
@@ -6075,27 +6088,27 @@
       </c>
       <c r="K53" s="24" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L53" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Guntur</t>
         </is>
       </c>
       <c r="M53" s="26" t="inlineStr">
         <is>
-          <t>'560091</t>
+          <t>'522007</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O53" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P53" s="23" t="inlineStr">
@@ -6105,85 +6118,85 @@
       </c>
       <c r="Q53" s="23" t="inlineStr">
         <is>
-          <t>370429573110</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R53" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370429573110</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>#1092</t>
+          <t>#1096</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Kowsalya</t>
+          <t>Indu Rekha</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - S</t>
+          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
         </is>
       </c>
       <c r="D54" s="15" t="n">
         <v>46200</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>1290</v>
+        <v>2224</v>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
-          <t>Customer Not Available X Office Or Residence Closed</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L54" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Anantapur Urban</t>
         </is>
       </c>
       <c r="M54" s="22" t="inlineStr">
         <is>
-          <t>'600096</t>
+          <t>'515001</t>
         </is>
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O54" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P54" s="19" t="inlineStr">
@@ -6193,29 +6206,29 @@
       </c>
       <c r="Q54" s="19" t="inlineStr">
         <is>
-          <t>14112363585911</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R54" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363585911</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>#1091</t>
+          <t>#1095</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>Vijay Aadarsh Adarsh</t>
+          <t>Priya Dharshini Pd</t>
         </is>
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Wine Blossom Top - 2XL</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
@@ -6251,22 +6264,22 @@
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
-          <t>Receiver Requested Delivery On Another Date (Cir)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L55" s="24" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Villupuram</t>
         </is>
       </c>
       <c r="M55" s="26" t="inlineStr">
         <is>
-          <t>'641107</t>
+          <t>'604204</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O55" s="23" t="inlineStr">
@@ -6281,50 +6294,50 @@
       </c>
       <c r="Q55" s="23" t="inlineStr">
         <is>
-          <t>7D131457369</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R55" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131457369</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>#1090</t>
+          <t>#1094</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Kamal Thiyagarajan</t>
+          <t>Usha .R</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Vanya Bloom Top - S</t>
+          <t>Dainty Dots Teal - 3XL</t>
         </is>
       </c>
       <c r="D56" s="15" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F56" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr">
@@ -6344,17 +6357,17 @@
       </c>
       <c r="L56" s="20" t="inlineStr">
         <is>
-          <t>Tirupur</t>
+          <t>Hosur</t>
         </is>
       </c>
       <c r="M56" s="22" t="inlineStr">
         <is>
-          <t>'641606</t>
+          <t>'635109</t>
         </is>
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O56" s="19" t="inlineStr">
@@ -6369,36 +6382,36 @@
       </c>
       <c r="Q56" s="19" t="inlineStr">
         <is>
-          <t>370395354997</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R56" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370395354997</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>#1089</t>
+          <t>#1093</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Divya Divya</t>
+          <t>Ramya Gowda</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - L</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
@@ -6432,75 +6445,75 @@
       </c>
       <c r="L57" s="24" t="inlineStr">
         <is>
-          <t>Kuppatti</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M57" s="26" t="inlineStr">
         <is>
-          <t>'635118</t>
+          <t>'560091</t>
         </is>
       </c>
       <c r="N57" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O57" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P57" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q57" s="23" t="inlineStr">
         <is>
-          <t>SRSC9946388102</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R57" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>#1088</t>
+          <t>#1092</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Nutan Manerkar</t>
+          <t>Kowsalya</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - 2XL</t>
+          <t>Moss Majesty - S</t>
         </is>
       </c>
       <c r="D58" s="15" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>1112</v>
+        <v>1290</v>
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I58" s="19" t="inlineStr">
@@ -6520,17 +6533,17 @@
       </c>
       <c r="L58" s="20" t="inlineStr">
         <is>
-          <t>Margao</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M58" s="22" t="inlineStr">
         <is>
-          <t>'403601</t>
+          <t>'600096</t>
         </is>
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr">
@@ -6557,24 +6570,24 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>#1087</t>
+          <t>#1091</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Devi Rv</t>
+          <t>Vijay Aadarsh Adarsh</t>
         </is>
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>1290</v>
+        <v>1112</v>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
@@ -6603,22 +6616,22 @@
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
-          <t>Customer Not Contactable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L59" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M59" s="26" t="inlineStr">
         <is>
-          <t>'600110</t>
+          <t>'641107</t>
         </is>
       </c>
       <c r="N59" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O59" s="23" t="inlineStr">
@@ -6633,36 +6646,36 @@
       </c>
       <c r="Q59" s="23" t="inlineStr">
         <is>
-          <t>SF3576445793KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R59" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>#1086</t>
+          <t>#1090</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>D Keerthi</t>
+          <t>Kamal Thiyagarajan</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 3XL</t>
+          <t>Vanya Bloom Top - S</t>
         </is>
       </c>
       <c r="D60" s="15" t="n">
         <v>46198</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
@@ -6696,17 +6709,17 @@
       </c>
       <c r="L60" s="20" t="inlineStr">
         <is>
-          <t>Chittoor</t>
+          <t>Tirupur</t>
         </is>
       </c>
       <c r="M60" s="22" t="inlineStr">
         <is>
-          <t>'517234</t>
+          <t>'641606</t>
         </is>
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O60" s="19" t="inlineStr">
@@ -6721,36 +6734,36 @@
       </c>
       <c r="Q60" s="19" t="inlineStr">
         <is>
-          <t>SRSC3884345902</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R60" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>#1085</t>
+          <t>#1089</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>Mohanakrishnan Devanathan</t>
+          <t>Divya Divya</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - M</t>
+          <t>Moss Majesty - L</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
         <v>46198</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>1032</v>
+        <v>1290</v>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
@@ -6784,17 +6797,17 @@
       </c>
       <c r="L61" s="24" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Kuppatti</t>
         </is>
       </c>
       <c r="M61" s="26" t="inlineStr">
         <is>
-          <t>'605006</t>
+          <t>'635118</t>
         </is>
       </c>
       <c r="N61" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O61" s="23" t="inlineStr">
@@ -6804,34 +6817,34 @@
       </c>
       <c r="P61" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q61" s="23" t="inlineStr">
         <is>
-          <t>370384504495</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R61" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370384504495</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>#1084</t>
+          <t>#1088</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Gowri R</t>
+          <t>Nutan Manerkar</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Wine Blossom Top - 2XL</t>
         </is>
       </c>
       <c r="D62" s="15" t="n">
@@ -6872,22 +6885,22 @@
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Margao</t>
         </is>
       </c>
       <c r="M62" s="22" t="inlineStr">
         <is>
-          <t>'600096</t>
+          <t>'403601</t>
         </is>
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O62" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P62" s="19" t="inlineStr">
@@ -6897,36 +6910,36 @@
       </c>
       <c r="Q62" s="19" t="inlineStr">
         <is>
-          <t>SRSP2020476035</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R62" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>#1083</t>
+          <t>#1087</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Sukanya R</t>
+          <t>Devi Rv</t>
         </is>
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>Coral Bloom Top - M, Purple Panache - M</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
@@ -6965,17 +6978,17 @@
       </c>
       <c r="M63" s="26" t="inlineStr">
         <is>
-          <t>'600095</t>
+          <t>'600110</t>
         </is>
       </c>
       <c r="N63" s="23" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O63" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P63" s="23" t="inlineStr">
@@ -6997,24 +7010,24 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>#1082</t>
+          <t>#1086</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Harshini Rajendran</t>
+          <t>D Keerthi</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - XL</t>
+          <t>Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D64" s="15" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
@@ -7033,37 +7046,37 @@
       </c>
       <c r="I64" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J64" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K64" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Chittoor</t>
         </is>
       </c>
       <c r="M64" s="22" t="inlineStr">
         <is>
-          <t>'630003</t>
+          <t>'517234</t>
         </is>
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O64" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P64" s="19" t="inlineStr">
@@ -7073,36 +7086,36 @@
       </c>
       <c r="Q64" s="19" t="inlineStr">
         <is>
-          <t>1319460341769</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R64" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1319460341769</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>#1081</t>
+          <t>#1085</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>Harshini Rajendran</t>
+          <t>Mohanakrishnan Devanathan</t>
         </is>
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - S</t>
+          <t>Purple Panache - M</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
@@ -7121,37 +7134,37 @@
       </c>
       <c r="I65" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J65" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K65" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L65" s="24" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="M65" s="26" t="inlineStr">
         <is>
-          <t>'630003</t>
+          <t>'605006</t>
         </is>
       </c>
       <c r="N65" s="23" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O65" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P65" s="23" t="inlineStr">
@@ -7161,36 +7174,36 @@
       </c>
       <c r="Q65" s="23" t="inlineStr">
         <is>
-          <t>1319460341773</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R65" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1319460341773</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>#1080</t>
+          <t>#1084</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Chandraelectro Corporation</t>
+          <t>Gowri R</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D66" s="15" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>3176</v>
+        <v>1112</v>
       </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
@@ -7224,17 +7237,17 @@
       </c>
       <c r="L66" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M66" s="22" t="inlineStr">
         <is>
-          <t>'625001</t>
+          <t>'600096</t>
         </is>
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O66" s="19" t="inlineStr">
@@ -7249,50 +7262,50 @@
       </c>
       <c r="Q66" s="19" t="inlineStr">
         <is>
-          <t>14112362553816</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R66" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362553816</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>#1078</t>
+          <t>#1083</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>Gomathi Dhanapal</t>
+          <t>Sukanya R</t>
         </is>
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Coral Bloom Top - M, Purple Panache - M</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
         <v>46197</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I67" s="23" t="inlineStr">
@@ -7317,12 +7330,12 @@
       </c>
       <c r="M67" s="26" t="inlineStr">
         <is>
-          <t>'600073</t>
+          <t>'600095</t>
         </is>
       </c>
       <c r="N67" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O67" s="23" t="inlineStr">
@@ -7337,136 +7350,488 @@
       </c>
       <c r="Q67" s="23" t="inlineStr">
         <is>
-          <t>SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R67" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="19" t="inlineStr">
         <is>
+          <t>#1082</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C68" s="21" t="inlineStr">
+        <is>
+          <t>Urban Ruby - XL</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M68" s="22" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N68" s="19" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P68" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q68" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R68" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>#1081</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - S</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I69" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="24" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M69" s="26" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N69" s="23" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O69" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P69" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q69" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R69" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>#1080</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Chandraelectro Corporation</t>
+        </is>
+      </c>
+      <c r="C70" s="21" t="inlineStr">
+        <is>
+          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="M70" s="22" t="inlineStr">
+        <is>
+          <t>'625001</t>
+        </is>
+      </c>
+      <c r="N70" s="19" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O70" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P70" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q70" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R70" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>#1078</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>Gomathi Dhanapal</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I71" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J71" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="24" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M71" s="26" t="inlineStr">
+        <is>
+          <t>'600073</t>
+        </is>
+      </c>
+      <c r="N71" s="23" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O71" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P71" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q71" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R71" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
           <t>#1071</t>
         </is>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>Soumya Shetty</t>
         </is>
       </c>
-      <c r="C68" s="21" t="inlineStr">
+      <c r="C72" s="21" t="inlineStr">
         <is>
           <t>Sapphire Charm Top - M</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D72" s="15" t="n">
         <v>46195</v>
       </c>
-      <c r="E68" s="17" t="n">
+      <c r="E72" s="17" t="n">
         <v>1112</v>
       </c>
-      <c r="F68" s="19" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>Prepaid (Razorpay)</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I72" s="19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K68" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="20" t="inlineStr">
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="20" t="inlineStr">
         <is>
           <t>Bijapur</t>
         </is>
       </c>
-      <c r="M68" s="22" t="inlineStr">
+      <c r="M72" s="22" t="inlineStr">
         <is>
           <t>'586101</t>
         </is>
       </c>
-      <c r="N68" s="19" t="inlineStr">
-        <is>
-          <t>DELIVERED</t>
-        </is>
-      </c>
-      <c r="O68" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P68" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q68" s="19" t="inlineStr">
-        <is>
-          <t>14112363889759</t>
-        </is>
-      </c>
-      <c r="R68" s="19" t="inlineStr">
-        <is>
-          <t>https://shiprocket.co/tracking/14112363889759</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="27" t="inlineStr">
+      <c r="N72" s="19" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O72" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P72" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q72" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R72" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B69" s="28">
-        <f>COUNTA(A2:A68)</f>
+      <c r="B73" s="28">
+        <f>COUNTA(A2:A72)</f>
         <v/>
       </c>
-      <c r="C69" s="27" t="n"/>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="C73" s="27" t="n"/>
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E69" s="30">
-        <f>SUM(E2:E68)</f>
+      <c r="E73" s="30">
+        <f>SUM(E2:E72)</f>
         <v/>
       </c>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
-      <c r="H69" s="27" t="n"/>
-      <c r="I69" s="27" t="n"/>
-      <c r="J69" s="27" t="n"/>
-      <c r="K69" s="27" t="n"/>
-      <c r="L69" s="27" t="n"/>
-      <c r="M69" s="27" t="n"/>
-      <c r="N69" s="27" t="n"/>
-      <c r="O69" s="27" t="n"/>
-      <c r="P69" s="27" t="n"/>
-      <c r="Q69" s="27" t="n"/>
-      <c r="R69" s="27" t="n"/>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
+      <c r="H73" s="27" t="n"/>
+      <c r="I73" s="27" t="n"/>
+      <c r="J73" s="27" t="n"/>
+      <c r="K73" s="27" t="n"/>
+      <c r="L73" s="27" t="n"/>
+      <c r="M73" s="27" t="n"/>
+      <c r="N73" s="27" t="n"/>
+      <c r="O73" s="27" t="n"/>
+      <c r="P73" s="27" t="n"/>
+      <c r="Q73" s="27" t="n"/>
+      <c r="R73" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7492,14 +7857,14 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="31" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7658,7 +8023,7 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -7673,12 +8038,12 @@
       </c>
       <c r="Q2" s="19" t="inlineStr">
         <is>
-          <t>14112365216334</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R2" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112365216334</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7746,12 +8111,12 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -7761,12 +8126,12 @@
       </c>
       <c r="Q3" s="23" t="inlineStr">
         <is>
-          <t>370503334064</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R3" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370503334064</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7834,7 +8199,7 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -7849,12 +8214,12 @@
       </c>
       <c r="Q4" s="19" t="inlineStr">
         <is>
-          <t>370503560906</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R4" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370503560906</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7922,12 +8287,12 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="23" t="inlineStr">
@@ -7937,12 +8302,12 @@
       </c>
       <c r="Q5" s="23" t="inlineStr">
         <is>
-          <t>19041932647740</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041932647740</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8375,12 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="19" t="inlineStr">
@@ -8025,12 +8390,12 @@
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>370494726459</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370494726459</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8463,7 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -8113,12 +8478,12 @@
       </c>
       <c r="Q7" s="23" t="inlineStr">
         <is>
-          <t>7D131169474</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131169474</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8551,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -8201,12 +8566,12 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>SRSC0319007800</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8249,17 +8614,17 @@
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t>Customer Cancelled Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L9" s="24" t="inlineStr">
@@ -8274,7 +8639,7 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -8289,12 +8654,12 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>SF3593208175KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8337,17 +8702,17 @@
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -8362,7 +8727,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -8377,12 +8742,12 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>14112364415189</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112364415189</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8815,7 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -8465,12 +8830,12 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>SRSC9436482183</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8903,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -8553,12 +8918,12 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>SF3158678399SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8991,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -8641,12 +9006,12 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>14112363521699</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363521699</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8714,7 +9079,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -8729,12 +9094,12 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>14112364314371</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112364314371</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8802,7 +9167,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -8817,12 +9182,12 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>14112363687734</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363687734</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8890,7 +9255,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -8905,12 +9270,12 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>370430051263</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370430051263</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8978,12 +9343,12 @@
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -8993,12 +9358,12 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>14112367080297</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112367080297</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9431,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -9081,12 +9446,12 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>370429882984</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370429882984</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9519,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -9169,12 +9534,12 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>14112365054938</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112365054938</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9607,12 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -9257,12 +9622,12 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>SF3586915332KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9695,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -9345,12 +9710,12 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>14112362848987</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362848987</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9768,7 @@
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -9418,7 +9783,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
@@ -9433,12 +9798,12 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>370429573110</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370429573110</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9481,17 +9846,17 @@
       </c>
       <c r="I23" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>Customer Not Available X Office Or Residence Closed</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
@@ -9506,7 +9871,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -9521,12 +9886,12 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>14112363585911</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363585911</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9944,7 @@
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>Receiver Requested Delivery On Another Date (Cir)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -9594,7 +9959,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -9609,12 +9974,12 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>7D131457369</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131457369</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9682,7 +10047,7 @@
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -9697,12 +10062,12 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>370395354997</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370395354997</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9770,7 +10135,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -9785,12 +10150,12 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>SRSC9946388102</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9858,7 +10223,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -9931,7 +10296,7 @@
       </c>
       <c r="K28" s="20" t="inlineStr">
         <is>
-          <t>Customer Not Contactable</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -9946,7 +10311,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -9961,12 +10326,12 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>SF3576445793KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10399,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -10049,12 +10414,12 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>SRSC3884345902</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10487,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -10137,12 +10502,12 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>370384504495</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370384504495</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10575,7 @@
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -10225,12 +10590,12 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>SRSP2020476035</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10663,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
@@ -10361,17 +10726,17 @@
       </c>
       <c r="I33" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
@@ -10386,7 +10751,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -10401,12 +10766,12 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>1319460341769</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1319460341769</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10449,17 +10814,17 @@
       </c>
       <c r="I34" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J34" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
@@ -10474,7 +10839,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -10489,12 +10854,12 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>1319460341773</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1319460341773</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10927,7 @@
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -10577,12 +10942,12 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>14112362553816</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362553816</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10650,7 +11015,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -10665,12 +11030,12 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10738,7 +11103,7 @@
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
@@ -10753,12 +11118,12 @@
       </c>
       <c r="Q37" s="23" t="inlineStr">
         <is>
-          <t>14112363889759</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363889759</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10807,7 +11172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10820,14 +11185,14 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -10925,24 +11290,24 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>#1148</t>
+          <t>#1152</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>Amirtha Varshini</t>
+          <t>Pooja Akiwate</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - L</t>
+          <t>Daisy Dusk Yellow - XXL</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
@@ -10976,12 +11341,12 @@
       </c>
       <c r="L2" s="20" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Shirol</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>'627007</t>
+          <t>'416122</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
@@ -11013,24 +11378,24 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>#1147</t>
+          <t>#1151</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Vishalini Priya</t>
+          <t>Subha Chandrasekar</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
+          <t>Cocoa Elegance Top - XL</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2780</v>
+        <v>1390</v>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
@@ -11064,12 +11429,12 @@
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>'600117</t>
+          <t>'600083</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
@@ -11101,24 +11466,24 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>#1146</t>
+          <t>#1150</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Astin</t>
+          <t>Kavitha Sharma</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Geometric Glam - L, Purple Panache - L</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>2243</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
@@ -11152,12 +11517,12 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Vizianagaram District</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>'613007</t>
+          <t>'535558</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
@@ -11189,38 +11554,38 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>#1144</t>
+          <t>#1149</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Deepak Raj</t>
+          <t>Princy Raj</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Rose Charm Top - S</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1211</v>
+        <v>1290</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -11240,17 +11605,17 @@
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>'600045</t>
+          <t>'613204</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -11265,50 +11630,50 @@
       </c>
       <c r="Q5" s="23" t="inlineStr">
         <is>
-          <t>SF3158681570SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>#1143</t>
+          <t>#1148</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Nandhini V</t>
+          <t>Amirtha Varshini</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - M</t>
+          <t>Plum Pinstripe - L</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -11328,17 +11693,17 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>'631601</t>
+          <t>'627007</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -11353,50 +11718,50 @@
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>19041933834995</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933834995</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>#1142</t>
+          <t>#1147</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Sunanda P</t>
+          <t>Vishalini Priya</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
+          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -11416,17 +11781,17 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>'560011</t>
+          <t>'600117</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -11441,36 +11806,36 @@
       </c>
       <c r="Q7" s="23" t="inlineStr">
         <is>
-          <t>19041933767110</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933767110</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>#1141</t>
+          <t>#1146</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Priya Kathiravan</t>
+          <t>Astin</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Geometric Glam - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1211</v>
+        <v>2243</v>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
@@ -11504,17 +11869,17 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Sathyamoorthy Nagar</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>'614804</t>
+          <t>'613007</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -11529,50 +11894,50 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>SF3158681535SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>#1139</t>
+          <t>#1144</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Keerthana C</t>
+          <t>Deepak Raj</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Rose Charm Top - S</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1112</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -11597,12 +11962,12 @@
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>'600091</t>
+          <t>'600045</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR PICKUP</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -11617,50 +11982,50 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>7D125041276</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D125041276</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>#1138</t>
+          <t>#1143</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Preeti Niranjan</t>
+          <t>Nandhini V</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - S</t>
+          <t>Wine Blossom Top - M</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
         <v>46207</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -11680,17 +12045,17 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>Karwar Uttar Kannada</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>'581400</t>
+          <t>'631601</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -11705,36 +12070,36 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>143263608413636</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608413636</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>#1137</t>
+          <t>#1142</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Sasi Gouru</t>
+          <t>Sunanda P</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
         <v>46207</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1211</v>
+        <v>2779</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
@@ -11768,17 +12133,17 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>'500090</t>
+          <t>'560011</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -11793,50 +12158,50 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>SF3622719795KR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>#1136</t>
+          <t>#1141</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Bala Murali</t>
+          <t>Priya Kathiravan</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1290</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -11856,17 +12221,17 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram District</t>
+          <t>Sathyamoorthy Nagar</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>'623707</t>
+          <t>'614804</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -11881,33 +12246,33 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>19041933357982</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933357982</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>#1135</t>
+          <t>#1139</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Anusha Bekkanti</t>
+          <t>Keerthana C</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>1112</v>
@@ -11944,17 +12309,17 @@
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Harlur Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>'560102</t>
+          <t>'600091</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -11969,36 +12334,36 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>19041933358111</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933358111</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>#1134</t>
+          <t>#1138</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Kaylash Pinkky</t>
+          <t>Preeti Niranjan</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Wine Blossom Top - S</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
@@ -12032,17 +12397,17 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Karwar Uttar Kannada</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>'500010</t>
+          <t>'581400</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -12057,36 +12422,36 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>19041933375224</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933375224</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>#1133</t>
+          <t>#1137</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Deva E</t>
+          <t>Sasi Gouru</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>3096</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -12120,17 +12485,17 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>'600056</t>
+          <t>'500090</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -12145,50 +12510,50 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>143263612093343</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263612093343</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>#1132</t>
+          <t>#1136</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Sudha Manikandan</t>
+          <t>Bala Murali</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
         <v>46206</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -12208,17 +12573,17 @@
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Paramakudi , Ramanathapuram District</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>'625016</t>
+          <t>'623707</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -12233,50 +12598,50 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>370577344761</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370577344761</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>#1131</t>
+          <t>#1135</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Sindhuri Kalidindi</t>
+          <t>Anusha Bekkanti</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
         <v>46206</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -12296,17 +12661,17 @@
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Harlur Bengaluru</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>'146024</t>
+          <t>'560102</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -12321,50 +12686,50 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>14112362996290</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362996290</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>#1130</t>
+          <t>#1134</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Sudha G</t>
+          <t>Kaylash Pinkky</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>3336</v>
+        <v>1131</v>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
@@ -12384,17 +12749,17 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>'639001</t>
+          <t>'500010</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -12409,36 +12774,36 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>143263608436527</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608436527</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>#1129</t>
+          <t>#1133</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Mamillapalli Sivakumari</t>
+          <t>Deva E</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>1112</v>
+        <v>3096</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -12472,17 +12837,17 @@
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>Thiruvallur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>'601204</t>
+          <t>'600056</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -12497,36 +12862,36 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>370574614355</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370574614355</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>#1128</t>
+          <t>#1132</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Shanmuga Priya Priya</t>
+          <t>Sudha Manikandan</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - M</t>
+          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>1032</v>
+        <v>2144</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
@@ -12560,22 +12925,22 @@
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>'632009</t>
+          <t>'625016</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -12585,36 +12950,36 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>SF3158680701SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>#1127</t>
+          <t>#1131</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Rajani Reddy</t>
+          <t>Sindhuri Kalidindi</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - M</t>
+          <t>Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
@@ -12648,17 +13013,17 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>'560076</t>
+          <t>'146024</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -12673,36 +13038,36 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>370554649599</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370554649599</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>#1126</t>
+          <t>#1130</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Sulochana N</t>
+          <t>Sudha G</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Rosy Mist - M</t>
+          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>1890</v>
+        <v>3336</v>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
@@ -12736,22 +13101,22 @@
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>'515002</t>
+          <t>'639001</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P22" s="19" t="inlineStr">
@@ -12761,36 +13126,36 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>370552365989</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370552365989</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>#1125</t>
+          <t>#1129</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Subha A.R</t>
+          <t>Mamillapalli Sivakumari</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - S</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>2680</v>
+        <v>1112</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -12819,22 +13184,22 @@
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>Chennai 600107</t>
+          <t>Thiruvallur</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>'600107</t>
+          <t>'601204</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNFULFILLED</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -12849,36 +13214,36 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>1091393193440</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393193440</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>#1124</t>
+          <t>#1128</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Anusha Madhukar</t>
+          <t>Shanmuga Priya Priya</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
@@ -12912,17 +13277,17 @@
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>'500035</t>
+          <t>'632009</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -12937,50 +13302,50 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>SF3158680814SPF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>#1123</t>
+          <t>#1127</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Ujwala Gajula</t>
+          <t>Rajani Reddy</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
+          <t>Sunset Petal - M</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>2064</v>
+        <v>1112</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -13000,17 +13365,17 @@
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>'500019</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -13025,50 +13390,50 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>7D131505337</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131505337</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>#1122</t>
+          <t>#1126</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Suganya Suganyasridhar</t>
+          <t>Sulochana N</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - XL, Purple Panache - XL</t>
+          <t>Rosy Mist - M</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>2064</v>
+        <v>1890</v>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -13088,22 +13453,22 @@
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Anantapur</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>'606902</t>
+          <t>'515002</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P26" s="19" t="inlineStr">
@@ -13113,36 +13478,36 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>370553698802</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370553698802</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>#1121</t>
+          <t>#1125</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Salla Mahesh</t>
+          <t>Subha A.R</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
+          <t>Sunset Petal - L, Teal Tempo - S</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2144</v>
+        <v>2680</v>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
@@ -13176,17 +13541,17 @@
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>Godavarikhani</t>
+          <t>Chennai 600107</t>
         </is>
       </c>
       <c r="M27" s="26" t="inlineStr">
         <is>
-          <t>'505210</t>
+          <t>'600107</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -13201,55 +13566,55 @@
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
-          <t>370550963576</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370550963576</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>#1120</t>
+          <t>#1124</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Nisha J</t>
+          <t>Anusha Madhukar</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
@@ -13264,17 +13629,17 @@
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
-          <t>Chengalpattu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>'603002</t>
+          <t>'500035</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>CANCELED</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -13289,50 +13654,50 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>14112362403829</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362403829</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>#1119</t>
+          <t>#1123</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Vijayasri S Narendran</t>
+          <t>Ujwala Gajula</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Blossom Taupe Chic Set - 2XL</t>
+          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>1890</v>
+        <v>2064</v>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -13347,22 +13712,22 @@
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>Avadi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>'600062</t>
+          <t>'500019</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -13377,50 +13742,50 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>1091393138630</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393138630</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>#1118</t>
+          <t>#1122</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Aswathy P</t>
+          <t>Suganya Suganyasridhar</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - M</t>
+          <t>Bold Basil - XL, Purple Panache - XL</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>1032</v>
+        <v>2064</v>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -13440,17 +13805,17 @@
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>'682030</t>
+          <t>'606902</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -13465,50 +13830,50 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>7D131502192</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131502192</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>#1117</t>
+          <t>#1121</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Dr Jovin Jose</t>
+          <t>Salla Mahesh</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - M</t>
+          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -13528,17 +13893,17 @@
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>Kanhangad</t>
+          <t>Godavarikhani</t>
         </is>
       </c>
       <c r="M31" s="26" t="inlineStr">
         <is>
-          <t>'671326</t>
+          <t>'505210</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>FULFILLED</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -13553,136 +13918,488 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>7D131501705</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131501705</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
+          <t>#1120</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Nisha J</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>Chengalpattu</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>'603002</t>
+        </is>
+      </c>
+      <c r="N32" s="19" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P32" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q32" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>#1119</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Vijayasri S Narendran</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>Blossom Taupe Chic Set - 2XL</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="inlineStr">
+        <is>
+          <t>Avadi</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>'600062</t>
+        </is>
+      </c>
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q33" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>#1118</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Aswathy P</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Urban Ruby - M</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>Ernakulam</t>
+        </is>
+      </c>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>'682030</t>
+        </is>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O34" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q34" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>#1117</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Dr Jovin Jose</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - M</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="24" t="inlineStr">
+        <is>
+          <t>Kanhangad</t>
+        </is>
+      </c>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>'671326</t>
+        </is>
+      </c>
+      <c r="N35" s="23" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q35" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
           <t>#1115</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Vidya Jothi</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D36" s="15" t="n">
         <v>46204</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E36" s="17" t="n">
         <v>1390</v>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" s="19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" s="20" t="inlineStr">
-        <is>
-          <t>Deliveryattempted Unabletocontactrecipient</t>
-        </is>
-      </c>
-      <c r="L32" s="20" t="inlineStr">
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="M32" s="22" t="inlineStr">
+      <c r="M36" s="22" t="inlineStr">
         <is>
           <t>'641062</t>
         </is>
       </c>
-      <c r="N32" s="19" t="inlineStr">
-        <is>
-          <t>UNDELIVERED</t>
-        </is>
-      </c>
-      <c r="O32" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P32" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q32" s="19" t="inlineStr">
-        <is>
-          <t>370526573181</t>
-        </is>
-      </c>
-      <c r="R32" s="19" t="inlineStr">
-        <is>
-          <t>https://shiprocket.co/tracking/370526573181</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q36" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B33" s="28">
-        <f>COUNTA(A2:A32)</f>
+      <c r="B37" s="28">
+        <f>COUNTA(A2:A36)</f>
         <v/>
       </c>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E33" s="30">
-        <f>SUM(E2:E32)</f>
+      <c r="E37" s="30">
+        <f>SUM(E2:E36)</f>
         <v/>
       </c>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="27" t="n"/>
-      <c r="R33" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="27" t="n"/>
+      <c r="K37" s="27" t="n"/>
+      <c r="L37" s="27" t="n"/>
+      <c r="M37" s="27" t="n"/>
+      <c r="N37" s="27" t="n"/>
+      <c r="O37" s="27" t="n"/>
+      <c r="P37" s="27" t="n"/>
+      <c r="Q37" s="27" t="n"/>
+      <c r="R37" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -715,16 +715,16 @@
         <v>107964</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1032</v>
+        <v>9726</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>106932</v>
+        <v>98238</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.08450704225352113</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0</v>
+        <v>0.1136363636363636</v>
       </c>
     </row>
     <row r="6">
@@ -1449,14 +1449,14 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158681570SPF</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933834995</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933834995</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933767110</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933767110</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158681535SPF</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D125041276</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D125041276</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143263608413636</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/143263608413636</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3622719795KR</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933357982</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933357982</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933358111</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933358111</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933375224</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933375224</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143263612093343</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/143263612093343</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370577344761</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370577344761</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362996290</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362996290</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143263608436527</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/143263608436527</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370574614355</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370574614355</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P24" s="19" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158680701SPF</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370554649599</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370554649599</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370552365989</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370552365989</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L27" s="24" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1091393193440</t>
         </is>
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1091393193440</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158680814SPF</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131505337</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131505337</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370553698802</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370553698802</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370550963576</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370550963576</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362403829</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1091393138630</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131502192</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131501705</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Deliveryattempted Unabletocontactrecipient</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370526573181</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370526573181</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="Q37" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112365216334</t>
         </is>
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P38" s="19" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370503334064</t>
         </is>
       </c>
       <c r="R38" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370503334064</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="N39" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O39" s="23" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="Q39" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370503560906</t>
         </is>
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370503560906</t>
         </is>
       </c>
     </row>
@@ -4959,12 +4959,12 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P40" s="19" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="Q40" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041932647740</t>
         </is>
       </c>
       <c r="R40" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="N41" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P41" s="23" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="Q41" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370494726459</t>
         </is>
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370494726459</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O42" s="19" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="Q42" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131169474</t>
         </is>
       </c>
       <c r="R42" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O43" s="23" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="Q43" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC0319007800</t>
         </is>
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
         </is>
       </c>
     </row>
@@ -5286,17 +5286,17 @@
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K44" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Cancelled Otp Verified</t>
         </is>
       </c>
       <c r="L44" s="20" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="Q44" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3593208175KR</t>
         </is>
       </c>
       <c r="R44" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
         </is>
       </c>
     </row>
@@ -5374,17 +5374,17 @@
       </c>
       <c r="I45" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L45" s="24" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="N45" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O45" s="23" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="Q45" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112364415189</t>
         </is>
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O46" s="19" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="Q46" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC9436482183</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="N47" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O47" s="23" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="Q47" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158678399SPF</t>
         </is>
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O48" s="19" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="Q48" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363521699</t>
         </is>
       </c>
       <c r="R48" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O49" s="23" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="Q49" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112364314371</t>
         </is>
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O50" s="19" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="Q50" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363687734</t>
         </is>
       </c>
       <c r="R50" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="N51" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O51" s="23" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="Q51" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370430051263</t>
         </is>
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370430051263</t>
         </is>
       </c>
     </row>
@@ -6015,12 +6015,12 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O52" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P52" s="19" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="Q52" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112367080297</t>
         </is>
       </c>
       <c r="R52" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="N53" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O53" s="23" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="Q53" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370429882984</t>
         </is>
       </c>
       <c r="R53" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370429882984</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O54" s="19" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="Q54" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112365054938</t>
         </is>
       </c>
       <c r="R54" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="N55" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O55" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P55" s="23" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="Q55" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3586915332KR</t>
         </is>
       </c>
       <c r="R55" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O56" s="19" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="Q56" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362848987</t>
         </is>
       </c>
       <c r="R56" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customerunavailable Deliveryattempted</t>
         </is>
       </c>
       <c r="L57" s="24" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="N57" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-3RD ATTEMPT</t>
         </is>
       </c>
       <c r="O57" s="23" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="Q57" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370429573110</t>
         </is>
       </c>
       <c r="R57" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370429573110</t>
         </is>
       </c>
     </row>
@@ -6518,17 +6518,17 @@
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Available X Office Or Residence Closed</t>
         </is>
       </c>
       <c r="L58" s="20" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="Q58" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363585911</t>
         </is>
       </c>
       <c r="R58" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Receiver Requested Delivery On Another Date (Cir)</t>
         </is>
       </c>
       <c r="L59" s="24" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="N59" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O59" s="23" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="Q59" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131457369</t>
         </is>
       </c>
       <c r="R59" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O60" s="19" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="Q60" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370395354997</t>
         </is>
       </c>
       <c r="R60" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370395354997</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="N61" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O61" s="23" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="Q61" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC9946388102</t>
         </is>
       </c>
       <c r="R61" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O62" s="19" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="K63" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Contactable</t>
         </is>
       </c>
       <c r="L63" s="24" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="N63" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-3RD ATTEMPT</t>
         </is>
       </c>
       <c r="O63" s="23" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="Q63" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3576445793KR</t>
         </is>
       </c>
       <c r="R63" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O64" s="19" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="Q64" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC3884345902</t>
         </is>
       </c>
       <c r="R64" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="N65" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O65" s="23" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="Q65" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370384504495</t>
         </is>
       </c>
       <c r="R65" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370384504495</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O66" s="19" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="Q66" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSP2020476035</t>
         </is>
       </c>
       <c r="R66" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="N67" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O67" s="23" t="inlineStr">
@@ -7398,17 +7398,17 @@
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K68" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L68" s="20" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O68" s="19" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="Q68" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1319460341769</t>
         </is>
       </c>
       <c r="R68" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
         </is>
       </c>
     </row>
@@ -7486,17 +7486,17 @@
       </c>
       <c r="I69" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J69" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K69" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L69" s="24" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="N69" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O69" s="23" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="Q69" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1319460341773</t>
         </is>
       </c>
       <c r="R69" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O70" s="19" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="Q70" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362553816</t>
         </is>
       </c>
       <c r="R70" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="N71" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O71" s="23" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="Q71" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSP8409363746</t>
         </is>
       </c>
       <c r="R71" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O72" s="19" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="Q72" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363889759</t>
         </is>
       </c>
       <c r="R72" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363889759</t>
         </is>
       </c>
     </row>
@@ -7857,14 +7857,14 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
     <col width="31" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="Q2" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112365216334</t>
         </is>
       </c>
       <c r="R2" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
         </is>
       </c>
     </row>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="Q3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370503334064</t>
         </is>
       </c>
       <c r="R3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370503334064</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="Q4" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370503560906</t>
         </is>
       </c>
       <c r="R4" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370503560906</t>
         </is>
       </c>
     </row>
@@ -8287,12 +8287,12 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="23" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="Q5" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041932647740</t>
         </is>
       </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
         </is>
       </c>
     </row>
@@ -8375,12 +8375,12 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370494726459</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370494726459</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="Q7" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131169474</t>
         </is>
       </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC0319007800</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
         </is>
       </c>
     </row>
@@ -8614,17 +8614,17 @@
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Cancelled Otp Verified</t>
         </is>
       </c>
       <c r="L9" s="24" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -8654,12 +8654,12 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3593208175KR</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
         </is>
       </c>
     </row>
@@ -8702,17 +8702,17 @@
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112364415189</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC9436482183</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
         </is>
       </c>
     </row>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158678399SPF</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363521699</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112364314371</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363687734</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370430051263</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370430051263</t>
         </is>
       </c>
     </row>
@@ -9343,12 +9343,12 @@
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112367080297</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370429882984</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370429882984</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112365054938</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3586915332KR</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362848987</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customerunavailable Deliveryattempted</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-3RD ATTEMPT</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370429573110</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370429573110</t>
         </is>
       </c>
     </row>
@@ -9846,17 +9846,17 @@
       </c>
       <c r="I23" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Available X Office Or Residence Closed</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363585911</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Receiver Requested Delivery On Another Date (Cir)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131457369</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370395354997</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370395354997</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -10150,12 +10150,12 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC9946388102</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="K28" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Contactable</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED-3RD ATTEMPT</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3576445793KR</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSC3884345902</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370384504495</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370384504495</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSP2020476035</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="I33" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1319460341769</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
         </is>
       </c>
     </row>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="I34" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J34" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept   Otp Verified</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>RTO OFD</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1319460341773</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362553816</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
         </is>
       </c>
     </row>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SRSP8409363746</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="Q37" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363889759</t>
         </is>
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363889759</t>
         </is>
       </c>
     </row>
@@ -11185,14 +11185,14 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>NEW ORDER</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158681570SPF</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -12070,12 +12070,12 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933834995</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933834995</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933767110</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933767110</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158681535SPF</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -12334,12 +12334,12 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D125041276</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D125041276</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143263608413636</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/143263608413636</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3622719795KR</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -12598,12 +12598,12 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933357982</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933357982</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT-AT DESTINATION HUB</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933358111</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933358111</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041933375224</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041933375224</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -12862,12 +12862,12 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143263612093343</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/143263612093343</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370577344761</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370577344761</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362996290</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362996290</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
@@ -13126,12 +13126,12 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143263608436527</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/143263608436527</t>
         </is>
       </c>
     </row>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>UNFULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370574614355</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370574614355</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P24" s="19" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158680701SPF</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
         </is>
       </c>
     </row>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -13390,12 +13390,12 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370554649599</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370554649599</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370552365989</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370552365989</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L27" s="24" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -13566,12 +13566,12 @@
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1091393193440</t>
         </is>
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1091393193440</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -13654,12 +13654,12 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3158680814SPF</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131505337</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131505337</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370553698802</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370553698802</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370550963576</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370550963576</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112362403829</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pickup Not Attempted</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1091393138630</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -14182,12 +14182,12 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131502192</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>PICKUP EXCEPTION</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -14270,12 +14270,12 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7D131501705</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Deliveryattempted Unabletocontactrecipient</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -14358,12 +14358,12 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>370526573181</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/370526573181</t>
         </is>
       </c>
     </row>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -4592,7 +4592,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Deliveryattempted Unabletocontactrecipient</t>
+          <t>Delivery Attempted Unable To Contact Recipient</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K44" s="20" t="inlineStr">
         <is>
-          <t>Customer Cancelled Otp Verified</t>
+          <t>Customer Cancelled O T P Verified</t>
         </is>
       </c>
       <c r="L44" s="20" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L45" s="24" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>Customer Unavailable Delivery Attempted</t>
         </is>
       </c>
       <c r="L57" s="24" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="K68" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L68" s="20" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="K69" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L69" s="24" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t>Customer Cancelled Otp Verified</t>
+          <t>Customer Cancelled O T P Verified</t>
         </is>
       </c>
       <c r="L9" s="24" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>Customerunavailable Deliveryattempted</t>
+          <t>Customer Unavailable Delivery Attempted</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept   Otp Verified</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
@@ -11185,7 +11185,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="33" customWidth="1" min="14" max="14"/>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Deliveryattempted Unabletocontactrecipient</t>
+          <t>Delivery Attempted Unable To Contact Recipient</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -3820,7 +3820,7 @@
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -709,22 +709,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>107964</v>
+        <v>114853</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9726</v>
+        <v>12048</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>98238</v>
+        <v>102805</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.1956521739130435</v>
       </c>
     </row>
     <row r="6">
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1211</v>
+        <v>7068</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>46174</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>52054</v>
+        <v>53086</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -809,10 +809,10 @@
         <v>46204</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>55910</v>
+        <v>61767</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>9012</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1436,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1449,10 +1449,10 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1554,17 +1554,17 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>#1152</t>
+          <t>#1156</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>Pooja Akiwate</t>
+          <t>Nandhini Manikandan</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XXL</t>
+          <t>Lime Regalia Top - XXL</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="L2" s="20" t="inlineStr">
         <is>
-          <t>Shirol</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>'416122</t>
+          <t>'641006</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -1630,36 +1630,36 @@
       </c>
       <c r="Q2" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1319460365571</t>
         </is>
       </c>
       <c r="R2" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1319460365571</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>#1151</t>
+          <t>#1155</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Subha Chandrasekar</t>
+          <t>Surekha Aketi</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Cocoa Elegance Top - XL</t>
+          <t>Sunset Petal - XXL</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>1390</v>
+        <v>1112</v>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
@@ -1693,17 +1693,17 @@
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Padur</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>'600083</t>
+          <t>'603103</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
@@ -1718,50 +1718,50 @@
       </c>
       <c r="Q3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3638044545KR</t>
         </is>
       </c>
       <c r="R3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3638044545KR</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>#1150</t>
+          <t>#1154</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Kavitha Sharma</t>
+          <t>Sagar Reddy</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Ameera Purple Royale Anarkali Dress - M</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>1211</v>
+        <v>2144</v>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Vizianagaram District</t>
+          <t>Banglore</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>'535558</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -1806,36 +1806,36 @@
       </c>
       <c r="Q4" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041934667424</t>
         </is>
       </c>
       <c r="R4" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041934667424</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>#1149</t>
+          <t>#1153</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Princy Raj</t>
+          <t>Chellakumar Duraisamy</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Daisy Dusk Yellow - S</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Ponnamaravathy</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>'613204</t>
+          <t>'622408</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -1894,36 +1894,36 @@
       </c>
       <c r="Q5" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041934667575</t>
         </is>
       </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041934667575</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>#1148</t>
+          <t>#1152</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Amirtha Varshini</t>
+          <t>Pooja Akiwate</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - L</t>
+          <t>Daisy Dusk Yellow - XXL</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -1957,17 +1957,17 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Shirol</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>'627007</t>
+          <t>'416122</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -1994,24 +1994,24 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>#1147</t>
+          <t>#1151</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Vishalini Priya</t>
+          <t>Subha Chandrasekar</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
+          <t>Cocoa Elegance Top - XL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2780</v>
+        <v>1390</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
@@ -2045,17 +2045,17 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>'600117</t>
+          <t>'600083</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -2070,36 +2070,36 @@
       </c>
       <c r="Q7" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041934666444</t>
         </is>
       </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041934666444</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>#1146</t>
+          <t>#1150</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Astin</t>
+          <t>Kavitha Sharma</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Geometric Glam - L, Purple Panache - L</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>2243</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Vizianagaram District</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>'613007</t>
+          <t>'535558</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>PICKED UP</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -2158,50 +2158,50 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3637423403KR</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3637423403KR</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>#1144</t>
+          <t>#1149</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Deepak Raj</t>
+          <t>Princy Raj</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Rose Charm Top - S</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1211</v>
+        <v>1290</v>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -2221,17 +2221,17 @@
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>'600045</t>
+          <t>'613204</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -2246,50 +2246,50 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>SF3158681570SPF</t>
+          <t>370671755029</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
+          <t>https://shiprocket.co/tracking/370671755029</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>#1143</t>
+          <t>#1148</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Nandhini V</t>
+          <t>Amirtha Varshini</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - M</t>
+          <t>Plum Pinstripe - L</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>'631601</t>
+          <t>'627007</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -2334,50 +2334,50 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>19041933834995</t>
+          <t>19041934246912</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933834995</t>
+          <t>https://shiprocket.co/tracking/19041934246912</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>#1142</t>
+          <t>#1147</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Sunanda P</t>
+          <t>Vishalini Priya</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
+          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -2397,17 +2397,17 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>'560011</t>
+          <t>'600117</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -2422,36 +2422,36 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>19041933767110</t>
+          <t>19041934196744</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933767110</t>
+          <t>https://shiprocket.co/tracking/19041934196744</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>#1141</t>
+          <t>#1146</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Priya Kathiravan</t>
+          <t>Astin</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Geometric Glam - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1211</v>
+        <v>2243</v>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
@@ -2485,17 +2485,17 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>Sathyamoorthy Nagar</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>'614804</t>
+          <t>'613007</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -2510,50 +2510,50 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>SF3158681535SPF</t>
+          <t>14112362766068</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
+          <t>https://shiprocket.co/tracking/14112362766068</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>#1139</t>
+          <t>#1144</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Keerthana C</t>
+          <t>Deepak Raj</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Rose Charm Top - S</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1112</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>'600091</t>
+          <t>'600045</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR PICKUP</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -2598,50 +2598,50 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>7D125041276</t>
+          <t>SF3158681570SPF</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D125041276</t>
+          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>#1138</t>
+          <t>#1143</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Preeti Niranjan</t>
+          <t>Nandhini V</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - S</t>
+          <t>Wine Blossom Top - M</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
         <v>46207</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>Karwar Uttar Kannada</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>'581400</t>
+          <t>'631601</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -2686,36 +2686,36 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>143263608413636</t>
+          <t>19041933834995</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608413636</t>
+          <t>https://shiprocket.co/tracking/19041933834995</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>#1137</t>
+          <t>#1142</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Sasi Gouru</t>
+          <t>Sunanda P</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
         <v>46207</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>1211</v>
+        <v>2779</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>'500090</t>
+          <t>'560011</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -2774,50 +2774,50 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>SF3622719795KR</t>
+          <t>19041933767110</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
+          <t>https://shiprocket.co/tracking/19041933767110</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>#1136</t>
+          <t>#1141</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Bala Murali</t>
+          <t>Priya Kathiravan</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1290</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -2837,17 +2837,17 @@
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram District</t>
+          <t>Sathyamoorthy Nagar</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>'623707</t>
+          <t>'614804</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -2862,33 +2862,33 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>19041933357982</t>
+          <t>SF3158681535SPF</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933357982</t>
+          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>#1135</t>
+          <t>#1139</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Anusha Bekkanti</t>
+          <t>Keerthana C</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>1112</v>
@@ -2925,22 +2925,22 @@
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>Harlur Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>'560102</t>
+          <t>'600091</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -2950,36 +2950,36 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>19041933358111</t>
+          <t>7D125041276</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933358111</t>
+          <t>https://shiprocket.co/tracking/7D125041276</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>#1134</t>
+          <t>#1138</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Kaylash Pinkky</t>
+          <t>Preeti Niranjan</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Wine Blossom Top - S</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
@@ -3013,22 +3013,22 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Karwar Uttar Kannada</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>'500010</t>
+          <t>'581400</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="19" t="inlineStr">
@@ -3038,36 +3038,36 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>19041933375224</t>
+          <t>143263608413636</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933375224</t>
+          <t>https://shiprocket.co/tracking/143263608413636</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>#1133</t>
+          <t>#1137</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Deva E</t>
+          <t>Sasi Gouru</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>3096</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -3101,17 +3101,17 @@
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>'600056</t>
+          <t>'500090</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -3126,50 +3126,50 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>143263612093343</t>
+          <t>SF3622719795KR</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263612093343</t>
+          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>#1132</t>
+          <t>#1136</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Sudha Manikandan</t>
+          <t>Bala Murali</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
         <v>46206</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -3189,17 +3189,17 @@
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Paramakudi , Ramanathapuram District</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>'625016</t>
+          <t>'623707</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
@@ -3214,50 +3214,50 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>370577344761</t>
+          <t>19041933357982</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370577344761</t>
+          <t>https://shiprocket.co/tracking/19041933357982</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>#1131</t>
+          <t>#1135</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Sindhuri Kalidindi</t>
+          <t>Anusha Bekkanti</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
         <v>46206</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -3277,22 +3277,22 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Harlur Bengaluru</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>'146024</t>
+          <t>'560102</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P21" s="23" t="inlineStr">
@@ -3302,50 +3302,50 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>14112362996290</t>
+          <t>19041933358111</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362996290</t>
+          <t>https://shiprocket.co/tracking/19041933358111</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>#1130</t>
+          <t>#1134</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Sudha G</t>
+          <t>Kaylash Pinkky</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>3336</v>
+        <v>1131</v>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>'639001</t>
+          <t>'500010</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
@@ -3390,36 +3390,36 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>143263608436527</t>
+          <t>19041933375224</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608436527</t>
+          <t>https://shiprocket.co/tracking/19041933375224</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>#1129</t>
+          <t>#1133</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Mamillapalli Sivakumari</t>
+          <t>Deva E</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>1112</v>
+        <v>3096</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -3453,22 +3453,22 @@
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>Thiruvallur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>'601204</t>
+          <t>'600056</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P23" s="23" t="inlineStr">
@@ -3478,36 +3478,36 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>370574614355</t>
+          <t>143263612093343</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370574614355</t>
+          <t>https://shiprocket.co/tracking/143263612093343</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>#1128</t>
+          <t>#1132</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Shanmuga Priya Priya</t>
+          <t>Sudha Manikandan</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - M</t>
+          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1032</v>
+        <v>2144</v>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
@@ -3536,27 +3536,27 @@
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unable To Contact Recipient Delivery Attempted</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>'632009</t>
+          <t>'625016</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P24" s="19" t="inlineStr">
@@ -3566,36 +3566,36 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>SF3158680701SPF</t>
+          <t>370577344761</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
+          <t>https://shiprocket.co/tracking/370577344761</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>#1127</t>
+          <t>#1131</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Rajani Reddy</t>
+          <t>Sindhuri Kalidindi</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - M</t>
+          <t>Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
@@ -3629,22 +3629,22 @@
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>'560076</t>
+          <t>'146024</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">
@@ -3654,36 +3654,36 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>370554649599</t>
+          <t>14112362996290</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370554649599</t>
+          <t>https://shiprocket.co/tracking/14112362996290</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>#1126</t>
+          <t>#1130</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Sulochana N</t>
+          <t>Sudha G</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Rosy Mist - M</t>
+          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1890</v>
+        <v>3336</v>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>'515002</t>
+          <t>'639001</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
@@ -3742,36 +3742,36 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>370552365989</t>
+          <t>143263608436527</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370552365989</t>
+          <t>https://shiprocket.co/tracking/143263608436527</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>#1125</t>
+          <t>#1129</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Subha A.R</t>
+          <t>Mamillapalli Sivakumari</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - S</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2680</v>
+        <v>1112</v>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
@@ -3800,27 +3800,27 @@
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>Unable To Contact Recipient Delivery Attempted</t>
         </is>
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>Chennai 600107</t>
+          <t>Thiruvallur</t>
         </is>
       </c>
       <c r="M27" s="26" t="inlineStr">
         <is>
-          <t>'600107</t>
+          <t>'601204</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">
@@ -3830,36 +3830,36 @@
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
-          <t>1091393193440</t>
+          <t>370574614355</t>
         </is>
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393193440</t>
+          <t>https://shiprocket.co/tracking/370574614355</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>#1124</t>
+          <t>#1128</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Anusha Madhukar</t>
+          <t>Shanmuga Priya Priya</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
@@ -3893,22 +3893,22 @@
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>'500035</t>
+          <t>'632009</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P28" s="19" t="inlineStr">
@@ -3918,50 +3918,50 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>SF3158680814SPF</t>
+          <t>SF3158680701SPF</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
+          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>#1123</t>
+          <t>#1127</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Ujwala Gajula</t>
+          <t>Rajani Reddy</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
+          <t>Sunset Petal - M</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>2064</v>
+        <v>1112</v>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -3981,22 +3981,22 @@
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>'500019</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P29" s="23" t="inlineStr">
@@ -4006,50 +4006,50 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>7D131505337</t>
+          <t>370554649599</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131505337</t>
+          <t>https://shiprocket.co/tracking/370554649599</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>#1122</t>
+          <t>#1126</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Suganya Suganyasridhar</t>
+          <t>Sulochana N</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - XL, Purple Panache - XL</t>
+          <t>Rosy Mist - M</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>2064</v>
+        <v>1890</v>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -4069,22 +4069,22 @@
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Anantapur</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>'606902</t>
+          <t>'515002</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P30" s="19" t="inlineStr">
@@ -4094,36 +4094,36 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>370553698802</t>
+          <t>370552365989</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370553698802</t>
+          <t>https://shiprocket.co/tracking/370552365989</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>#1121</t>
+          <t>#1125</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Salla Mahesh</t>
+          <t>Subha A.R</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
+          <t>Sunset Petal - L, Teal Tempo - S</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>2144</v>
+        <v>2680</v>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
@@ -4157,22 +4157,22 @@
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>Godavarikhani</t>
+          <t>Chennai 600107</t>
         </is>
       </c>
       <c r="M31" s="26" t="inlineStr">
         <is>
-          <t>'505210</t>
+          <t>'600107</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr">
@@ -4182,55 +4182,55 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>370550963576</t>
+          <t>1091393193440</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370550963576</t>
+          <t>https://shiprocket.co/tracking/1091393193440</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>#1120</t>
+          <t>#1124</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Nisha J</t>
+          <t>Anusha Madhukar</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J32" s="19" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
-          <t>Chengalpattu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>'603002</t>
+          <t>'500035</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>CANCELED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P32" s="19" t="inlineStr">
@@ -4270,50 +4270,50 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>14112362403829</t>
+          <t>SF3158680814SPF</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362403829</t>
+          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>#1119</t>
+          <t>#1123</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Vijayasri S Narendran</t>
+          <t>Ujwala Gajula</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Blossom Taupe Chic Set - 2XL</t>
+          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>1890</v>
+        <v>2064</v>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -4328,22 +4328,22 @@
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
         <is>
-          <t>Avadi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="M33" s="26" t="inlineStr">
         <is>
-          <t>'600062</t>
+          <t>'500019</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -4358,50 +4358,50 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>1091393138630</t>
+          <t>7D131505337</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393138630</t>
+          <t>https://shiprocket.co/tracking/7D131505337</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>#1118</t>
+          <t>#1122</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Aswathy P</t>
+          <t>Suganya Suganyasridhar</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - M</t>
+          <t>Bold Basil - XL, Purple Panache - XL</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>1032</v>
+        <v>2064</v>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -4416,22 +4416,22 @@
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rejected By Recipient With Verification Not Required</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>'682030</t>
+          <t>'606902</t>
         </is>
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -4446,50 +4446,50 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>7D131502192</t>
+          <t>370553698802</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131502192</t>
+          <t>https://shiprocket.co/tracking/370553698802</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>#1117</t>
+          <t>#1121</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>Dr Jovin Jose</t>
+          <t>Salla Mahesh</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - M</t>
+          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="L35" s="24" t="inlineStr">
         <is>
-          <t>Kanhangad</t>
+          <t>Godavarikhani</t>
         </is>
       </c>
       <c r="M35" s="26" t="inlineStr">
         <is>
-          <t>'671326</t>
+          <t>'505210</t>
         </is>
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -4534,55 +4534,55 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>7D131501705</t>
+          <t>370550963576</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131501705</t>
+          <t>https://shiprocket.co/tracking/370550963576</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>#1115</t>
+          <t>#1120</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Vidya Jothi</t>
+          <t>Nisha J</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Dainty Dots Teal - 2XL</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>1390</v>
+        <v>1032</v>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I36" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J36" s="19" t="inlineStr">
@@ -4592,22 +4592,22 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>Delivery Attempted Unable To Contact Recipient</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chengalpattu</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
         <is>
-          <t>'641062</t>
+          <t>'603002</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -4622,50 +4622,50 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>370526573181</t>
+          <t>14112362403829</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370526573181</t>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>#1114</t>
+          <t>#1119</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Kruthika Vignesh</t>
+          <t>Vijayasri S Narendran</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Blossom Taupe Chic Set - 2XL</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>1112</v>
+        <v>1890</v>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -4685,22 +4685,22 @@
       </c>
       <c r="L37" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Avadi</t>
         </is>
       </c>
       <c r="M37" s="26" t="inlineStr">
         <is>
-          <t>'600078</t>
+          <t>'600062</t>
         </is>
       </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P37" s="23" t="inlineStr">
@@ -4710,33 +4710,33 @@
       </c>
       <c r="Q37" s="23" t="inlineStr">
         <is>
-          <t>14112365216334</t>
+          <t>1091393138630</t>
         </is>
       </c>
       <c r="R37" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112365216334</t>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>#1113</t>
+          <t>#1118</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Maha Jayaraman</t>
+          <t>Aswathy P</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - XL</t>
+          <t>Urban Ruby - M</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>1032</v>
@@ -4773,22 +4773,22 @@
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Ernakulam</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
         <is>
-          <t>'605008</t>
+          <t>'682030</t>
         </is>
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P38" s="19" t="inlineStr">
@@ -4798,33 +4798,33 @@
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>
-          <t>370503334064</t>
+          <t>7D131502192</t>
         </is>
       </c>
       <c r="R38" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370503334064</t>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>#1112</t>
+          <t>#1117</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Perikala Vivekananda</t>
+          <t>Dr Jovin Jose</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - S</t>
+          <t>Daisy Dusk Yellow - M</t>
         </is>
       </c>
       <c r="D39" s="11" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>1112</v>
@@ -4861,22 +4861,22 @@
       </c>
       <c r="L39" s="24" t="inlineStr">
         <is>
-          <t>Tenali</t>
+          <t>Kanhangad</t>
         </is>
       </c>
       <c r="M39" s="26" t="inlineStr">
         <is>
-          <t>'522201</t>
+          <t>'671326</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O39" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P39" s="23" t="inlineStr">
@@ -4886,36 +4886,36 @@
       </c>
       <c r="Q39" s="23" t="inlineStr">
         <is>
-          <t>370503560906</t>
+          <t>7D131501705</t>
         </is>
       </c>
       <c r="R39" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370503560906</t>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>#1111</t>
+          <t>#1115</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Jeeva Ramprabu</t>
+          <t>Vidya Jothi</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>2784</v>
+        <v>1390</v>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M40" s="22" t="inlineStr">
         <is>
-          <t>'626707</t>
+          <t>'641062</t>
         </is>
       </c>
       <c r="N40" s="19" t="inlineStr">
@@ -4974,36 +4974,36 @@
       </c>
       <c r="Q40" s="19" t="inlineStr">
         <is>
-          <t>19041932647740</t>
+          <t>370526573181</t>
         </is>
       </c>
       <c r="R40" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041932647740</t>
+          <t>https://shiprocket.co/tracking/370526573181</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>#1110</t>
+          <t>#1114</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Sharanyaa K</t>
+          <t>Kruthika Vignesh</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - M, Sunset Petal - M</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>2144</v>
+        <v>1112</v>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="L41" s="24" t="inlineStr">
         <is>
-          <t>Pondicherry</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M41" s="26" t="inlineStr">
         <is>
-          <t>'605011</t>
+          <t>'600078</t>
         </is>
       </c>
       <c r="N41" s="23" t="inlineStr">
@@ -5062,50 +5062,50 @@
       </c>
       <c r="Q41" s="23" t="inlineStr">
         <is>
-          <t>370494726459</t>
+          <t>14112365216334</t>
         </is>
       </c>
       <c r="R41" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370494726459</t>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>#1109</t>
+          <t>#1113</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Anusha Anusha</t>
+          <t>Maha Jayaraman</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - 3XL</t>
+          <t>Dainty Dots Teal - XL</t>
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>1032</v>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I42" s="19" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>Hyderbad</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="M42" s="22" t="inlineStr">
         <is>
-          <t>'500086</t>
+          <t>'605008</t>
         </is>
       </c>
       <c r="N42" s="19" t="inlineStr">
@@ -5150,50 +5150,50 @@
       </c>
       <c r="Q42" s="19" t="inlineStr">
         <is>
-          <t>7D131169474</t>
+          <t>370503334064</t>
         </is>
       </c>
       <c r="R42" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131169474</t>
+          <t>https://shiprocket.co/tracking/370503334064</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>#1108</t>
+          <t>#1112</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>Bharathi Dinesh</t>
+          <t>Perikala Vivekananda</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - S</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I43" s="23" t="inlineStr">
@@ -5213,22 +5213,22 @@
       </c>
       <c r="L43" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Tenali</t>
         </is>
       </c>
       <c r="M43" s="26" t="inlineStr">
         <is>
-          <t>'600077</t>
+          <t>'522201</t>
         </is>
       </c>
       <c r="N43" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O43" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P43" s="23" t="inlineStr">
@@ -5238,36 +5238,36 @@
       </c>
       <c r="Q43" s="23" t="inlineStr">
         <is>
-          <t>SRSC0319007800</t>
+          <t>370503560906</t>
         </is>
       </c>
       <c r="R43" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+          <t>https://shiprocket.co/tracking/370503560906</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>#1107</t>
+          <t>#1111</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Meghana R</t>
+          <t>Jeeva Ramprabu</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Aranya Grace Anarkali Dress - XL</t>
+          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>2680</v>
+        <v>2784</v>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
@@ -5286,37 +5286,37 @@
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K44" s="20" t="inlineStr">
         <is>
-          <t>Customer Cancelled O T P Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>Kolar</t>
+          <t>Paramakudi , Ramanathapuram</t>
         </is>
       </c>
       <c r="M44" s="22" t="inlineStr">
         <is>
-          <t>'563102</t>
+          <t>'626707</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P44" s="19" t="inlineStr">
@@ -5326,29 +5326,29 @@
       </c>
       <c r="Q44" s="19" t="inlineStr">
         <is>
-          <t>SF3593208175KR</t>
+          <t>19041932647740</t>
         </is>
       </c>
       <c r="R44" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>#1105</t>
+          <t>#1110</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>Akila Senthil</t>
+          <t>Sharanyaa K</t>
         </is>
       </c>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
+          <t>Moss Majesty - M, Sunset Petal - M</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
@@ -5359,52 +5359,52 @@
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I45" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept O T P Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L45" s="24" t="inlineStr">
         <is>
-          <t>Salem</t>
+          <t>Pondicherry</t>
         </is>
       </c>
       <c r="M45" s="26" t="inlineStr">
         <is>
-          <t>'636005</t>
+          <t>'605011</t>
         </is>
       </c>
       <c r="N45" s="23" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O45" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P45" s="23" t="inlineStr">
@@ -5414,36 +5414,36 @@
       </c>
       <c r="Q45" s="23" t="inlineStr">
         <is>
-          <t>14112364415189</t>
+          <t>370494726459</t>
         </is>
       </c>
       <c r="R45" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112364415189</t>
+          <t>https://shiprocket.co/tracking/370494726459</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>#1104</t>
+          <t>#1109</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Gopal Kowsi</t>
+          <t>Anusha Anusha</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Purple Panache - 3XL</t>
         </is>
       </c>
       <c r="D46" s="15" t="n">
         <v>46202</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
@@ -5477,12 +5477,12 @@
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
-          <t>Vanavasi</t>
+          <t>Hyderbad</t>
         </is>
       </c>
       <c r="M46" s="22" t="inlineStr">
         <is>
-          <t>'636457</t>
+          <t>'500086</t>
         </is>
       </c>
       <c r="N46" s="19" t="inlineStr">
@@ -5502,36 +5502,36 @@
       </c>
       <c r="Q46" s="19" t="inlineStr">
         <is>
-          <t>SRSC9436482183</t>
+          <t>7D131169474</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>#1103</t>
+          <t>#1108</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Praveena Manoharan</t>
+          <t>Bharathi Dinesh</t>
         </is>
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - XL</t>
+          <t>Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
@@ -5570,17 +5570,17 @@
       </c>
       <c r="M47" s="26" t="inlineStr">
         <is>
-          <t>'600100</t>
+          <t>'600077</t>
         </is>
       </c>
       <c r="N47" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O47" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P47" s="23" t="inlineStr">
@@ -5590,36 +5590,36 @@
       </c>
       <c r="Q47" s="23" t="inlineStr">
         <is>
-          <t>SF3158678399SPF</t>
+          <t>SRSC0319007800</t>
         </is>
       </c>
       <c r="R47" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>#1102</t>
+          <t>#1107</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Smitha Ag</t>
+          <t>Meghana R</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L</t>
+          <t>Aranya Grace Anarkali Dress - XL</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>1032</v>
+        <v>2680</v>
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
@@ -5638,32 +5638,32 @@
       </c>
       <c r="I48" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K48" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Cancelled O T P Verified</t>
         </is>
       </c>
       <c r="L48" s="20" t="inlineStr">
         <is>
-          <t>Muvattupuzha</t>
+          <t>Kolar</t>
         </is>
       </c>
       <c r="M48" s="22" t="inlineStr">
         <is>
-          <t>'686661</t>
+          <t>'563102</t>
         </is>
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O48" s="19" t="inlineStr">
@@ -5678,85 +5678,85 @@
       </c>
       <c r="Q48" s="19" t="inlineStr">
         <is>
-          <t>14112363521699</t>
+          <t>SF3593208175KR</t>
         </is>
       </c>
       <c r="R48" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363521699</t>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>#1101</t>
+          <t>#1105</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Apsara Reddy</t>
+          <t>Akila Senthil</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
+          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>3176</v>
+        <v>2144</v>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I49" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K49" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Refused To Accept O T P Verified</t>
         </is>
       </c>
       <c r="L49" s="24" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Salem</t>
         </is>
       </c>
       <c r="M49" s="26" t="inlineStr">
         <is>
-          <t>'518003</t>
+          <t>'636005</t>
         </is>
       </c>
       <c r="N49" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>RTO DELIVERED</t>
         </is>
       </c>
       <c r="O49" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P49" s="23" t="inlineStr">
@@ -5766,36 +5766,36 @@
       </c>
       <c r="Q49" s="23" t="inlineStr">
         <is>
-          <t>14112364314371</t>
+          <t>14112364415189</t>
         </is>
       </c>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112364314371</t>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>#1100</t>
+          <t>#1104</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Shailu Reddy</t>
+          <t>Gopal Kowsi</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - 2XL</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D50" s="15" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>1290</v>
+        <v>1112</v>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="L50" s="20" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Vanavasi</t>
         </is>
       </c>
       <c r="M50" s="22" t="inlineStr">
         <is>
-          <t>'506002</t>
+          <t>'636457</t>
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr">
@@ -5854,50 +5854,50 @@
       </c>
       <c r="Q50" s="19" t="inlineStr">
         <is>
-          <t>14112363687734</t>
+          <t>SRSC9436482183</t>
         </is>
       </c>
       <c r="R50" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363687734</t>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>#1099</t>
+          <t>#1103</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Durai Kannan</t>
+          <t>Praveena Manoharan</t>
         </is>
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - L</t>
+          <t>Purple Panache - XL</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>1032</v>
+        <v>1290</v>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I51" s="23" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L51" s="24" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M51" s="26" t="inlineStr">
         <is>
-          <t>'641008</t>
+          <t>'600100</t>
         </is>
       </c>
       <c r="N51" s="23" t="inlineStr">
@@ -5942,29 +5942,29 @@
       </c>
       <c r="Q51" s="23" t="inlineStr">
         <is>
-          <t>370430051263</t>
+          <t>SF3158678399SPF</t>
         </is>
       </c>
       <c r="R51" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370430051263</t>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>#1098</t>
+          <t>#1102</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>B Padmapriya</t>
+          <t>Smitha Ag</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - L</t>
+          <t>Mystic Mist Red - L</t>
         </is>
       </c>
       <c r="D52" s="15" t="n">
@@ -6000,27 +6000,27 @@
       </c>
       <c r="K52" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Long Pincode</t>
         </is>
       </c>
       <c r="L52" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Muvattupuzha</t>
         </is>
       </c>
       <c r="M52" s="22" t="inlineStr">
         <is>
-          <t>'500017</t>
+          <t>'686661</t>
         </is>
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O52" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P52" s="19" t="inlineStr">
@@ -6030,36 +6030,36 @@
       </c>
       <c r="Q52" s="19" t="inlineStr">
         <is>
-          <t>14112367080297</t>
+          <t>14112363521699</t>
         </is>
       </c>
       <c r="R52" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112367080297</t>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>#1097</t>
+          <t>#1101</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Apsara Reddy</t>
         </is>
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>Grape Leaf Glam - M</t>
+          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>1112</v>
+        <v>3176</v>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="L53" s="24" t="inlineStr">
         <is>
-          <t>Guntur</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="M53" s="26" t="inlineStr">
         <is>
-          <t>'522007</t>
+          <t>'518003</t>
         </is>
       </c>
       <c r="N53" s="23" t="inlineStr">
@@ -6118,50 +6118,50 @@
       </c>
       <c r="Q53" s="23" t="inlineStr">
         <is>
-          <t>370429882984</t>
+          <t>14112364314371</t>
         </is>
       </c>
       <c r="R53" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370429882984</t>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>#1096</t>
+          <t>#1100</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Indu Rekha</t>
+          <t>Shailu Reddy</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
+          <t>Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D54" s="15" t="n">
         <v>46200</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>2224</v>
+        <v>1290</v>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="L54" s="20" t="inlineStr">
         <is>
-          <t>Anantapur Urban</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="M54" s="22" t="inlineStr">
         <is>
-          <t>'515001</t>
+          <t>'506002</t>
         </is>
       </c>
       <c r="N54" s="19" t="inlineStr">
@@ -6206,50 +6206,50 @@
       </c>
       <c r="Q54" s="19" t="inlineStr">
         <is>
-          <t>14112365054938</t>
+          <t>14112363687734</t>
         </is>
       </c>
       <c r="R54" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112365054938</t>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>#1095</t>
+          <t>#1099</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>Priya Dharshini Pd</t>
+          <t>Durai Kannan</t>
         </is>
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - 2XL</t>
+          <t>Moss Majesty - L</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I55" s="23" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="L55" s="24" t="inlineStr">
         <is>
-          <t>Villupuram</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M55" s="26" t="inlineStr">
         <is>
-          <t>'604204</t>
+          <t>'641008</t>
         </is>
       </c>
       <c r="N55" s="23" t="inlineStr">
@@ -6294,29 +6294,29 @@
       </c>
       <c r="Q55" s="23" t="inlineStr">
         <is>
-          <t>SF3586915332KR</t>
+          <t>370430051263</t>
         </is>
       </c>
       <c r="R55" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+          <t>https://shiprocket.co/tracking/370430051263</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>#1094</t>
+          <t>#1098</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Usha .R</t>
+          <t>B Padmapriya</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 3XL</t>
+          <t>Bold Basil - L</t>
         </is>
       </c>
       <c r="D56" s="15" t="n">
@@ -6327,17 +6327,17 @@
       </c>
       <c r="F56" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="L56" s="20" t="inlineStr">
         <is>
-          <t>Hosur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M56" s="22" t="inlineStr">
         <is>
-          <t>'635109</t>
+          <t>'500017</t>
         </is>
       </c>
       <c r="N56" s="19" t="inlineStr">
@@ -6382,50 +6382,50 @@
       </c>
       <c r="Q56" s="19" t="inlineStr">
         <is>
-          <t>14112362848987</t>
+          <t>14112367080297</t>
         </is>
       </c>
       <c r="R56" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362848987</t>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>#1093</t>
+          <t>#1097</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Ramya Gowda</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Grape Leaf Glam - M</t>
         </is>
       </c>
       <c r="D57" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I57" s="23" t="inlineStr">
@@ -6440,27 +6440,27 @@
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
-          <t>Customer Unavailable Delivery Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L57" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Guntur</t>
         </is>
       </c>
       <c r="M57" s="26" t="inlineStr">
         <is>
-          <t>'560091</t>
+          <t>'522007</t>
         </is>
       </c>
       <c r="N57" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O57" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P57" s="23" t="inlineStr">
@@ -6470,85 +6470,85 @@
       </c>
       <c r="Q57" s="23" t="inlineStr">
         <is>
-          <t>370429573110</t>
+          <t>370429882984</t>
         </is>
       </c>
       <c r="R57" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370429573110</t>
+          <t>https://shiprocket.co/tracking/370429882984</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>#1092</t>
+          <t>#1096</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Kowsalya</t>
+          <t>Indu Rekha</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - S</t>
+          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
         </is>
       </c>
       <c r="D58" s="15" t="n">
         <v>46200</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>1290</v>
+        <v>2224</v>
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
-          <t>Customer Not Available X Office Or Residence Closed</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L58" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Anantapur Urban</t>
         </is>
       </c>
       <c r="M58" s="22" t="inlineStr">
         <is>
-          <t>'600096</t>
+          <t>'515001</t>
         </is>
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P58" s="19" t="inlineStr">
@@ -6558,29 +6558,29 @@
       </c>
       <c r="Q58" s="19" t="inlineStr">
         <is>
-          <t>14112363585911</t>
+          <t>14112365054938</t>
         </is>
       </c>
       <c r="R58" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112363585911</t>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>#1091</t>
+          <t>#1095</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Vijay Aadarsh Adarsh</t>
+          <t>Priya Dharshini Pd</t>
         </is>
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Wine Blossom Top - 2XL</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
@@ -6616,27 +6616,27 @@
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
-          <t>Receiver Requested Delivery On Another Date (Cir)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L59" s="24" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Villupuram</t>
         </is>
       </c>
       <c r="M59" s="26" t="inlineStr">
         <is>
-          <t>'641107</t>
+          <t>'604204</t>
         </is>
       </c>
       <c r="N59" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-1ST ATTEMPT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O59" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P59" s="23" t="inlineStr">
@@ -6646,50 +6646,50 @@
       </c>
       <c r="Q59" s="23" t="inlineStr">
         <is>
-          <t>7D131457369</t>
+          <t>SF3586915332KR</t>
         </is>
       </c>
       <c r="R59" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131457369</t>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>#1090</t>
+          <t>#1094</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Kamal Thiyagarajan</t>
+          <t>Usha .R</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Vanya Bloom Top - S</t>
+          <t>Dainty Dots Teal - 3XL</t>
         </is>
       </c>
       <c r="D60" s="15" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G60" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H60" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I60" s="19" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="L60" s="20" t="inlineStr">
         <is>
-          <t>Tirupur</t>
+          <t>Hosur</t>
         </is>
       </c>
       <c r="M60" s="22" t="inlineStr">
         <is>
-          <t>'641606</t>
+          <t>'635109</t>
         </is>
       </c>
       <c r="N60" s="19" t="inlineStr">
@@ -6734,36 +6734,36 @@
       </c>
       <c r="Q60" s="19" t="inlineStr">
         <is>
-          <t>370395354997</t>
+          <t>14112362848987</t>
         </is>
       </c>
       <c r="R60" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370395354997</t>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>#1089</t>
+          <t>#1093</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>Divya Divya</t>
+          <t>Ramya Gowda</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - L</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
@@ -6782,120 +6782,120 @@
       </c>
       <c r="I61" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J61" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Unavailable Delivery Attempted</t>
         </is>
       </c>
       <c r="L61" s="24" t="inlineStr">
         <is>
-          <t>Kuppatti</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M61" s="26" t="inlineStr">
         <is>
-          <t>'635118</t>
+          <t>'560091</t>
         </is>
       </c>
       <c r="N61" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O61" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P61" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q61" s="23" t="inlineStr">
         <is>
-          <t>SRSC9946388102</t>
+          <t>370429573110</t>
         </is>
       </c>
       <c r="R61" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+          <t>https://shiprocket.co/tracking/370429573110</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>#1088</t>
+          <t>#1092</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Nutan Manerkar</t>
+          <t>Kowsalya</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - 2XL</t>
+          <t>Moss Majesty - S</t>
         </is>
       </c>
       <c r="D62" s="15" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>1112</v>
+        <v>1290</v>
       </c>
       <c r="F62" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G62" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I62" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J62" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K62" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Available X Office Or Residence Closed</t>
         </is>
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>Margao</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M62" s="22" t="inlineStr">
         <is>
-          <t>'403601</t>
+          <t>'600096</t>
         </is>
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>RTO DELIVERED</t>
         </is>
       </c>
       <c r="O62" s="19" t="inlineStr">
@@ -6910,36 +6910,36 @@
       </c>
       <c r="Q62" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14112363585911</t>
         </is>
       </c>
       <c r="R62" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>#1087</t>
+          <t>#1091</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Devi Rv</t>
+          <t>Vijay Aadarsh Adarsh</t>
         </is>
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>1290</v>
+        <v>1112</v>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
@@ -6968,22 +6968,22 @@
       </c>
       <c r="K63" s="24" t="inlineStr">
         <is>
-          <t>Customer Not Contactable</t>
+          <t>Receiver Requested Delivery On Another Date (Cir)</t>
         </is>
       </c>
       <c r="L63" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M63" s="26" t="inlineStr">
         <is>
-          <t>'600110</t>
+          <t>'641107</t>
         </is>
       </c>
       <c r="N63" s="23" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O63" s="23" t="inlineStr">
@@ -6998,36 +6998,36 @@
       </c>
       <c r="Q63" s="23" t="inlineStr">
         <is>
-          <t>SF3576445793KR</t>
+          <t>7D131457369</t>
         </is>
       </c>
       <c r="R63" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>#1086</t>
+          <t>#1090</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>D Keerthi</t>
+          <t>Kamal Thiyagarajan</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 3XL</t>
+          <t>Vanya Bloom Top - S</t>
         </is>
       </c>
       <c r="D64" s="15" t="n">
         <v>46198</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
@@ -7061,12 +7061,12 @@
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t>Chittoor</t>
+          <t>Tirupur</t>
         </is>
       </c>
       <c r="M64" s="22" t="inlineStr">
         <is>
-          <t>'517234</t>
+          <t>'641606</t>
         </is>
       </c>
       <c r="N64" s="19" t="inlineStr">
@@ -7086,36 +7086,36 @@
       </c>
       <c r="Q64" s="19" t="inlineStr">
         <is>
-          <t>SRSC3884345902</t>
+          <t>370395354997</t>
         </is>
       </c>
       <c r="R64" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+          <t>https://shiprocket.co/tracking/370395354997</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>#1085</t>
+          <t>#1089</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>Mohanakrishnan Devanathan</t>
+          <t>Divya Divya</t>
         </is>
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - M</t>
+          <t>Moss Majesty - L</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
         <v>46198</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>1032</v>
+        <v>1290</v>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="L65" s="24" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Kuppatti</t>
         </is>
       </c>
       <c r="M65" s="26" t="inlineStr">
         <is>
-          <t>'605006</t>
+          <t>'635118</t>
         </is>
       </c>
       <c r="N65" s="23" t="inlineStr">
@@ -7169,34 +7169,34 @@
       </c>
       <c r="P65" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q65" s="23" t="inlineStr">
         <is>
-          <t>370384504495</t>
+          <t>SRSC9946388102</t>
         </is>
       </c>
       <c r="R65" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370384504495</t>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>#1084</t>
+          <t>#1088</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Gowri R</t>
+          <t>Nutan Manerkar</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Wine Blossom Top - 2XL</t>
         </is>
       </c>
       <c r="D66" s="15" t="n">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="L66" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Margao</t>
         </is>
       </c>
       <c r="M66" s="22" t="inlineStr">
         <is>
-          <t>'600096</t>
+          <t>'403601</t>
         </is>
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O66" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P66" s="19" t="inlineStr">
@@ -7262,36 +7262,36 @@
       </c>
       <c r="Q66" s="19" t="inlineStr">
         <is>
-          <t>SRSP2020476035</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R66" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>#1083</t>
+          <t>#1087</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>Sukanya R</t>
+          <t>Devi Rv</t>
         </is>
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>Coral Bloom Top - M, Purple Panache - M</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
@@ -7310,17 +7310,17 @@
       </c>
       <c r="I67" s="23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J67" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K67" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Customer Not Contactable</t>
         </is>
       </c>
       <c r="L67" s="24" t="inlineStr">
@@ -7330,17 +7330,17 @@
       </c>
       <c r="M67" s="26" t="inlineStr">
         <is>
-          <t>'600095</t>
+          <t>'600110</t>
         </is>
       </c>
       <c r="N67" s="23" t="inlineStr">
         <is>
-          <t>SELF FULFILED</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O67" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P67" s="23" t="inlineStr">
@@ -7350,36 +7350,36 @@
       </c>
       <c r="Q67" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3576445793KR</t>
         </is>
       </c>
       <c r="R67" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>#1082</t>
+          <t>#1086</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Harshini Rajendran</t>
+          <t>D Keerthi</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - XL</t>
+          <t>Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D68" s="15" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F68" s="19" t="inlineStr">
         <is>
@@ -7398,37 +7398,37 @@
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K68" s="20" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept O T P Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L68" s="20" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Chittoor</t>
         </is>
       </c>
       <c r="M68" s="22" t="inlineStr">
         <is>
-          <t>'630003</t>
+          <t>'517234</t>
         </is>
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O68" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P68" s="19" t="inlineStr">
@@ -7438,36 +7438,36 @@
       </c>
       <c r="Q68" s="19" t="inlineStr">
         <is>
-          <t>1319460341769</t>
+          <t>SRSC3884345902</t>
         </is>
       </c>
       <c r="R68" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1319460341769</t>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>#1081</t>
+          <t>#1085</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>Harshini Rajendran</t>
+          <t>Mohanakrishnan Devanathan</t>
         </is>
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - S</t>
+          <t>Purple Panache - M</t>
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>1290</v>
+        <v>1032</v>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
@@ -7486,37 +7486,37 @@
       </c>
       <c r="I69" s="23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J69" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K69" s="24" t="inlineStr">
         <is>
-          <t>Customer Refused To Accept O T P Verified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L69" s="24" t="inlineStr">
         <is>
-          <t>Karaikudi</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="M69" s="26" t="inlineStr">
         <is>
-          <t>'630003</t>
+          <t>'605006</t>
         </is>
       </c>
       <c r="N69" s="23" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O69" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P69" s="23" t="inlineStr">
@@ -7526,36 +7526,36 @@
       </c>
       <c r="Q69" s="23" t="inlineStr">
         <is>
-          <t>1319460341773</t>
+          <t>370384504495</t>
         </is>
       </c>
       <c r="R69" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1319460341773</t>
+          <t>https://shiprocket.co/tracking/370384504495</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>#1080</t>
+          <t>#1084</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Chandraelectro Corporation</t>
+          <t>Gowri R</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D70" s="15" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>3176</v>
+        <v>1112</v>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L70" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M70" s="22" t="inlineStr">
         <is>
-          <t>'625001</t>
+          <t>'600096</t>
         </is>
       </c>
       <c r="N70" s="19" t="inlineStr">
@@ -7614,50 +7614,50 @@
       </c>
       <c r="Q70" s="19" t="inlineStr">
         <is>
-          <t>14112362553816</t>
+          <t>SRSP2020476035</t>
         </is>
       </c>
       <c r="R70" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362553816</t>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>#1078</t>
+          <t>#1083</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>Gomathi Dhanapal</t>
+          <t>Sukanya R</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Coral Bloom Top - M, Purple Panache - M</t>
         </is>
       </c>
       <c r="D71" s="11" t="n">
         <v>46197</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I71" s="23" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="M71" s="26" t="inlineStr">
         <is>
-          <t>'600073</t>
+          <t>'600095</t>
         </is>
       </c>
       <c r="N71" s="23" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>SELF FULFILED</t>
         </is>
       </c>
       <c r="O71" s="23" t="inlineStr">
@@ -7702,136 +7702,576 @@
       </c>
       <c r="Q71" s="23" t="inlineStr">
         <is>
-          <t>SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R71" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="19" t="inlineStr">
         <is>
+          <t>#1082</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>Urban Ruby - XL</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I72" s="19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L72" s="20" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M72" s="22" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N72" s="19" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O72" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P72" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q72" s="19" t="inlineStr">
+        <is>
+          <t>1319460341769</t>
+        </is>
+      </c>
+      <c r="R72" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>#1081</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - S</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I73" s="23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J73" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L73" s="24" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M73" s="26" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N73" s="23" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O73" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P73" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q73" s="23" t="inlineStr">
+        <is>
+          <t>1319460341773</t>
+        </is>
+      </c>
+      <c r="R73" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>#1080</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>Chandraelectro Corporation</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H74" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K74" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="20" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="M74" s="22" t="inlineStr">
+        <is>
+          <t>'625001</t>
+        </is>
+      </c>
+      <c r="N74" s="19" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O74" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P74" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q74" s="19" t="inlineStr">
+        <is>
+          <t>14112362553816</t>
+        </is>
+      </c>
+      <c r="R74" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>#1079</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>Mohana Mona</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="inlineStr">
+        <is>
+          <t>Moss Majesty - M</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E75" s="13" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I75" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J75" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="24" t="inlineStr">
+        <is>
+          <t>Dharmapuri</t>
+        </is>
+      </c>
+      <c r="M75" s="26" t="inlineStr">
+        <is>
+          <t>'636705</t>
+        </is>
+      </c>
+      <c r="N75" s="23" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O75" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P75" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q75" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R75" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>#1078</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Gomathi Dhanapal</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G76" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H76" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I76" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K76" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="20" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>'600073</t>
+        </is>
+      </c>
+      <c r="N76" s="19" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O76" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P76" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q76" s="19" t="inlineStr">
+        <is>
+          <t>SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="R76" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
           <t>#1071</t>
         </is>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>Soumya Shetty</t>
         </is>
       </c>
-      <c r="C72" s="21" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
         <is>
           <t>Sapphire Charm Top - M</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
+      <c r="D77" s="11" t="n">
         <v>46195</v>
       </c>
-      <c r="E72" s="17" t="n">
+      <c r="E77" s="13" t="n">
         <v>1112</v>
       </c>
-      <c r="F72" s="19" t="inlineStr">
+      <c r="F77" s="23" t="inlineStr">
         <is>
           <t>Prepaid (Razorpay)</t>
         </is>
       </c>
-      <c r="G72" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I72" s="19" t="inlineStr">
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I77" s="23" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="J72" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K72" s="20" t="inlineStr">
+      <c r="J77" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L72" s="20" t="inlineStr">
+      <c r="L77" s="24" t="inlineStr">
         <is>
           <t>Bijapur</t>
         </is>
       </c>
-      <c r="M72" s="22" t="inlineStr">
+      <c r="M77" s="26" t="inlineStr">
         <is>
           <t>'586101</t>
         </is>
       </c>
-      <c r="N72" s="19" t="inlineStr">
+      <c r="N77" s="23" t="inlineStr">
         <is>
           <t>DELIVERED</t>
         </is>
       </c>
-      <c r="O72" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P72" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q72" s="19" t="inlineStr">
+      <c r="O77" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P77" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q77" s="23" t="inlineStr">
         <is>
           <t>14112363889759</t>
         </is>
       </c>
-      <c r="R72" s="19" t="inlineStr">
+      <c r="R77" s="23" t="inlineStr">
         <is>
           <t>https://shiprocket.co/tracking/14112363889759</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B73" s="28">
-        <f>COUNTA(A2:A72)</f>
+      <c r="B78" s="28">
+        <f>COUNTA(A2:A77)</f>
         <v/>
       </c>
-      <c r="C73" s="27" t="n"/>
-      <c r="D73" s="29" t="inlineStr">
+      <c r="C78" s="27" t="n"/>
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E73" s="30">
-        <f>SUM(E2:E72)</f>
+      <c r="E78" s="30">
+        <f>SUM(E2:E77)</f>
         <v/>
       </c>
-      <c r="F73" s="27" t="n"/>
-      <c r="G73" s="27" t="n"/>
-      <c r="H73" s="27" t="n"/>
-      <c r="I73" s="27" t="n"/>
-      <c r="J73" s="27" t="n"/>
-      <c r="K73" s="27" t="n"/>
-      <c r="L73" s="27" t="n"/>
-      <c r="M73" s="27" t="n"/>
-      <c r="N73" s="27" t="n"/>
-      <c r="O73" s="27" t="n"/>
-      <c r="P73" s="27" t="n"/>
-      <c r="Q73" s="27" t="n"/>
-      <c r="R73" s="27" t="n"/>
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="27" t="n"/>
+      <c r="H78" s="27" t="n"/>
+      <c r="I78" s="27" t="n"/>
+      <c r="J78" s="27" t="n"/>
+      <c r="K78" s="27" t="n"/>
+      <c r="L78" s="27" t="n"/>
+      <c r="M78" s="27" t="n"/>
+      <c r="N78" s="27" t="n"/>
+      <c r="O78" s="27" t="n"/>
+      <c r="P78" s="27" t="n"/>
+      <c r="Q78" s="27" t="n"/>
+      <c r="R78" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7844,7 +8284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8023,12 +8463,12 @@
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P2" s="19" t="inlineStr">
@@ -8727,7 +9167,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>RTO DELIVERED</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -8976,7 +9416,7 @@
       </c>
       <c r="K13" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Long Pincode</t>
         </is>
       </c>
       <c r="L13" s="24" t="inlineStr">
@@ -8991,7 +9431,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -9758,12 +10198,12 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -9783,7 +10223,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
@@ -9871,7 +10311,7 @@
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>RTO IN TRANSIT</t>
+          <t>RTO DELIVERED</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -10286,12 +10726,12 @@
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -10311,7 +10751,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>UNDELIVERED-3RD ATTEMPT</t>
+          <t>RTO IN TRANSIT</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
@@ -10751,7 +11191,7 @@
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>RTO DELIVERED</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -10839,7 +11279,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>RTO OFD</t>
+          <t>RTO DELIVERED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -10954,38 +11394,38 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>#1078</t>
+          <t>#1079</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Gomathi Dhanapal</t>
+          <t>Mohana Mona</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
         <v>46197</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I36" s="19" t="inlineStr">
@@ -10995,7 +11435,7 @@
       </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K36" s="20" t="inlineStr">
@@ -11005,22 +11445,22 @@
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Dharmapuri</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
         <is>
-          <t>'600073</t>
+          <t>'636705</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P36" s="19" t="inlineStr">
@@ -11030,33 +11470,33 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>#1071</t>
+          <t>#1078</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Soumya Shetty</t>
+          <t>Gomathi Dhanapal</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>Sapphire Charm Top - M</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>1112</v>
@@ -11093,73 +11533,161 @@
       </c>
       <c r="L37" s="24" t="inlineStr">
         <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M37" s="26" t="inlineStr">
+        <is>
+          <t>'600073</t>
+        </is>
+      </c>
+      <c r="N37" s="23" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O37" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" s="23" t="inlineStr">
+        <is>
+          <t>SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="R37" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>#1071</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Soumya Shetty</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Sapphire Charm Top - M</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
           <t>Bijapur</t>
         </is>
       </c>
-      <c r="M37" s="26" t="inlineStr">
+      <c r="M38" s="22" t="inlineStr">
         <is>
           <t>'586101</t>
         </is>
       </c>
-      <c r="N37" s="23" t="inlineStr">
+      <c r="N38" s="19" t="inlineStr">
         <is>
           <t>DELIVERED</t>
         </is>
       </c>
-      <c r="O37" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P37" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q37" s="23" t="inlineStr">
+      <c r="O38" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q38" s="19" t="inlineStr">
         <is>
           <t>14112363889759</t>
         </is>
       </c>
-      <c r="R37" s="23" t="inlineStr">
+      <c r="R38" s="19" t="inlineStr">
         <is>
           <t>https://shiprocket.co/tracking/14112363889759</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B38" s="28">
-        <f>COUNTA(A2:A37)</f>
+      <c r="B39" s="28">
+        <f>COUNTA(A2:A38)</f>
         <v/>
       </c>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E38" s="30">
-        <f>SUM(E2:E37)</f>
+      <c r="E39" s="30">
+        <f>SUM(E2:E38)</f>
         <v/>
       </c>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="27" t="n"/>
-      <c r="J38" s="27" t="n"/>
-      <c r="K38" s="27" t="n"/>
-      <c r="L38" s="27" t="n"/>
-      <c r="M38" s="27" t="n"/>
-      <c r="N38" s="27" t="n"/>
-      <c r="O38" s="27" t="n"/>
-      <c r="P38" s="27" t="n"/>
-      <c r="Q38" s="27" t="n"/>
-      <c r="R38" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="n"/>
+      <c r="J39" s="27" t="n"/>
+      <c r="K39" s="27" t="n"/>
+      <c r="L39" s="27" t="n"/>
+      <c r="M39" s="27" t="n"/>
+      <c r="N39" s="27" t="n"/>
+      <c r="O39" s="27" t="n"/>
+      <c r="P39" s="27" t="n"/>
+      <c r="Q39" s="27" t="n"/>
+      <c r="R39" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11172,7 +11700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11185,10 +11713,10 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -11290,17 +11818,17 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>#1152</t>
+          <t>#1156</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>Pooja Akiwate</t>
+          <t>Nandhini Manikandan</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XXL</t>
+          <t>Lime Regalia Top - XXL</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
@@ -11341,17 +11869,17 @@
       </c>
       <c r="L2" s="20" t="inlineStr">
         <is>
-          <t>Shirol</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>'416122</t>
+          <t>'641006</t>
         </is>
       </c>
       <c r="N2" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O2" s="19" t="inlineStr">
@@ -11366,36 +11894,36 @@
       </c>
       <c r="Q2" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1319460365571</t>
         </is>
       </c>
       <c r="R2" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/1319460365571</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>#1151</t>
+          <t>#1155</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Subha Chandrasekar</t>
+          <t>Surekha Aketi</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Cocoa Elegance Top - XL</t>
+          <t>Sunset Petal - XXL</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>1390</v>
+        <v>1112</v>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
@@ -11429,17 +11957,17 @@
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Padur</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>'600083</t>
+          <t>'603103</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>PICKUP SCHEDULED</t>
         </is>
       </c>
       <c r="O3" s="23" t="inlineStr">
@@ -11454,50 +11982,50 @@
       </c>
       <c r="Q3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3638044545KR</t>
         </is>
       </c>
       <c r="R3" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3638044545KR</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>#1150</t>
+          <t>#1154</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Kavitha Sharma</t>
+          <t>Sagar Reddy</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - XL</t>
+          <t>Ameera Purple Royale Anarkali Dress - M</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>1211</v>
+        <v>2144</v>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -11517,17 +12045,17 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Vizianagaram District</t>
+          <t>Banglore</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>'535558</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>OUT FOR PICKUP</t>
         </is>
       </c>
       <c r="O4" s="19" t="inlineStr">
@@ -11542,36 +12070,36 @@
       </c>
       <c r="Q4" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041934667424</t>
         </is>
       </c>
       <c r="R4" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041934667424</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>#1149</t>
+          <t>#1153</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Princy Raj</t>
+          <t>Chellakumar Duraisamy</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Daisy Dusk Yellow - S</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
@@ -11605,17 +12133,17 @@
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Ponnamaravathy</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>'613204</t>
+          <t>'622408</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>FULFILLED</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
@@ -11630,36 +12158,36 @@
       </c>
       <c r="Q5" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041934667575</t>
         </is>
       </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041934667575</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>#1148</t>
+          <t>#1152</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Amirtha Varshini</t>
+          <t>Pooja Akiwate</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - L</t>
+          <t>Daisy Dusk Yellow - XXL</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
@@ -11683,7 +12211,7 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -11693,17 +12221,17 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>Tirunelveli</t>
+          <t>Shirol</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>'627007</t>
+          <t>'416122</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>CANCELED</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
@@ -11730,24 +12258,24 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>#1147</t>
+          <t>#1151</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Vishalini Priya</t>
+          <t>Subha Chandrasekar</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
+          <t>Cocoa Elegance Top - XL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2780</v>
+        <v>1390</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
@@ -11781,17 +12309,17 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>'600117</t>
+          <t>'600083</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>SHIPPED</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -11806,36 +12334,36 @@
       </c>
       <c r="Q7" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19041934666444</t>
         </is>
       </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/19041934666444</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>#1146</t>
+          <t>#1150</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Astin</t>
+          <t>Kavitha Sharma</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Geometric Glam - L, Purple Panache - L</t>
+          <t>Sunset Petal - XL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>2243</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
@@ -11869,17 +12397,17 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>Thanjavur</t>
+          <t>Vizianagaram District</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>'613007</t>
+          <t>'535558</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>NEW ORDER</t>
+          <t>PICKED UP</t>
         </is>
       </c>
       <c r="O8" s="19" t="inlineStr">
@@ -11894,50 +12422,50 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SF3637423403KR</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://shiprocket.co/tracking/SF3637423403KR</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>#1144</t>
+          <t>#1149</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Deepak Raj</t>
+          <t>Princy Raj</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Rose Charm Top - S</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1211</v>
+        <v>1290</v>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -11957,17 +12485,17 @@
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>'600045</t>
+          <t>'613204</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -11982,50 +12510,50 @@
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
-          <t>SF3158681570SPF</t>
+          <t>370671755029</t>
         </is>
       </c>
       <c r="R9" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
+          <t>https://shiprocket.co/tracking/370671755029</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>#1143</t>
+          <t>#1148</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Nandhini V</t>
+          <t>Amirtha Varshini</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - M</t>
+          <t>Plum Pinstripe - L</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -12045,17 +12573,17 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>Kanchipuram</t>
+          <t>Tirunelveli</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>'631601</t>
+          <t>'627007</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
@@ -12070,50 +12598,50 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>19041933834995</t>
+          <t>19041934246912</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933834995</t>
+          <t>https://shiprocket.co/tracking/19041934246912</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>#1142</t>
+          <t>#1147</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Sunanda P</t>
+          <t>Vishalini Priya</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
+          <t>Geometric Glam - 3XL, Daisy Dusk Yellow - 3XL</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -12133,17 +12661,17 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>'560011</t>
+          <t>'600117</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -12158,36 +12686,36 @@
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
-          <t>19041933767110</t>
+          <t>19041934196744</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933767110</t>
+          <t>https://shiprocket.co/tracking/19041934196744</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>#1141</t>
+          <t>#1146</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Priya Kathiravan</t>
+          <t>Astin</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Geometric Glam - L, Purple Panache - L</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1211</v>
+        <v>2243</v>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
@@ -12221,17 +12749,17 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>Sathyamoorthy Nagar</t>
+          <t>Thanjavur</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>'614804</t>
+          <t>'613007</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -12246,50 +12774,50 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>SF3158681535SPF</t>
+          <t>14112362766068</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
+          <t>https://shiprocket.co/tracking/14112362766068</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>#1139</t>
+          <t>#1144</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Keerthana C</t>
+          <t>Deepak Raj</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - XL</t>
+          <t>Rose Charm Top - S</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1112</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -12314,12 +12842,12 @@
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>'600091</t>
+          <t>'600045</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR PICKUP</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -12334,50 +12862,50 @@
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
-          <t>7D125041276</t>
+          <t>SF3158681570SPF</t>
         </is>
       </c>
       <c r="R13" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D125041276</t>
+          <t>https://shiprocket.co/tracking/SF3158681570SPF</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>#1138</t>
+          <t>#1143</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Preeti Niranjan</t>
+          <t>Nandhini V</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - S</t>
+          <t>Wine Blossom Top - M</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
         <v>46207</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -12397,17 +12925,17 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>Karwar Uttar Kannada</t>
+          <t>Kanchipuram</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>'581400</t>
+          <t>'631601</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
@@ -12422,36 +12950,36 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>143263608413636</t>
+          <t>19041933834995</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608413636</t>
+          <t>https://shiprocket.co/tracking/19041933834995</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>#1137</t>
+          <t>#1142</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Sasi Gouru</t>
+          <t>Sunanda P</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Azure Bloom Top - XXL, Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
         <v>46207</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>1211</v>
+        <v>2779</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -12485,17 +13013,17 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>'500090</t>
+          <t>'560011</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
         <is>
-          <t>PICKUP SCHEDULED</t>
+          <t>REACHED DESTINATION HUB</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -12510,50 +13038,50 @@
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
-          <t>SF3622719795KR</t>
+          <t>19041933767110</t>
         </is>
       </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
+          <t>https://shiprocket.co/tracking/19041933767110</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>#1136</t>
+          <t>#1141</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Bala Murali</t>
+          <t>Priya Kathiravan</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1290</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -12573,17 +13101,17 @@
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>Paramakudi , Ramanathapuram District</t>
+          <t>Sathyamoorthy Nagar</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>'623707</t>
+          <t>'614804</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -12598,33 +13126,33 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>19041933357982</t>
+          <t>SF3158681535SPF</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933357982</t>
+          <t>https://shiprocket.co/tracking/SF3158681535SPF</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>#1135</t>
+          <t>#1139</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Anusha Bekkanti</t>
+          <t>Keerthana C</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL</t>
+          <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>1112</v>
@@ -12661,22 +13189,22 @@
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>Harlur Bengaluru</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>'560102</t>
+          <t>'600091</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-AT DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -12686,36 +13214,36 @@
       </c>
       <c r="Q17" s="23" t="inlineStr">
         <is>
-          <t>19041933358111</t>
+          <t>7D125041276</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933358111</t>
+          <t>https://shiprocket.co/tracking/7D125041276</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>#1134</t>
+          <t>#1138</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Kaylash Pinkky</t>
+          <t>Preeti Niranjan</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Purple Panache - L</t>
+          <t>Wine Blossom Top - S</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1131</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
@@ -12749,22 +13277,22 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>Secunderabad</t>
+          <t>Karwar Uttar Kannada</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>'500010</t>
+          <t>'581400</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="19" t="inlineStr">
@@ -12774,36 +13302,36 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>19041933375224</t>
+          <t>143263608413636</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/19041933375224</t>
+          <t>https://shiprocket.co/tracking/143263608413636</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>#1133</t>
+          <t>#1137</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Deva E</t>
+          <t>Sasi Gouru</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>3096</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -12837,17 +13365,17 @@
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>'600056</t>
+          <t>'500090</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -12862,50 +13390,50 @@
       </c>
       <c r="Q19" s="23" t="inlineStr">
         <is>
-          <t>143263612093343</t>
+          <t>SF3622719795KR</t>
         </is>
       </c>
       <c r="R19" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263612093343</t>
+          <t>https://shiprocket.co/tracking/SF3622719795KR</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>#1132</t>
+          <t>#1136</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Sudha Manikandan</t>
+          <t>Bala Murali</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
+          <t>Bold Basil - 2XL</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
         <v>46206</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>2144</v>
+        <v>1290</v>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -12925,17 +13453,17 @@
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>Madurai</t>
+          <t>Paramakudi , Ramanathapuram District</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>'625016</t>
+          <t>'623707</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
@@ -12950,50 +13478,50 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>370577344761</t>
+          <t>19041933357982</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370577344761</t>
+          <t>https://shiprocket.co/tracking/19041933357982</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>#1131</t>
+          <t>#1135</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Sindhuri Kalidindi</t>
+          <t>Anusha Bekkanti</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Plum Pinstripe - 2XL</t>
+          <t>Wine Blossom Top - XL</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
         <v>46206</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -13013,22 +13541,22 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Hoshiarpur</t>
+          <t>Harlur Bengaluru</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>'146024</t>
+          <t>'560102</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>IN TRANSIT-EN-ROUTE</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P21" s="23" t="inlineStr">
@@ -13038,50 +13566,50 @@
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
-          <t>14112362996290</t>
+          <t>19041933358111</t>
         </is>
       </c>
       <c r="R21" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362996290</t>
+          <t>https://shiprocket.co/tracking/19041933358111</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>#1130</t>
+          <t>#1134</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Sudha G</t>
+          <t>Kaylash Pinkky</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
+          <t>Purple Panache - L</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>3336</v>
+        <v>1131</v>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -13101,12 +13629,12 @@
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>Karur</t>
+          <t>Secunderabad</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>'639001</t>
+          <t>'500010</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
@@ -13126,36 +13654,36 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>143263608436527</t>
+          <t>19041933375224</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/143263608436527</t>
+          <t>https://shiprocket.co/tracking/19041933375224</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>#1129</t>
+          <t>#1133</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Mamillapalli Sivakumari</t>
+          <t>Deva E</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - L</t>
+          <t>Plum Pinstripe - 3XL, Purple Panache - 3XL, Bold Basil - 3XL</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>1112</v>
+        <v>3096</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -13189,22 +13717,22 @@
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>Thiruvallur</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>'601204</t>
+          <t>'600056</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P23" s="23" t="inlineStr">
@@ -13214,36 +13742,36 @@
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
-          <t>370574614355</t>
+          <t>143263612093343</t>
         </is>
       </c>
       <c r="R23" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370574614355</t>
+          <t>https://shiprocket.co/tracking/143263612093343</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>#1128</t>
+          <t>#1132</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Shanmuga Priya Priya</t>
+          <t>Sudha Manikandan</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Moss Majesty - M</t>
+          <t>Mystic Mist Red - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1032</v>
+        <v>2144</v>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
@@ -13272,27 +13800,27 @@
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unable To Contact Recipient Delivery Attempted</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
-          <t>Vellore</t>
+          <t>Madurai</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>'632009</t>
+          <t>'625016</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>DELIVERED</t>
+          <t>UNDELIVERED-1ST ATTEMPT</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P24" s="19" t="inlineStr">
@@ -13302,36 +13830,36 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>SF3158680701SPF</t>
+          <t>370577344761</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
+          <t>https://shiprocket.co/tracking/370577344761</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>#1127</t>
+          <t>#1131</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Rajani Reddy</t>
+          <t>Sindhuri Kalidindi</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - M</t>
+          <t>Plum Pinstripe - 2XL</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
@@ -13365,22 +13893,22 @@
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hoshiarpur</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>'560076</t>
+          <t>'146024</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>IN TRANSIT-EN-ROUTE</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">
@@ -13390,36 +13918,36 @@
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
-          <t>370554649599</t>
+          <t>14112362996290</t>
         </is>
       </c>
       <c r="R25" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370554649599</t>
+          <t>https://shiprocket.co/tracking/14112362996290</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>#1126</t>
+          <t>#1130</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Sulochana N</t>
+          <t>Sudha G</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Rosy Mist - M</t>
+          <t>Wine Blossom Top - XL, Dahlia Dusk - XL, Daisy Dusk Yellow - XL</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1890</v>
+        <v>3336</v>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
@@ -13453,12 +13981,12 @@
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Karur</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>'515002</t>
+          <t>'639001</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
@@ -13478,36 +14006,36 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>370552365989</t>
+          <t>143263608436527</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370552365989</t>
+          <t>https://shiprocket.co/tracking/143263608436527</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>#1125</t>
+          <t>#1129</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Subha A.R</t>
+          <t>Mamillapalli Sivakumari</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Sunset Petal - L, Teal Tempo - S</t>
+          <t>Daisy Dusk Yellow - L</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2680</v>
+        <v>1112</v>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
@@ -13536,27 +14064,27 @@
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>Unable To Contact Recipient Delivery Attempted</t>
         </is>
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>Chennai 600107</t>
+          <t>Thiruvallur</t>
         </is>
       </c>
       <c r="M27" s="26" t="inlineStr">
         <is>
-          <t>'600107</t>
+          <t>'601204</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">
@@ -13566,36 +14094,36 @@
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
-          <t>1091393193440</t>
+          <t>370574614355</t>
         </is>
       </c>
       <c r="R27" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393193440</t>
+          <t>https://shiprocket.co/tracking/370574614355</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>#1124</t>
+          <t>#1128</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Anusha Madhukar</t>
+          <t>Shanmuga Priya Priya</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Sunset Petal - S</t>
+          <t>Moss Majesty - M</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1112</v>
+        <v>1032</v>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
@@ -13629,22 +14157,22 @@
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vellore</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>'500035</t>
+          <t>'632009</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P28" s="19" t="inlineStr">
@@ -13654,50 +14182,50 @@
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>SF3158680814SPF</t>
+          <t>SF3158680701SPF</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
+          <t>https://shiprocket.co/tracking/SF3158680701SPF</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>#1123</t>
+          <t>#1127</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Ujwala Gajula</t>
+          <t>Rajani Reddy</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
+          <t>Sunset Petal - M</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>2064</v>
+        <v>1112</v>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -13717,22 +14245,22 @@
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>Nallagandla</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>'500019</t>
+          <t>'560076</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P29" s="23" t="inlineStr">
@@ -13742,50 +14270,50 @@
       </c>
       <c r="Q29" s="23" t="inlineStr">
         <is>
-          <t>7D131505337</t>
+          <t>370554649599</t>
         </is>
       </c>
       <c r="R29" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131505337</t>
+          <t>https://shiprocket.co/tracking/370554649599</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>#1122</t>
+          <t>#1126</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Suganya Suganyasridhar</t>
+          <t>Sulochana N</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Bold Basil - XL, Purple Panache - XL</t>
+          <t>Rosy Mist - M</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>2064</v>
+        <v>1890</v>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -13805,22 +14333,22 @@
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
-          <t>Tiruvannamalai</t>
+          <t>Anantapur</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>'606902</t>
+          <t>'515002</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>IN TRANSIT</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P30" s="19" t="inlineStr">
@@ -13830,36 +14358,36 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>370553698802</t>
+          <t>370552365989</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370553698802</t>
+          <t>https://shiprocket.co/tracking/370552365989</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>#1121</t>
+          <t>#1125</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Salla Mahesh</t>
+          <t>Subha A.R</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
+          <t>Sunset Petal - L, Teal Tempo - S</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>2144</v>
+        <v>2680</v>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
@@ -13893,22 +14421,22 @@
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>Godavarikhani</t>
+          <t>Chennai 600107</t>
         </is>
       </c>
       <c r="M31" s="26" t="inlineStr">
         <is>
-          <t>'505210</t>
+          <t>'600107</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>REACHED DESTINATION HUB</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr">
@@ -13918,55 +14446,55 @@
       </c>
       <c r="Q31" s="23" t="inlineStr">
         <is>
-          <t>370550963576</t>
+          <t>1091393193440</t>
         </is>
       </c>
       <c r="R31" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/370550963576</t>
+          <t>https://shiprocket.co/tracking/1091393193440</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>#1120</t>
+          <t>#1124</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Nisha J</t>
+          <t>Anusha Madhukar</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Dainty Dots Teal - 2XL</t>
+          <t>Sunset Petal - S</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
         <v>46205</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1032</v>
+        <v>1112</v>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J32" s="19" t="inlineStr">
@@ -13981,22 +14509,22 @@
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
-          <t>Chengalpattu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>'603002</t>
+          <t>'500035</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>CANCELED</t>
+          <t>DELIVERED</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P32" s="19" t="inlineStr">
@@ -14006,50 +14534,50 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>14112362403829</t>
+          <t>SF3158680814SPF</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/14112362403829</t>
+          <t>https://shiprocket.co/tracking/SF3158680814SPF</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>#1119</t>
+          <t>#1123</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Vijayasri S Narendran</t>
+          <t>Ujwala Gajula</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Blossom Taupe Chic Set - 2XL</t>
+          <t>Moss Majesty - 2XL, Purple Panache - 2XL</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
         <v>46205</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>1890</v>
+        <v>2064</v>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -14064,22 +14592,22 @@
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>Pickup Not Attempted</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
         <is>
-          <t>Avadi</t>
+          <t>Nallagandla</t>
         </is>
       </c>
       <c r="M33" s="26" t="inlineStr">
         <is>
-          <t>'600062</t>
+          <t>'500019</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>OUT FOR DELIVERY</t>
+          <t>IN TRANSIT</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -14094,50 +14622,50 @@
       </c>
       <c r="Q33" s="23" t="inlineStr">
         <is>
-          <t>1091393138630</t>
+          <t>7D131505337</t>
         </is>
       </c>
       <c r="R33" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/1091393138630</t>
+          <t>https://shiprocket.co/tracking/7D131505337</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>#1118</t>
+          <t>#1122</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Aswathy P</t>
+          <t>Suganya Suganyasridhar</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Urban Ruby - M</t>
+          <t>Bold Basil - XL, Purple Panache - XL</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>1032</v>
+        <v>2064</v>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -14152,22 +14680,22 @@
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rejected By Recipient With Verification Not Required</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
-          <t>Ernakulam</t>
+          <t>Tiruvannamalai</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>'682030</t>
+          <t>'606902</t>
         </is>
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>UNDELIVERED</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr">
@@ -14182,50 +14710,50 @@
       </c>
       <c r="Q34" s="19" t="inlineStr">
         <is>
-          <t>7D131502192</t>
+          <t>370553698802</t>
         </is>
       </c>
       <c r="R34" s="19" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131502192</t>
+          <t>https://shiprocket.co/tracking/370553698802</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>#1117</t>
+          <t>#1121</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>Dr Jovin Jose</t>
+          <t>Salla Mahesh</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>Daisy Dusk Yellow - M</t>
+          <t>Mystic Mist Red - L, Ocean Elegance Top - L</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1112</v>
+        <v>2144</v>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>Prepaid (Razorpay)</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -14245,17 +14773,17 @@
       </c>
       <c r="L35" s="24" t="inlineStr">
         <is>
-          <t>Kanhangad</t>
+          <t>Godavarikhani</t>
         </is>
       </c>
       <c r="M35" s="26" t="inlineStr">
         <is>
-          <t>'671326</t>
+          <t>'505210</t>
         </is>
       </c>
       <c r="N35" s="23" t="inlineStr">
         <is>
-          <t>PICKUP EXCEPTION</t>
+          <t>OUT FOR DELIVERY</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -14270,136 +14798,488 @@
       </c>
       <c r="Q35" s="23" t="inlineStr">
         <is>
-          <t>7D131501705</t>
+          <t>370550963576</t>
         </is>
       </c>
       <c r="R35" s="23" t="inlineStr">
         <is>
-          <t>https://shiprocket.co/tracking/7D131501705</t>
+          <t>https://shiprocket.co/tracking/370550963576</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
+          <t>#1120</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Nisha J</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>Chengalpattu</t>
+        </is>
+      </c>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>'603002</t>
+        </is>
+      </c>
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P36" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q36" s="19" t="inlineStr">
+        <is>
+          <t>14112362403829</t>
+        </is>
+      </c>
+      <c r="R36" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>#1119</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>Vijayasri S Narendran</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>Blossom Taupe Chic Set - 2XL</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="24" t="inlineStr">
+        <is>
+          <t>Avadi</t>
+        </is>
+      </c>
+      <c r="M37" s="26" t="inlineStr">
+        <is>
+          <t>'600062</t>
+        </is>
+      </c>
+      <c r="N37" s="23" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O37" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" s="23" t="inlineStr">
+        <is>
+          <t>1091393138630</t>
+        </is>
+      </c>
+      <c r="R37" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>#1118</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Aswathy P</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Urban Ruby - M</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>Ernakulam</t>
+        </is>
+      </c>
+      <c r="M38" s="22" t="inlineStr">
+        <is>
+          <t>'682030</t>
+        </is>
+      </c>
+      <c r="N38" s="19" t="inlineStr">
+        <is>
+          <t>REACHED DESTINATION HUB</t>
+        </is>
+      </c>
+      <c r="O38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P38" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q38" s="19" t="inlineStr">
+        <is>
+          <t>7D131502192</t>
+        </is>
+      </c>
+      <c r="R38" s="19" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>#1117</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Dr Jovin Jose</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - M</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="24" t="inlineStr">
+        <is>
+          <t>Kanhangad</t>
+        </is>
+      </c>
+      <c r="M39" s="26" t="inlineStr">
+        <is>
+          <t>'671326</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
+          <t>REACHED DESTINATION HUB</t>
+        </is>
+      </c>
+      <c r="O39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q39" s="23" t="inlineStr">
+        <is>
+          <t>7D131501705</t>
+        </is>
+      </c>
+      <c r="R39" s="23" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
           <t>#1115</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Vidya Jothi</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>Daisy Dusk Yellow - XL</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D40" s="15" t="n">
         <v>46204</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E40" s="17" t="n">
         <v>1390</v>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>Delivery Attempted Unable To Contact Recipient</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
         <is>
           <t>Coimbatore</t>
         </is>
       </c>
-      <c r="M36" s="22" t="inlineStr">
+      <c r="M40" s="22" t="inlineStr">
         <is>
           <t>'641062</t>
         </is>
       </c>
-      <c r="N36" s="19" t="inlineStr">
-        <is>
-          <t>UNDELIVERED</t>
-        </is>
-      </c>
-      <c r="O36" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P36" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q36" s="19" t="inlineStr">
+      <c r="N40" s="19" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O40" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P40" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q40" s="19" t="inlineStr">
         <is>
           <t>370526573181</t>
         </is>
       </c>
-      <c r="R36" s="19" t="inlineStr">
+      <c r="R40" s="19" t="inlineStr">
         <is>
           <t>https://shiprocket.co/tracking/370526573181</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B37" s="28">
-        <f>COUNTA(A2:A36)</f>
+      <c r="B41" s="28">
+        <f>COUNTA(A2:A40)</f>
         <v/>
       </c>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E37" s="30">
-        <f>SUM(E2:E36)</f>
+      <c r="E41" s="30">
+        <f>SUM(E2:E40)</f>
         <v/>
       </c>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="27" t="n"/>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-      <c r="P37" s="27" t="n"/>
-      <c r="Q37" s="27" t="n"/>
-      <c r="R37" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="27" t="n"/>
+      <c r="K41" s="27" t="n"/>
+      <c r="L41" s="27" t="n"/>
+      <c r="M41" s="27" t="n"/>
+      <c r="N41" s="27" t="n"/>
+      <c r="O41" s="27" t="n"/>
+      <c r="P41" s="27" t="n"/>
+      <c r="Q41" s="27" t="n"/>
+      <c r="R41" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -7252,7 +7252,7 @@
       </c>
       <c r="O66" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P66" s="19" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="O27" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -2225,7 +2225,7 @@
       </c>
       <c r="O8" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="22" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O17" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="26" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="O24" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P24" s="22" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="O30" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P30" s="22" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="O34" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P34" s="22" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="O39" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P39" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q39" s="26" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="P45" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q45" s="26" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="O8" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="22" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="O17" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="26" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="O24" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P24" s="22" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="O30" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P30" s="22" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="O34" s="22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P34" s="22" t="inlineStr">
@@ -15745,12 +15745,12 @@
       </c>
       <c r="O39" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P39" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q39" s="26" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="P45" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q45" s="26" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -766,7 +766,7 @@
         <v>18422</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>149506</v>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -718,10 +718,10 @@
         <v>188590</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>20662</v>
+        <v>17486</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>6</v>
@@ -769,10 +769,10 @@
         <v>81</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>149506</v>
+        <v>152682</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1228070175438596</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0.3333333333333333</v>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -712,19 +712,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="4" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>178496</v>
+        <v>238038</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>9518</v>
+        <v>23710</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -763,19 +763,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" s="7" t="n">
-        <v>16358</v>
+        <v>18422</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>152620</v>
+        <v>195906</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04</v>
+        <v>0.09859154929577464</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.3461538461538461</v>
       </c>
     </row>
     <row r="9">
@@ -838,10 +838,10 @@
         <v>46174</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>0</v>
+        <v>53086</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -860,10 +860,10 @@
         <v>46204</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>178496</v>
+        <v>184952</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1192,10 +1192,114 @@
         </is>
       </c>
       <c r="C33" s="19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D33" s="20" t="n">
-        <v>18546</v>
+        <v>21468</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>10144</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="20" t="n">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>16476</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>10044</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>1112</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T102"/>
+  <dimension ref="A1:T144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11554,41 +11658,4157 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="30" t="inlineStr">
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>#1120</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="inlineStr">
+        <is>
+          <t>Nisha J</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K102" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="23" t="inlineStr">
+        <is>
+          <t>Chengalpattu</t>
+        </is>
+      </c>
+      <c r="M102" s="25" t="inlineStr">
+        <is>
+          <t>'603002</t>
+        </is>
+      </c>
+      <c r="N102" s="22" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q102" s="22" t="inlineStr">
+        <is>
+          <t>14112362403829</t>
+        </is>
+      </c>
+      <c r="R102" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
+        </is>
+      </c>
+      <c r="S102" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-2XL</t>
+        </is>
+      </c>
+      <c r="T102" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>#1119</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>Vijayasri S Narendran</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>Blossom Taupe Chic Set - 2XL</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E103" s="20" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F103" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G103" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H103" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I103" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J103" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K103" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="27" t="inlineStr">
+        <is>
+          <t>Avadi</t>
+        </is>
+      </c>
+      <c r="M103" s="29" t="inlineStr">
+        <is>
+          <t>'600062</t>
+        </is>
+      </c>
+      <c r="N103" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O103" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P103" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q103" s="26" t="inlineStr">
+        <is>
+          <t>1091393138630</t>
+        </is>
+      </c>
+      <c r="R103" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
+        </is>
+      </c>
+      <c r="S103" s="26" t="inlineStr">
+        <is>
+          <t>C-BT-BE-2XL</t>
+        </is>
+      </c>
+      <c r="T103" s="26" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>#1118</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="inlineStr">
+        <is>
+          <t>Aswathy P</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>Urban Ruby - M</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K104" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="23" t="inlineStr">
+        <is>
+          <t>Ernakulam</t>
+        </is>
+      </c>
+      <c r="M104" s="25" t="inlineStr">
+        <is>
+          <t>'682030</t>
+        </is>
+      </c>
+      <c r="N104" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q104" s="22" t="inlineStr">
+        <is>
+          <t>7D131502192</t>
+        </is>
+      </c>
+      <c r="R104" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
+        </is>
+      </c>
+      <c r="S104" s="22" t="inlineStr">
+        <is>
+          <t>TOP-UR-RD-M</t>
+        </is>
+      </c>
+      <c r="T104" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>#1117</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>Dr Jovin Jose</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - M</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E105" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F105" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G105" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I105" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J105" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K105" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="27" t="inlineStr">
+        <is>
+          <t>Kanhangad</t>
+        </is>
+      </c>
+      <c r="M105" s="29" t="inlineStr">
+        <is>
+          <t>'671326</t>
+        </is>
+      </c>
+      <c r="N105" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O105" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P105" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q105" s="26" t="inlineStr">
+        <is>
+          <t>7D131501705</t>
+        </is>
+      </c>
+      <c r="R105" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
+        </is>
+      </c>
+      <c r="S105" s="26" t="inlineStr">
+        <is>
+          <t>TOP-DD-YL-M</t>
+        </is>
+      </c>
+      <c r="T105" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>#1115</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="inlineStr">
+        <is>
+          <t>Vidya Jothi</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - XL</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J106" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K106" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="23" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M106" s="25" t="inlineStr">
+        <is>
+          <t>'641062</t>
+        </is>
+      </c>
+      <c r="N106" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O106" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P106" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q106" s="22" t="inlineStr">
+        <is>
+          <t>370526573181</t>
+        </is>
+      </c>
+      <c r="R106" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370526573181</t>
+        </is>
+      </c>
+      <c r="S106" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-YL-XL</t>
+        </is>
+      </c>
+      <c r="T106" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="26" t="inlineStr">
+        <is>
+          <t>#1114</t>
+        </is>
+      </c>
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>Kruthika Vignesh</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E107" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F107" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G107" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I107" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J107" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K107" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M107" s="29" t="inlineStr">
+        <is>
+          <t>'600078</t>
+        </is>
+      </c>
+      <c r="N107" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O107" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P107" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q107" s="26" t="inlineStr">
+        <is>
+          <t>14112365216334</t>
+        </is>
+      </c>
+      <c r="R107" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
+        </is>
+      </c>
+      <c r="S107" s="26" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-XL</t>
+        </is>
+      </c>
+      <c r="T107" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>#1113</t>
+        </is>
+      </c>
+      <c r="B108" s="23" t="inlineStr">
+        <is>
+          <t>Maha Jayaraman</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - XL</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F108" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J108" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K108" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="23" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="M108" s="25" t="inlineStr">
+        <is>
+          <t>'605008</t>
+        </is>
+      </c>
+      <c r="N108" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O108" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P108" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q108" s="22" t="inlineStr">
+        <is>
+          <t>370503334064</t>
+        </is>
+      </c>
+      <c r="R108" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503334064</t>
+        </is>
+      </c>
+      <c r="S108" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-XL</t>
+        </is>
+      </c>
+      <c r="T108" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="26" t="inlineStr">
+        <is>
+          <t>#1112</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>Perikala Vivekananda</t>
+        </is>
+      </c>
+      <c r="C109" s="28" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - S</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E109" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F109" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G109" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H109" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I109" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J109" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K109" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="27" t="inlineStr">
+        <is>
+          <t>Tenali</t>
+        </is>
+      </c>
+      <c r="M109" s="29" t="inlineStr">
+        <is>
+          <t>'522201</t>
+        </is>
+      </c>
+      <c r="N109" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O109" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P109" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q109" s="26" t="inlineStr">
+        <is>
+          <t>370503560906</t>
+        </is>
+      </c>
+      <c r="R109" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503560906</t>
+        </is>
+      </c>
+      <c r="S109" s="26" t="inlineStr">
+        <is>
+          <t>TOP-DD-YL-S</t>
+        </is>
+      </c>
+      <c r="T109" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>#1111</t>
+        </is>
+      </c>
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>Jeeva Ramprabu</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>2784</v>
+      </c>
+      <c r="F110" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J110" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K110" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="23" t="inlineStr">
+        <is>
+          <t>Paramakudi , Ramanathapuram</t>
+        </is>
+      </c>
+      <c r="M110" s="25" t="inlineStr">
+        <is>
+          <t>'626707</t>
+        </is>
+      </c>
+      <c r="N110" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O110" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P110" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q110" s="22" t="inlineStr">
+        <is>
+          <t>19041932647740</t>
+        </is>
+      </c>
+      <c r="R110" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
+        </is>
+      </c>
+      <c r="S110" s="22" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-L, C-KA-NB-L</t>
+        </is>
+      </c>
+      <c r="T110" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, CHUDIDHAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
+        <is>
+          <t>#1110</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>Sharanyaa K</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>Moss Majesty - M, Sunset Petal - M</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E111" s="20" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F111" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G111" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H111" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I111" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J111" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K111" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="27" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="M111" s="29" t="inlineStr">
+        <is>
+          <t>'605011</t>
+        </is>
+      </c>
+      <c r="N111" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O111" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P111" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q111" s="26" t="inlineStr">
+        <is>
+          <t>370494726459</t>
+        </is>
+      </c>
+      <c r="R111" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370494726459</t>
+        </is>
+      </c>
+      <c r="S111" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-M, TOP-SP-DO-M</t>
+        </is>
+      </c>
+      <c r="T111" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="22" t="inlineStr">
+        <is>
+          <t>#1109</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>Anusha Anusha</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>Purple Panache - 3XL</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F112" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J112" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K112" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="23" t="inlineStr">
+        <is>
+          <t>Hyderbad</t>
+        </is>
+      </c>
+      <c r="M112" s="25" t="inlineStr">
+        <is>
+          <t>'500086</t>
+        </is>
+      </c>
+      <c r="N112" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O112" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P112" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q112" s="22" t="inlineStr">
+        <is>
+          <t>7D131169474</t>
+        </is>
+      </c>
+      <c r="R112" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
+        </is>
+      </c>
+      <c r="S112" s="22" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-3XL</t>
+        </is>
+      </c>
+      <c r="T112" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
+        <is>
+          <t>#1108</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>Bharathi Dinesh</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>Bold Basil - 3XL</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E113" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F113" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G113" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H113" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I113" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J113" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K113" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M113" s="29" t="inlineStr">
+        <is>
+          <t>'600077</t>
+        </is>
+      </c>
+      <c r="N113" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O113" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P113" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q113" s="26" t="inlineStr">
+        <is>
+          <t>SRSC0319007800</t>
+        </is>
+      </c>
+      <c r="R113" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+        </is>
+      </c>
+      <c r="S113" s="26" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-3XL</t>
+        </is>
+      </c>
+      <c r="T113" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>#1107</t>
+        </is>
+      </c>
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>Meghana R</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>Aranya Grace Anarkali Dress - XL</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>2680</v>
+      </c>
+      <c r="F114" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I114" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J114" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K114" s="23" t="inlineStr">
+        <is>
+          <t>Customer Cancelled O T P Verified</t>
+        </is>
+      </c>
+      <c r="L114" s="23" t="inlineStr">
+        <is>
+          <t>Kolar</t>
+        </is>
+      </c>
+      <c r="M114" s="25" t="inlineStr">
+        <is>
+          <t>'563102</t>
+        </is>
+      </c>
+      <c r="N114" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O114" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P114" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q114" s="22" t="inlineStr">
+        <is>
+          <t>SF3593208175KR</t>
+        </is>
+      </c>
+      <c r="R114" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+        </is>
+      </c>
+      <c r="S114" s="22" t="inlineStr">
+        <is>
+          <t>A-SUM9239-XL</t>
+        </is>
+      </c>
+      <c r="T114" s="22" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
+        <is>
+          <t>#1105</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>Akila Senthil</t>
+        </is>
+      </c>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E115" s="20" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F115" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G115" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H115" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I115" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J115" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K115" s="27" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L115" s="27" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="M115" s="29" t="inlineStr">
+        <is>
+          <t>'636005</t>
+        </is>
+      </c>
+      <c r="N115" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O115" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P115" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q115" s="26" t="inlineStr">
+        <is>
+          <t>14112364415189</t>
+        </is>
+      </c>
+      <c r="R115" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
+        </is>
+      </c>
+      <c r="S115" s="26" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-2XL, TOP-SP-DO-XXL</t>
+        </is>
+      </c>
+      <c r="T115" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>#1104</t>
+        </is>
+      </c>
+      <c r="B116" s="23" t="inlineStr">
+        <is>
+          <t>Gopal Kowsi</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>Sunset Petal - XL</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F116" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G116" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I116" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J116" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K116" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="23" t="inlineStr">
+        <is>
+          <t>Vanavasi</t>
+        </is>
+      </c>
+      <c r="M116" s="25" t="inlineStr">
+        <is>
+          <t>'636457</t>
+        </is>
+      </c>
+      <c r="N116" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O116" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P116" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q116" s="22" t="inlineStr">
+        <is>
+          <t>SRSC9436482183</t>
+        </is>
+      </c>
+      <c r="R116" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+        </is>
+      </c>
+      <c r="S116" s="22" t="inlineStr">
+        <is>
+          <t>TOP-SP-DO-XL</t>
+        </is>
+      </c>
+      <c r="T116" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>#1103</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>Praveena Manoharan</t>
+        </is>
+      </c>
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>Purple Panache - XL</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="n">
+        <v>46201</v>
+      </c>
+      <c r="E117" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F117" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G117" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H117" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I117" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J117" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K117" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M117" s="29" t="inlineStr">
+        <is>
+          <t>'600100</t>
+        </is>
+      </c>
+      <c r="N117" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O117" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P117" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q117" s="26" t="inlineStr">
+        <is>
+          <t>SF3158678399SPF</t>
+        </is>
+      </c>
+      <c r="R117" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+        </is>
+      </c>
+      <c r="S117" s="26" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-XL</t>
+        </is>
+      </c>
+      <c r="T117" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>#1102</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>Smitha Ag</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - L</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I118" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J118" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K118" s="23" t="inlineStr">
+        <is>
+          <t>Customer Not Available X Office Or Residence Closed</t>
+        </is>
+      </c>
+      <c r="L118" s="23" t="inlineStr">
+        <is>
+          <t>Muvattupuzha</t>
+        </is>
+      </c>
+      <c r="M118" s="25" t="inlineStr">
+        <is>
+          <t>'686661</t>
+        </is>
+      </c>
+      <c r="N118" s="22" t="inlineStr">
+        <is>
+          <t>RTO OFD</t>
+        </is>
+      </c>
+      <c r="O118" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P118" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q118" s="22" t="inlineStr">
+        <is>
+          <t>14112363521699</t>
+        </is>
+      </c>
+      <c r="R118" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
+        </is>
+      </c>
+      <c r="S118" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-MR-L</t>
+        </is>
+      </c>
+      <c r="T118" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="26" t="inlineStr">
+        <is>
+          <t>#1101</t>
+        </is>
+      </c>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>Apsara Reddy</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E119" s="20" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F119" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G119" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H119" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I119" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J119" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K119" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="27" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="M119" s="29" t="inlineStr">
+        <is>
+          <t>'518003</t>
+        </is>
+      </c>
+      <c r="N119" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O119" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P119" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q119" s="26" t="inlineStr">
+        <is>
+          <t>14112364314371</t>
+        </is>
+      </c>
+      <c r="R119" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
+        </is>
+      </c>
+      <c r="S119" s="26" t="inlineStr">
+        <is>
+          <t>TOP-SP-DO-L, TOP-TT-BL-L, TOP-PP-PU-L</t>
+        </is>
+      </c>
+      <c r="T119" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>#1100</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>Shailu Reddy</t>
+        </is>
+      </c>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>Purple Panache - 2XL</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I120" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J120" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K120" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="23" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="M120" s="25" t="inlineStr">
+        <is>
+          <t>'506002</t>
+        </is>
+      </c>
+      <c r="N120" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O120" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P120" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q120" s="22" t="inlineStr">
+        <is>
+          <t>14112363687734</t>
+        </is>
+      </c>
+      <c r="R120" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
+        </is>
+      </c>
+      <c r="S120" s="22" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-2XL</t>
+        </is>
+      </c>
+      <c r="T120" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="26" t="inlineStr">
+        <is>
+          <t>#1099</t>
+        </is>
+      </c>
+      <c r="B121" s="27" t="inlineStr">
+        <is>
+          <t>Durai Kannan</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>Moss Majesty - L</t>
+        </is>
+      </c>
+      <c r="D121" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E121" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F121" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G121" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H121" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I121" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J121" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K121" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="27" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M121" s="29" t="inlineStr">
+        <is>
+          <t>'641008</t>
+        </is>
+      </c>
+      <c r="N121" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O121" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P121" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q121" s="26" t="inlineStr">
+        <is>
+          <t>370430051263</t>
+        </is>
+      </c>
+      <c r="R121" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370430051263</t>
+        </is>
+      </c>
+      <c r="S121" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-L</t>
+        </is>
+      </c>
+      <c r="T121" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>#1098</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="inlineStr">
+        <is>
+          <t>B Padmapriya</t>
+        </is>
+      </c>
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>Bold Basil - L</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I122" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J122" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K122" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="23" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="M122" s="25" t="inlineStr">
+        <is>
+          <t>'500017</t>
+        </is>
+      </c>
+      <c r="N122" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O122" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P122" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q122" s="22" t="inlineStr">
+        <is>
+          <t>14112367080297</t>
+        </is>
+      </c>
+      <c r="R122" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
+        </is>
+      </c>
+      <c r="S122" s="22" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-L</t>
+        </is>
+      </c>
+      <c r="T122" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="26" t="inlineStr">
+        <is>
+          <t>#1097</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>Krishna</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>Grape Leaf Glam - M</t>
+        </is>
+      </c>
+      <c r="D123" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E123" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F123" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G123" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H123" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I123" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J123" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K123" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="27" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+      <c r="M123" s="29" t="inlineStr">
+        <is>
+          <t>'522007</t>
+        </is>
+      </c>
+      <c r="N123" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O123" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P123" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q123" s="26" t="inlineStr">
+        <is>
+          <t>370429882984</t>
+        </is>
+      </c>
+      <c r="R123" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429882984</t>
+        </is>
+      </c>
+      <c r="S123" s="26" t="inlineStr">
+        <is>
+          <t>TOP-GL-GR-M</t>
+        </is>
+      </c>
+      <c r="T123" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>#1096</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>Indu Rekha</t>
+        </is>
+      </c>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>2224</v>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I124" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J124" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K124" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="23" t="inlineStr">
+        <is>
+          <t>Anantapur Urban</t>
+        </is>
+      </c>
+      <c r="M124" s="25" t="inlineStr">
+        <is>
+          <t>'515001</t>
+        </is>
+      </c>
+      <c r="N124" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O124" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P124" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q124" s="22" t="inlineStr">
+        <is>
+          <t>14112365054938</t>
+        </is>
+      </c>
+      <c r="R124" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
+        </is>
+      </c>
+      <c r="S124" s="22" t="inlineStr">
+        <is>
+          <t>TOP-HB-YL-3XL, TOP-OE-NB-3XL</t>
+        </is>
+      </c>
+      <c r="T124" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="26" t="inlineStr">
+        <is>
+          <t>#1095</t>
+        </is>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>Priya Dharshini Pd</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - 2XL</t>
+        </is>
+      </c>
+      <c r="D125" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E125" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F125" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G125" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H125" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I125" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J125" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K125" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="27" t="inlineStr">
+        <is>
+          <t>Villupuram</t>
+        </is>
+      </c>
+      <c r="M125" s="29" t="inlineStr">
+        <is>
+          <t>'604204</t>
+        </is>
+      </c>
+      <c r="N125" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O125" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P125" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q125" s="26" t="inlineStr">
+        <is>
+          <t>SF3586915332KR</t>
+        </is>
+      </c>
+      <c r="R125" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+        </is>
+      </c>
+      <c r="S125" s="26" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-2XL</t>
+        </is>
+      </c>
+      <c r="T125" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>#1094</t>
+        </is>
+      </c>
+      <c r="B126" s="23" t="inlineStr">
+        <is>
+          <t>Usha .R</t>
+        </is>
+      </c>
+      <c r="C126" s="24" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 3XL</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I126" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J126" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K126" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="23" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="M126" s="25" t="inlineStr">
+        <is>
+          <t>'635109</t>
+        </is>
+      </c>
+      <c r="N126" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O126" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P126" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q126" s="22" t="inlineStr">
+        <is>
+          <t>14112362848987</t>
+        </is>
+      </c>
+      <c r="R126" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
+        </is>
+      </c>
+      <c r="S126" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-3XL</t>
+        </is>
+      </c>
+      <c r="T126" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="26" t="inlineStr">
+        <is>
+          <t>#1093</t>
+        </is>
+      </c>
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>Ramya Gowda</t>
+        </is>
+      </c>
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>Bold Basil - 2XL</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E127" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F127" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G127" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H127" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I127" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J127" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K127" s="27" t="inlineStr">
+        <is>
+          <t>Customer Unavailable Delivery Attempted</t>
+        </is>
+      </c>
+      <c r="L127" s="27" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="M127" s="29" t="inlineStr">
+        <is>
+          <t>'560091</t>
+        </is>
+      </c>
+      <c r="N127" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O127" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P127" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q127" s="26" t="inlineStr">
+        <is>
+          <t>370429573110</t>
+        </is>
+      </c>
+      <c r="R127" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429573110</t>
+        </is>
+      </c>
+      <c r="S127" s="26" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-2XL</t>
+        </is>
+      </c>
+      <c r="T127" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>#1092</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="inlineStr">
+        <is>
+          <t>Kowsalya</t>
+        </is>
+      </c>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>Moss Majesty - S</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I128" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J128" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K128" s="23" t="inlineStr">
+        <is>
+          <t>Customer Not Available X Office Or Residence Closed</t>
+        </is>
+      </c>
+      <c r="L128" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M128" s="25" t="inlineStr">
+        <is>
+          <t>'600096</t>
+        </is>
+      </c>
+      <c r="N128" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O128" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P128" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q128" s="22" t="inlineStr">
+        <is>
+          <t>14112363585911</t>
+        </is>
+      </c>
+      <c r="R128" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
+        </is>
+      </c>
+      <c r="S128" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-S</t>
+        </is>
+      </c>
+      <c r="T128" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="26" t="inlineStr">
+        <is>
+          <t>#1091</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>Vijay Aadarsh Adarsh</t>
+        </is>
+      </c>
+      <c r="C129" s="28" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D129" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E129" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F129" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G129" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H129" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I129" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J129" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K129" s="27" t="inlineStr">
+        <is>
+          <t>Pna|Receiver Not Available/Reachable Over Phone</t>
+        </is>
+      </c>
+      <c r="L129" s="27" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M129" s="29" t="inlineStr">
+        <is>
+          <t>'641107</t>
+        </is>
+      </c>
+      <c r="N129" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O129" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P129" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q129" s="26" t="inlineStr">
+        <is>
+          <t>7D131457369</t>
+        </is>
+      </c>
+      <c r="R129" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
+        </is>
+      </c>
+      <c r="S129" s="26" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-XL</t>
+        </is>
+      </c>
+      <c r="T129" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>#1090</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="inlineStr">
+        <is>
+          <t>Kamal Thiyagarajan</t>
+        </is>
+      </c>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>Vanya Bloom Top - S</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I130" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J130" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K130" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="23" t="inlineStr">
+        <is>
+          <t>Tirupur</t>
+        </is>
+      </c>
+      <c r="M130" s="25" t="inlineStr">
+        <is>
+          <t>'641606</t>
+        </is>
+      </c>
+      <c r="N130" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O130" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P130" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q130" s="22" t="inlineStr">
+        <is>
+          <t>370395354997</t>
+        </is>
+      </c>
+      <c r="R130" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370395354997</t>
+        </is>
+      </c>
+      <c r="S130" s="22" t="inlineStr">
+        <is>
+          <t>TOP-VB-GR-S</t>
+        </is>
+      </c>
+      <c r="T130" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="26" t="inlineStr">
+        <is>
+          <t>#1089</t>
+        </is>
+      </c>
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>Divya Divya</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>Moss Majesty - L</t>
+        </is>
+      </c>
+      <c r="D131" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E131" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F131" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G131" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H131" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I131" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J131" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K131" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="27" t="inlineStr">
+        <is>
+          <t>Kuppatti</t>
+        </is>
+      </c>
+      <c r="M131" s="29" t="inlineStr">
+        <is>
+          <t>'635118</t>
+        </is>
+      </c>
+      <c r="N131" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O131" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P131" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q131" s="26" t="inlineStr">
+        <is>
+          <t>SRSC9946388102</t>
+        </is>
+      </c>
+      <c r="R131" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+        </is>
+      </c>
+      <c r="S131" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-L</t>
+        </is>
+      </c>
+      <c r="T131" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>#1088</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr">
+        <is>
+          <t>Nutan Manerkar</t>
+        </is>
+      </c>
+      <c r="C132" s="24" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - 2XL</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G132" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I132" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J132" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K132" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="23" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="M132" s="25" t="inlineStr">
+        <is>
+          <t>'403601</t>
+        </is>
+      </c>
+      <c r="N132" s="22" t="inlineStr">
+        <is>
+          <t>SELF FULFILED</t>
+        </is>
+      </c>
+      <c r="O132" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P132" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q132" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R132" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S132" s="22" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-2XL</t>
+        </is>
+      </c>
+      <c r="T132" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="26" t="inlineStr">
+        <is>
+          <t>#1087</t>
+        </is>
+      </c>
+      <c r="B133" s="27" t="inlineStr">
+        <is>
+          <t>Devi Rv</t>
+        </is>
+      </c>
+      <c r="C133" s="28" t="inlineStr">
+        <is>
+          <t>Bold Basil - 2XL</t>
+        </is>
+      </c>
+      <c r="D133" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E133" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F133" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G133" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H133" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I133" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J133" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K133" s="27" t="inlineStr">
+        <is>
+          <t>Customer Not Contactable</t>
+        </is>
+      </c>
+      <c r="L133" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M133" s="29" t="inlineStr">
+        <is>
+          <t>'600110</t>
+        </is>
+      </c>
+      <c r="N133" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O133" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P133" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q133" s="26" t="inlineStr">
+        <is>
+          <t>SF3576445793KR</t>
+        </is>
+      </c>
+      <c r="R133" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+        </is>
+      </c>
+      <c r="S133" s="26" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-2XL</t>
+        </is>
+      </c>
+      <c r="T133" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="22" t="inlineStr">
+        <is>
+          <t>#1086</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="inlineStr">
+        <is>
+          <t>D Keerthi</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>Bold Basil - 3XL</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F134" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I134" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J134" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K134" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" s="23" t="inlineStr">
+        <is>
+          <t>Chittoor</t>
+        </is>
+      </c>
+      <c r="M134" s="25" t="inlineStr">
+        <is>
+          <t>'517234</t>
+        </is>
+      </c>
+      <c r="N134" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O134" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P134" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q134" s="22" t="inlineStr">
+        <is>
+          <t>SRSC3884345902</t>
+        </is>
+      </c>
+      <c r="R134" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+        </is>
+      </c>
+      <c r="S134" s="22" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-3XL</t>
+        </is>
+      </c>
+      <c r="T134" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="26" t="inlineStr">
+        <is>
+          <t>#1085</t>
+        </is>
+      </c>
+      <c r="B135" s="27" t="inlineStr">
+        <is>
+          <t>Mohanakrishnan Devanathan</t>
+        </is>
+      </c>
+      <c r="C135" s="28" t="inlineStr">
+        <is>
+          <t>Purple Panache - M</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E135" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F135" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G135" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H135" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I135" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J135" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K135" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="27" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="M135" s="29" t="inlineStr">
+        <is>
+          <t>'605006</t>
+        </is>
+      </c>
+      <c r="N135" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O135" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P135" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q135" s="26" t="inlineStr">
+        <is>
+          <t>370384504495</t>
+        </is>
+      </c>
+      <c r="R135" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370384504495</t>
+        </is>
+      </c>
+      <c r="S135" s="26" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-M</t>
+        </is>
+      </c>
+      <c r="T135" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>#1084</t>
+        </is>
+      </c>
+      <c r="B136" s="23" t="inlineStr">
+        <is>
+          <t>Gowri R</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
+        <is>
+          <t>Sunset Petal - XL</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F136" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G136" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H136" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I136" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J136" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K136" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M136" s="25" t="inlineStr">
+        <is>
+          <t>'600096</t>
+        </is>
+      </c>
+      <c r="N136" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O136" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P136" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q136" s="22" t="inlineStr">
+        <is>
+          <t>SRSP2020476035</t>
+        </is>
+      </c>
+      <c r="R136" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+        </is>
+      </c>
+      <c r="S136" s="22" t="inlineStr">
+        <is>
+          <t>TOP-SP-DO-XL</t>
+        </is>
+      </c>
+      <c r="T136" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="26" t="inlineStr">
+        <is>
+          <t>#1083</t>
+        </is>
+      </c>
+      <c r="B137" s="27" t="inlineStr">
+        <is>
+          <t>Sukanya R</t>
+        </is>
+      </c>
+      <c r="C137" s="28" t="inlineStr">
+        <is>
+          <t>Coral Bloom Top - M, Purple Panache - M</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E137" s="20" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F137" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G137" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H137" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J137" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K137" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M137" s="29" t="inlineStr">
+        <is>
+          <t>'600095</t>
+        </is>
+      </c>
+      <c r="N137" s="26" t="inlineStr">
+        <is>
+          <t>SELF FULFILED</t>
+        </is>
+      </c>
+      <c r="O137" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P137" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q137" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R137" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S137" s="26" t="inlineStr">
+        <is>
+          <t>TOP-CB-CRD-M, TOP-PP-PU-M</t>
+        </is>
+      </c>
+      <c r="T137" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>#1082</t>
+        </is>
+      </c>
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>Urban Ruby - XL</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F138" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G138" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H138" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I138" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J138" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K138" s="23" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L138" s="23" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M138" s="25" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N138" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O138" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P138" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q138" s="22" t="inlineStr">
+        <is>
+          <t>1319460341769</t>
+        </is>
+      </c>
+      <c r="R138" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
+        </is>
+      </c>
+      <c r="S138" s="22" t="inlineStr">
+        <is>
+          <t>TOP-UR-RD-XL</t>
+        </is>
+      </c>
+      <c r="T138" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="26" t="inlineStr">
+        <is>
+          <t>#1081</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C139" s="28" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - S</t>
+        </is>
+      </c>
+      <c r="D139" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E139" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F139" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G139" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H139" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I139" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J139" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K139" s="27" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L139" s="27" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M139" s="29" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N139" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O139" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P139" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q139" s="26" t="inlineStr">
+        <is>
+          <t>1319460341773</t>
+        </is>
+      </c>
+      <c r="R139" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
+        </is>
+      </c>
+      <c r="S139" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-MR-S</t>
+        </is>
+      </c>
+      <c r="T139" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>#1080</t>
+        </is>
+      </c>
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>Chandraelectro Corporation</t>
+        </is>
+      </c>
+      <c r="C140" s="24" t="inlineStr">
+        <is>
+          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F140" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G140" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H140" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I140" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J140" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K140" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="23" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="M140" s="25" t="inlineStr">
+        <is>
+          <t>'625001</t>
+        </is>
+      </c>
+      <c r="N140" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O140" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P140" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q140" s="22" t="inlineStr">
+        <is>
+          <t>14112362553816</t>
+        </is>
+      </c>
+      <c r="R140" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
+        </is>
+      </c>
+      <c r="S140" s="22" t="inlineStr">
+        <is>
+          <t>TOP-TT-BL-2XL, TOP-MM-MR-2XL, TOP-RU-DB-XXL</t>
+        </is>
+      </c>
+      <c r="T140" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="26" t="inlineStr">
+        <is>
+          <t>#1079</t>
+        </is>
+      </c>
+      <c r="B141" s="27" t="inlineStr">
+        <is>
+          <t>Mohana Mona</t>
+        </is>
+      </c>
+      <c r="C141" s="28" t="inlineStr">
+        <is>
+          <t>Moss Majesty - M</t>
+        </is>
+      </c>
+      <c r="D141" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E141" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F141" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G141" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H141" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I141" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J141" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K141" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="27" t="inlineStr">
+        <is>
+          <t>Dharmapuri</t>
+        </is>
+      </c>
+      <c r="M141" s="29" t="inlineStr">
+        <is>
+          <t>'636705</t>
+        </is>
+      </c>
+      <c r="N141" s="26" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O141" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P141" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q141" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R141" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S141" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-M</t>
+        </is>
+      </c>
+      <c r="T141" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>#1078</t>
+        </is>
+      </c>
+      <c r="B142" s="23" t="inlineStr">
+        <is>
+          <t>Gomathi Dhanapal</t>
+        </is>
+      </c>
+      <c r="C142" s="24" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F142" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G142" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H142" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I142" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J142" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K142" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M142" s="25" t="inlineStr">
+        <is>
+          <t>'600073</t>
+        </is>
+      </c>
+      <c r="N142" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O142" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P142" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q142" s="22" t="inlineStr">
+        <is>
+          <t>SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="R142" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="S142" s="22" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-XL</t>
+        </is>
+      </c>
+      <c r="T142" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="26" t="inlineStr">
+        <is>
+          <t>#1071</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="inlineStr">
+        <is>
+          <t>Soumya Shetty</t>
+        </is>
+      </c>
+      <c r="C143" s="28" t="inlineStr">
+        <is>
+          <t>Sapphire Charm Top - M</t>
+        </is>
+      </c>
+      <c r="D143" s="18" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E143" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F143" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G143" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H143" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I143" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J143" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K143" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="27" t="inlineStr">
+        <is>
+          <t>Bijapur</t>
+        </is>
+      </c>
+      <c r="M143" s="29" t="inlineStr">
+        <is>
+          <t>'586101</t>
+        </is>
+      </c>
+      <c r="N143" s="26" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O143" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P143" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q143" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R143" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S143" s="26" t="inlineStr">
+        <is>
+          <t>TOP-SC-DB-M</t>
+        </is>
+      </c>
+      <c r="T143" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="30" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B102" s="31">
-        <f>COUNTA(A2:A101)</f>
+      <c r="B144" s="31">
+        <f>COUNTA(A2:A143)</f>
         <v/>
       </c>
-      <c r="C102" s="30" t="n"/>
-      <c r="D102" s="32" t="inlineStr">
+      <c r="C144" s="30" t="n"/>
+      <c r="D144" s="32" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E102" s="33">
-        <f>SUM(E2:E101)</f>
+      <c r="E144" s="33">
+        <f>SUM(E2:E143)</f>
         <v/>
       </c>
-      <c r="F102" s="30" t="n"/>
-      <c r="G102" s="30" t="n"/>
-      <c r="H102" s="30" t="n"/>
-      <c r="I102" s="30" t="n"/>
-      <c r="J102" s="30" t="n"/>
-      <c r="K102" s="30" t="n"/>
-      <c r="L102" s="30" t="n"/>
-      <c r="M102" s="30" t="n"/>
-      <c r="N102" s="30" t="n"/>
-      <c r="O102" s="30" t="n"/>
-      <c r="P102" s="30" t="n"/>
-      <c r="Q102" s="30" t="n"/>
-      <c r="R102" s="30" t="n"/>
-      <c r="S102" s="30" t="n"/>
-      <c r="T102" s="30" t="n"/>
+      <c r="F144" s="30" t="n"/>
+      <c r="G144" s="30" t="n"/>
+      <c r="H144" s="30" t="n"/>
+      <c r="I144" s="30" t="n"/>
+      <c r="J144" s="30" t="n"/>
+      <c r="K144" s="30" t="n"/>
+      <c r="L144" s="30" t="n"/>
+      <c r="M144" s="30" t="n"/>
+      <c r="N144" s="30" t="n"/>
+      <c r="O144" s="30" t="n"/>
+      <c r="P144" s="30" t="n"/>
+      <c r="Q144" s="30" t="n"/>
+      <c r="R144" s="30" t="n"/>
+      <c r="S144" s="30" t="n"/>
+      <c r="T144" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11601,29 +15821,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="31" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="47" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -11727,6 +15947,3668 @@
           <t>Category</t>
         </is>
       </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>#1114</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>Kruthika Vignesh</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>'600078</t>
+        </is>
+      </c>
+      <c r="N2" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O2" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P2" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q2" s="22" t="inlineStr">
+        <is>
+          <t>14112365216334</t>
+        </is>
+      </c>
+      <c r="R2" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365216334</t>
+        </is>
+      </c>
+      <c r="S2" s="22" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-XL</t>
+        </is>
+      </c>
+      <c r="T2" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>#1113</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>Maha Jayaraman</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - XL</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="27" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="M3" s="29" t="inlineStr">
+        <is>
+          <t>'605008</t>
+        </is>
+      </c>
+      <c r="N3" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O3" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P3" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q3" s="26" t="inlineStr">
+        <is>
+          <t>370503334064</t>
+        </is>
+      </c>
+      <c r="R3" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503334064</t>
+        </is>
+      </c>
+      <c r="S3" s="26" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-XL</t>
+        </is>
+      </c>
+      <c r="T3" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>#1112</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Perikala Vivekananda</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - S</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t>Tenali</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t>'522201</t>
+        </is>
+      </c>
+      <c r="N4" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O4" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P4" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>370503560906</t>
+        </is>
+      </c>
+      <c r="R4" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370503560906</t>
+        </is>
+      </c>
+      <c r="S4" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-YL-S</t>
+        </is>
+      </c>
+      <c r="T4" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>#1111</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Jeeva Ramprabu</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Purple Panache - L, Karunguyil Chudidhar Set - L</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>2784</v>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="27" t="inlineStr">
+        <is>
+          <t>Paramakudi , Ramanathapuram</t>
+        </is>
+      </c>
+      <c r="M5" s="29" t="inlineStr">
+        <is>
+          <t>'626707</t>
+        </is>
+      </c>
+      <c r="N5" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P5" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" s="26" t="inlineStr">
+        <is>
+          <t>19041932647740</t>
+        </is>
+      </c>
+      <c r="R5" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/19041932647740</t>
+        </is>
+      </c>
+      <c r="S5" s="26" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-L, C-KA-NB-L</t>
+        </is>
+      </c>
+      <c r="T5" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, CHUDIDHAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>#1110</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Sharanyaa K</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Moss Majesty - M, Sunset Petal - M</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>Pondicherry</t>
+        </is>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>'605011</t>
+        </is>
+      </c>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>370494726459</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370494726459</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-M, TOP-SP-DO-M</t>
+        </is>
+      </c>
+      <c r="T6" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>#1109</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Anusha Anusha</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Purple Panache - 3XL</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="27" t="inlineStr">
+        <is>
+          <t>Hyderbad</t>
+        </is>
+      </c>
+      <c r="M7" s="29" t="inlineStr">
+        <is>
+          <t>'500086</t>
+        </is>
+      </c>
+      <c r="N7" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O7" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P7" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" s="26" t="inlineStr">
+        <is>
+          <t>7D131169474</t>
+        </is>
+      </c>
+      <c r="R7" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131169474</t>
+        </is>
+      </c>
+      <c r="S7" s="26" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-3XL</t>
+        </is>
+      </c>
+      <c r="T7" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>#1108</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Bharathi Dinesh</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>Bold Basil - 3XL</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>'600077</t>
+        </is>
+      </c>
+      <c r="N8" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>SRSC0319007800</t>
+        </is>
+      </c>
+      <c r="R8" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC0319007800</t>
+        </is>
+      </c>
+      <c r="S8" s="22" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-3XL</t>
+        </is>
+      </c>
+      <c r="T8" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>#1107</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Meghana R</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Aranya Grace Anarkali Dress - XL</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>2680</v>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t>Customer Cancelled O T P Verified</t>
+        </is>
+      </c>
+      <c r="L9" s="27" t="inlineStr">
+        <is>
+          <t>Kolar</t>
+        </is>
+      </c>
+      <c r="M9" s="29" t="inlineStr">
+        <is>
+          <t>'563102</t>
+        </is>
+      </c>
+      <c r="N9" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O9" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P9" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q9" s="26" t="inlineStr">
+        <is>
+          <t>SF3593208175KR</t>
+        </is>
+      </c>
+      <c r="R9" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3593208175KR</t>
+        </is>
+      </c>
+      <c r="S9" s="26" t="inlineStr">
+        <is>
+          <t>A-SUM9239-XL</t>
+        </is>
+      </c>
+      <c r="T9" s="26" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>#1105</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Akila Senthil</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL, Sunset Petal - XXL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>'636005</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P10" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>14112364415189</t>
+        </is>
+      </c>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364415189</t>
+        </is>
+      </c>
+      <c r="S10" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-2XL, TOP-SP-DO-XXL</t>
+        </is>
+      </c>
+      <c r="T10" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>#1104</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Gopal Kowsi</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Sunset Petal - XL</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="27" t="inlineStr">
+        <is>
+          <t>Vanavasi</t>
+        </is>
+      </c>
+      <c r="M11" s="29" t="inlineStr">
+        <is>
+          <t>'636457</t>
+        </is>
+      </c>
+      <c r="N11" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P11" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
+        <is>
+          <t>SRSC9436482183</t>
+        </is>
+      </c>
+      <c r="R11" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9436482183</t>
+        </is>
+      </c>
+      <c r="S11" s="26" t="inlineStr">
+        <is>
+          <t>TOP-SP-DO-XL</t>
+        </is>
+      </c>
+      <c r="T11" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>#1103</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Praveena Manoharan</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Purple Panache - XL</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>46201</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>'600100</t>
+        </is>
+      </c>
+      <c r="N12" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P12" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>SF3158678399SPF</t>
+        </is>
+      </c>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3158678399SPF</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-XL</t>
+        </is>
+      </c>
+      <c r="T12" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>#1102</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Smitha Ag</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - L</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>Customer Not Available X Office Or Residence Closed</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>Muvattupuzha</t>
+        </is>
+      </c>
+      <c r="M13" s="29" t="inlineStr">
+        <is>
+          <t>'686661</t>
+        </is>
+      </c>
+      <c r="N13" s="26" t="inlineStr">
+        <is>
+          <t>RTO OFD</t>
+        </is>
+      </c>
+      <c r="O13" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P13" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q13" s="26" t="inlineStr">
+        <is>
+          <t>14112363521699</t>
+        </is>
+      </c>
+      <c r="R13" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363521699</t>
+        </is>
+      </c>
+      <c r="S13" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-MR-L</t>
+        </is>
+      </c>
+      <c r="T13" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>#1101</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Apsara Reddy</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Sunset Petal - L, Teal Tempo - L, Purple Panache - L</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="M14" s="25" t="inlineStr">
+        <is>
+          <t>'518003</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>14112364314371</t>
+        </is>
+      </c>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112364314371</t>
+        </is>
+      </c>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>TOP-SP-DO-L, TOP-TT-BL-L, TOP-PP-PU-L</t>
+        </is>
+      </c>
+      <c r="T14" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>#1100</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Shailu Reddy</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>Purple Panache - 2XL</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="M15" s="29" t="inlineStr">
+        <is>
+          <t>'506002</t>
+        </is>
+      </c>
+      <c r="N15" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O15" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P15" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q15" s="26" t="inlineStr">
+        <is>
+          <t>14112363687734</t>
+        </is>
+      </c>
+      <c r="R15" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363687734</t>
+        </is>
+      </c>
+      <c r="S15" s="26" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-2XL</t>
+        </is>
+      </c>
+      <c r="T15" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>#1099</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Durai Kannan</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Moss Majesty - L</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>'641008</t>
+        </is>
+      </c>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q16" s="22" t="inlineStr">
+        <is>
+          <t>370430051263</t>
+        </is>
+      </c>
+      <c r="R16" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370430051263</t>
+        </is>
+      </c>
+      <c r="S16" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-L</t>
+        </is>
+      </c>
+      <c r="T16" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>#1098</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>B Padmapriya</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>Bold Basil - L</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="27" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="M17" s="29" t="inlineStr">
+        <is>
+          <t>'500017</t>
+        </is>
+      </c>
+      <c r="N17" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O17" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P17" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q17" s="26" t="inlineStr">
+        <is>
+          <t>14112367080297</t>
+        </is>
+      </c>
+      <c r="R17" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112367080297</t>
+        </is>
+      </c>
+      <c r="S17" s="26" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-L</t>
+        </is>
+      </c>
+      <c r="T17" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>#1097</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Krishna</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Grape Leaf Glam - M</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+      <c r="M18" s="25" t="inlineStr">
+        <is>
+          <t>'522007</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q18" s="22" t="inlineStr">
+        <is>
+          <t>370429882984</t>
+        </is>
+      </c>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429882984</t>
+        </is>
+      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>TOP-GL-GR-M</t>
+        </is>
+      </c>
+      <c r="T18" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>#1096</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Indu Rekha</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Honey Bloom Top - 3XL, Ocean Elegance Top - 3XL</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>2224</v>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="27" t="inlineStr">
+        <is>
+          <t>Anantapur Urban</t>
+        </is>
+      </c>
+      <c r="M19" s="29" t="inlineStr">
+        <is>
+          <t>'515001</t>
+        </is>
+      </c>
+      <c r="N19" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O19" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P19" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q19" s="26" t="inlineStr">
+        <is>
+          <t>14112365054938</t>
+        </is>
+      </c>
+      <c r="R19" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112365054938</t>
+        </is>
+      </c>
+      <c r="S19" s="26" t="inlineStr">
+        <is>
+          <t>TOP-HB-YL-3XL, TOP-OE-NB-3XL</t>
+        </is>
+      </c>
+      <c r="T19" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>#1095</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Priya Dharshini Pd</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - 2XL</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>Villupuram</t>
+        </is>
+      </c>
+      <c r="M20" s="25" t="inlineStr">
+        <is>
+          <t>'604204</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P20" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q20" s="22" t="inlineStr">
+        <is>
+          <t>SF3586915332KR</t>
+        </is>
+      </c>
+      <c r="R20" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3586915332KR</t>
+        </is>
+      </c>
+      <c r="S20" s="22" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-2XL</t>
+        </is>
+      </c>
+      <c r="T20" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>#1094</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Usha .R</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 3XL</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="27" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="M21" s="29" t="inlineStr">
+        <is>
+          <t>'635109</t>
+        </is>
+      </c>
+      <c r="N21" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O21" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P21" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q21" s="26" t="inlineStr">
+        <is>
+          <t>14112362848987</t>
+        </is>
+      </c>
+      <c r="R21" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362848987</t>
+        </is>
+      </c>
+      <c r="S21" s="26" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-3XL</t>
+        </is>
+      </c>
+      <c r="T21" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>#1093</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Ramya Gowda</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Bold Basil - 2XL</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>Customer Unavailable Delivery Attempted</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>'560091</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>370429573110</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370429573110</t>
+        </is>
+      </c>
+      <c r="S22" s="22" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-2XL</t>
+        </is>
+      </c>
+      <c r="T22" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>#1092</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Kowsalya</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>Moss Majesty - S</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J23" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>Customer Not Available X Office Or Residence Closed</t>
+        </is>
+      </c>
+      <c r="L23" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M23" s="29" t="inlineStr">
+        <is>
+          <t>'600096</t>
+        </is>
+      </c>
+      <c r="N23" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O23" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P23" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q23" s="26" t="inlineStr">
+        <is>
+          <t>14112363585911</t>
+        </is>
+      </c>
+      <c r="R23" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112363585911</t>
+        </is>
+      </c>
+      <c r="S23" s="26" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-S</t>
+        </is>
+      </c>
+      <c r="T23" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>#1091</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Vijay Aadarsh Adarsh</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Pna|Receiver Not Available/Reachable Over Phone</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>'641107</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q24" s="22" t="inlineStr">
+        <is>
+          <t>7D131457369</t>
+        </is>
+      </c>
+      <c r="R24" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131457369</t>
+        </is>
+      </c>
+      <c r="S24" s="22" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-XL</t>
+        </is>
+      </c>
+      <c r="T24" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>#1090</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Kamal Thiyagarajan</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Vanya Bloom Top - S</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="27" t="inlineStr">
+        <is>
+          <t>Tirupur</t>
+        </is>
+      </c>
+      <c r="M25" s="29" t="inlineStr">
+        <is>
+          <t>'641606</t>
+        </is>
+      </c>
+      <c r="N25" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O25" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P25" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q25" s="26" t="inlineStr">
+        <is>
+          <t>370395354997</t>
+        </is>
+      </c>
+      <c r="R25" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370395354997</t>
+        </is>
+      </c>
+      <c r="S25" s="26" t="inlineStr">
+        <is>
+          <t>TOP-VB-GR-S</t>
+        </is>
+      </c>
+      <c r="T25" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>#1089</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Divya Divya</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Moss Majesty - L</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>Kuppatti</t>
+        </is>
+      </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>'635118</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="inlineStr">
+        <is>
+          <t>SRSC9946388102</t>
+        </is>
+      </c>
+      <c r="R26" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC9946388102</t>
+        </is>
+      </c>
+      <c r="S26" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-L</t>
+        </is>
+      </c>
+      <c r="T26" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>#1088</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Nutan Manerkar</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - 2XL</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="27" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="M27" s="29" t="inlineStr">
+        <is>
+          <t>'403601</t>
+        </is>
+      </c>
+      <c r="N27" s="26" t="inlineStr">
+        <is>
+          <t>SELF FULFILED</t>
+        </is>
+      </c>
+      <c r="O27" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P27" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" s="26" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-2XL</t>
+        </is>
+      </c>
+      <c r="T27" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>#1087</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Devi Rv</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>Bold Basil - 2XL</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>Customer Not Contactable</t>
+        </is>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>'600110</t>
+        </is>
+      </c>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q28" s="22" t="inlineStr">
+        <is>
+          <t>SF3576445793KR</t>
+        </is>
+      </c>
+      <c r="R28" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SF3576445793KR</t>
+        </is>
+      </c>
+      <c r="S28" s="22" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-2XL</t>
+        </is>
+      </c>
+      <c r="T28" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>#1086</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>D Keerthi</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>Bold Basil - 3XL</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="27" t="inlineStr">
+        <is>
+          <t>Chittoor</t>
+        </is>
+      </c>
+      <c r="M29" s="29" t="inlineStr">
+        <is>
+          <t>'517234</t>
+        </is>
+      </c>
+      <c r="N29" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O29" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P29" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q29" s="26" t="inlineStr">
+        <is>
+          <t>SRSC3884345902</t>
+        </is>
+      </c>
+      <c r="R29" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSC3884345902</t>
+        </is>
+      </c>
+      <c r="S29" s="26" t="inlineStr">
+        <is>
+          <t>TOP-BB-LG-3XL</t>
+        </is>
+      </c>
+      <c r="T29" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>#1085</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Mohanakrishnan Devanathan</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>Purple Panache - M</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>'605006</t>
+        </is>
+      </c>
+      <c r="N30" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O30" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P30" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q30" s="22" t="inlineStr">
+        <is>
+          <t>370384504495</t>
+        </is>
+      </c>
+      <c r="R30" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370384504495</t>
+        </is>
+      </c>
+      <c r="S30" s="22" t="inlineStr">
+        <is>
+          <t>TOP-PP-PU-M</t>
+        </is>
+      </c>
+      <c r="T30" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>#1084</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Gowri R</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>Sunset Petal - XL</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M31" s="29" t="inlineStr">
+        <is>
+          <t>'600096</t>
+        </is>
+      </c>
+      <c r="N31" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O31" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P31" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q31" s="26" t="inlineStr">
+        <is>
+          <t>SRSP2020476035</t>
+        </is>
+      </c>
+      <c r="R31" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP2020476035</t>
+        </is>
+      </c>
+      <c r="S31" s="26" t="inlineStr">
+        <is>
+          <t>TOP-SP-DO-XL</t>
+        </is>
+      </c>
+      <c r="T31" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>#1083</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Sukanya R</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>Coral Bloom Top - M, Purple Panache - M</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M32" s="25" t="inlineStr">
+        <is>
+          <t>'600095</t>
+        </is>
+      </c>
+      <c r="N32" s="22" t="inlineStr">
+        <is>
+          <t>SELF FULFILED</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P32" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" s="22" t="inlineStr">
+        <is>
+          <t>TOP-CB-CRD-M, TOP-PP-PU-M</t>
+        </is>
+      </c>
+      <c r="T32" s="22" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>#1082</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>Urban Ruby - XL</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="27" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L33" s="27" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M33" s="29" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N33" s="26" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P33" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q33" s="26" t="inlineStr">
+        <is>
+          <t>1319460341769</t>
+        </is>
+      </c>
+      <c r="R33" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341769</t>
+        </is>
+      </c>
+      <c r="S33" s="26" t="inlineStr">
+        <is>
+          <t>TOP-UR-RD-XL</t>
+        </is>
+      </c>
+      <c r="T33" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>#1081</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Harshini Rajendran</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>Mystic Mist Red - S</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>Customer Refused To Accept O T P Verified</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>Karaikudi</t>
+        </is>
+      </c>
+      <c r="M34" s="25" t="inlineStr">
+        <is>
+          <t>'630003</t>
+        </is>
+      </c>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>RTO DELIVERED</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q34" s="22" t="inlineStr">
+        <is>
+          <t>1319460341773</t>
+        </is>
+      </c>
+      <c r="R34" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1319460341773</t>
+        </is>
+      </c>
+      <c r="S34" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-MR-S</t>
+        </is>
+      </c>
+      <c r="T34" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>#1080</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Chandraelectro Corporation</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>Teal Tempo - 2XL, Mystic Mist Red - 2XL, Rustara - XXL</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>3176</v>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="27" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="M35" s="29" t="inlineStr">
+        <is>
+          <t>'625001</t>
+        </is>
+      </c>
+      <c r="N35" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O35" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P35" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q35" s="26" t="inlineStr">
+        <is>
+          <t>14112362553816</t>
+        </is>
+      </c>
+      <c r="R35" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362553816</t>
+        </is>
+      </c>
+      <c r="S35" s="26" t="inlineStr">
+        <is>
+          <t>TOP-TT-BL-2XL, TOP-MM-MR-2XL, TOP-RU-DB-XXL</t>
+        </is>
+      </c>
+      <c r="T35" s="26" t="inlineStr">
+        <is>
+          <t>TOPS, TOPS, TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>#1079</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Mohana Mona</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>Moss Majesty - M</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="23" t="inlineStr">
+        <is>
+          <t>Dharmapuri</t>
+        </is>
+      </c>
+      <c r="M36" s="25" t="inlineStr">
+        <is>
+          <t>'636705</t>
+        </is>
+      </c>
+      <c r="N36" s="22" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O36" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P36" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q36" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S36" s="22" t="inlineStr">
+        <is>
+          <t>TOP-MM-BG-M</t>
+        </is>
+      </c>
+      <c r="T36" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>#1078</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Gomathi Dhanapal</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
+        <is>
+          <t>Wine Blossom Top - XL</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="M37" s="29" t="inlineStr">
+        <is>
+          <t>'600073</t>
+        </is>
+      </c>
+      <c r="N37" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O37" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P37" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" s="26" t="inlineStr">
+        <is>
+          <t>SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="R37" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/SRSP8409363746</t>
+        </is>
+      </c>
+      <c r="S37" s="26" t="inlineStr">
+        <is>
+          <t>TOP-WB-PU-XL</t>
+        </is>
+      </c>
+      <c r="T37" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>#1071</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Soumya Shetty</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>Sapphire Charm Top - M</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>Bijapur</t>
+        </is>
+      </c>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>'586101</t>
+        </is>
+      </c>
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>FULFILLED</t>
+        </is>
+      </c>
+      <c r="O38" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P38" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q38" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S38" s="22" t="inlineStr">
+        <is>
+          <t>TOP-SC-DB-M</t>
+        </is>
+      </c>
+      <c r="T38" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="B39" s="31">
+        <f>COUNTA(A2:A38)</f>
+        <v/>
+      </c>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="E39" s="33">
+        <f>SUM(E2:E38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="30" t="n"/>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
+      <c r="M39" s="30" t="n"/>
+      <c r="N39" s="30" t="n"/>
+      <c r="O39" s="30" t="n"/>
+      <c r="P39" s="30" t="n"/>
+      <c r="Q39" s="30" t="n"/>
+      <c r="R39" s="30" t="n"/>
+      <c r="S39" s="30" t="n"/>
+      <c r="T39" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11739,7 +19621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T102"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21666,41 +29548,531 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="30" t="inlineStr">
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>#1120</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="inlineStr">
+        <is>
+          <t>Nisha J</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>Dainty Dots Teal - 2XL</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K102" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="23" t="inlineStr">
+        <is>
+          <t>Chengalpattu</t>
+        </is>
+      </c>
+      <c r="M102" s="25" t="inlineStr">
+        <is>
+          <t>'603002</t>
+        </is>
+      </c>
+      <c r="N102" s="22" t="inlineStr">
+        <is>
+          <t>CANCELED</t>
+        </is>
+      </c>
+      <c r="O102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P102" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q102" s="22" t="inlineStr">
+        <is>
+          <t>14112362403829</t>
+        </is>
+      </c>
+      <c r="R102" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/14112362403829</t>
+        </is>
+      </c>
+      <c r="S102" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-RB-2XL</t>
+        </is>
+      </c>
+      <c r="T102" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>#1119</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>Vijayasri S Narendran</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>Blossom Taupe Chic Set - 2XL</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E103" s="20" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F103" s="26" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G103" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H103" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I103" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J103" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K103" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="27" t="inlineStr">
+        <is>
+          <t>Avadi</t>
+        </is>
+      </c>
+      <c r="M103" s="29" t="inlineStr">
+        <is>
+          <t>'600062</t>
+        </is>
+      </c>
+      <c r="N103" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O103" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P103" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q103" s="26" t="inlineStr">
+        <is>
+          <t>1091393138630</t>
+        </is>
+      </c>
+      <c r="R103" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/1091393138630</t>
+        </is>
+      </c>
+      <c r="S103" s="26" t="inlineStr">
+        <is>
+          <t>C-BT-BE-2XL</t>
+        </is>
+      </c>
+      <c r="T103" s="26" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>#1118</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="inlineStr">
+        <is>
+          <t>Aswathy P</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>Urban Ruby - M</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K104" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="23" t="inlineStr">
+        <is>
+          <t>Ernakulam</t>
+        </is>
+      </c>
+      <c r="M104" s="25" t="inlineStr">
+        <is>
+          <t>'682030</t>
+        </is>
+      </c>
+      <c r="N104" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P104" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q104" s="22" t="inlineStr">
+        <is>
+          <t>7D131502192</t>
+        </is>
+      </c>
+      <c r="R104" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131502192</t>
+        </is>
+      </c>
+      <c r="S104" s="22" t="inlineStr">
+        <is>
+          <t>TOP-UR-RD-M</t>
+        </is>
+      </c>
+      <c r="T104" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>#1117</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>Dr Jovin Jose</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - M</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E105" s="20" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F105" s="26" t="inlineStr">
+        <is>
+          <t>Prepaid (Razorpay)</t>
+        </is>
+      </c>
+      <c r="G105" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I105" s="26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J105" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K105" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="27" t="inlineStr">
+        <is>
+          <t>Kanhangad</t>
+        </is>
+      </c>
+      <c r="M105" s="29" t="inlineStr">
+        <is>
+          <t>'671326</t>
+        </is>
+      </c>
+      <c r="N105" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O105" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P105" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q105" s="26" t="inlineStr">
+        <is>
+          <t>7D131501705</t>
+        </is>
+      </c>
+      <c r="R105" s="26" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/7D131501705</t>
+        </is>
+      </c>
+      <c r="S105" s="26" t="inlineStr">
+        <is>
+          <t>TOP-DD-YL-M</t>
+        </is>
+      </c>
+      <c r="T105" s="26" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>#1115</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="inlineStr">
+        <is>
+          <t>Vidya Jothi</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>Daisy Dusk Yellow - XL</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J106" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K106" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="23" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="M106" s="25" t="inlineStr">
+        <is>
+          <t>'641062</t>
+        </is>
+      </c>
+      <c r="N106" s="22" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="O106" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P106" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q106" s="22" t="inlineStr">
+        <is>
+          <t>370526573181</t>
+        </is>
+      </c>
+      <c r="R106" s="22" t="inlineStr">
+        <is>
+          <t>https://shiprocket.co/tracking/370526573181</t>
+        </is>
+      </c>
+      <c r="S106" s="22" t="inlineStr">
+        <is>
+          <t>TOP-DD-YL-XL</t>
+        </is>
+      </c>
+      <c r="T106" s="22" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="30" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B102" s="31">
-        <f>COUNTA(A2:A101)</f>
+      <c r="B107" s="31">
+        <f>COUNTA(A2:A106)</f>
         <v/>
       </c>
-      <c r="C102" s="30" t="n"/>
-      <c r="D102" s="32" t="inlineStr">
+      <c r="C107" s="30" t="n"/>
+      <c r="D107" s="32" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="E102" s="33">
-        <f>SUM(E2:E101)</f>
+      <c r="E107" s="33">
+        <f>SUM(E2:E106)</f>
         <v/>
       </c>
-      <c r="F102" s="30" t="n"/>
-      <c r="G102" s="30" t="n"/>
-      <c r="H102" s="30" t="n"/>
-      <c r="I102" s="30" t="n"/>
-      <c r="J102" s="30" t="n"/>
-      <c r="K102" s="30" t="n"/>
-      <c r="L102" s="30" t="n"/>
-      <c r="M102" s="30" t="n"/>
-      <c r="N102" s="30" t="n"/>
-      <c r="O102" s="30" t="n"/>
-      <c r="P102" s="30" t="n"/>
-      <c r="Q102" s="30" t="n"/>
-      <c r="R102" s="30" t="n"/>
-      <c r="S102" s="30" t="n"/>
-      <c r="T102" s="30" t="n"/>
+      <c r="F107" s="30" t="n"/>
+      <c r="G107" s="30" t="n"/>
+      <c r="H107" s="30" t="n"/>
+      <c r="I107" s="30" t="n"/>
+      <c r="J107" s="30" t="n"/>
+      <c r="K107" s="30" t="n"/>
+      <c r="L107" s="30" t="n"/>
+      <c r="M107" s="30" t="n"/>
+      <c r="N107" s="30" t="n"/>
+      <c r="O107" s="30" t="n"/>
+      <c r="P107" s="30" t="n"/>
+      <c r="Q107" s="30" t="n"/>
+      <c r="R107" s="30" t="n"/>
+      <c r="S107" s="30" t="n"/>
+      <c r="T107" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P22" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q22" s="22" t="inlineStr">
@@ -21782,7 +21782,7 @@
       </c>
       <c r="P22" s="22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q22" s="22" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -847,12 +847,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>16 (₹25,622.00)</t>
+          <t>15 (₹23,478.00)</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>4 (₹6,280.00)</t>
+          <t>5 (₹8,424.00)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -6129,7 +6129,7 @@
       </c>
       <c r="P42" s="27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q42" s="27" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="P27" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q27" s="31" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -5308,7 +5308,7 @@
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G53" s="31" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="F15" s="31" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="F31" s="31" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G31" s="31" t="inlineStr">
@@ -28490,7 +28490,7 @@
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>Partial COD</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -10796,17 +10796,17 @@
       </c>
       <c r="F90" s="27" t="inlineStr">
         <is>
-          <t>Partial COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G90" s="27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H90" s="27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I90" s="27" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="J90" s="27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K90" s="28" t="inlineStr">
@@ -32116,17 +32116,17 @@
       </c>
       <c r="F71" s="31" t="inlineStr">
         <is>
-          <t>Partial COD</t>
+          <t>Prepaid (Razorpay)</t>
         </is>
       </c>
       <c r="G71" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H71" s="31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="J71" s="31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K71" s="32" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -6303,7 +6303,7 @@
       </c>
       <c r="I44" s="27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J44" s="27" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="I48" s="27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J48" s="27" t="inlineStr">
@@ -27623,7 +27623,7 @@
       </c>
       <c r="I25" s="31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J25" s="31" t="inlineStr">
@@ -28015,7 +28015,7 @@
       </c>
       <c r="I29" s="31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J29" s="31" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -4569,7 +4569,7 @@
       </c>
       <c r="O26" s="27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P26" s="27" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="O69" s="31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P69" s="31" t="inlineStr">
@@ -25889,7 +25889,7 @@
       </c>
       <c r="O7" s="31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P7" s="31" t="inlineStr">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="O50" s="27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P50" s="27" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -757,11 +757,11 @@
         <v>391979</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>340033</v>
+        <v>336463</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>~ ₹2,394.60</t>
+          <t>~ ₹2,369.46</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>14 (₹19,908.00)</t>
+          <t>15 (₹23,478.00)</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Jan 2027" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Feb 2027" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mar 2027" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Category Summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,12 +28,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="dd-mm-yyyy"/>
     <numFmt numFmtId="167" formatCode="₹#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="mmm yyyy"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -225,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -286,7 +288,7 @@
     <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -298,7 +300,7 @@
     <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -334,6 +336,30 @@
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2384,6 +2410,343 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Delivered Orders</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Share (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>TOPS</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="n">
+        <v>216</v>
+      </c>
+      <c r="C2" s="40" t="n">
+        <v>390201.34</v>
+      </c>
+      <c r="D2" s="39" t="n">
+        <v>195</v>
+      </c>
+      <c r="E2" s="41" t="n">
+        <v>0.5490653264340458</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>CHUDIDHAR</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3" s="43" t="n">
+        <v>159679.35</v>
+      </c>
+      <c r="D3" s="42" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3" s="44" t="n">
+        <v>0.2246901418445315</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>ANARKALI</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="n">
+        <v>39</v>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>168321</v>
+      </c>
+      <c r="D4" s="39" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>0.2368500959292068</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>LEHENGA</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>13829</v>
+      </c>
+      <c r="D5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>0.01945924737023307</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>CO-ORD SET</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>22490</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="41" t="n">
+        <v>0.03164642948561297</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>HALF SAREE LEHENGA</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>0.004151043440754036</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>LONG GOWN</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>11182</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="41" t="n">
+        <v>0.01573456534051242</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>SHARARA</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>0.002729838737309434</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>DRESS</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>KURTI</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>SAREE</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="41" t="n">
+        <v>0.004151043440754036</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>22490</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>0.03164642948561297</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>SUIT</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>OTHERS</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>22490</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="44" t="n">
+        <v>0.03164642948561297</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="45">
+        <f>SUM(B2:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="38">
+        <f>SUM(C2:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="45">
+        <f>SUM(D2:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="46">
+        <f>SUM(E2:E15)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Janvi_Consolidated_Orders_2026_2027.xlsx
+++ b/Janvi_Consolidated_Orders_2026_2027.xlsx
@@ -19,7 +19,6 @@
     <sheet name="Jan 2027" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Feb 2027" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mar 2027" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Category Summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,13 +27,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="dd-mm-yyyy"/>
     <numFmt numFmtId="167" formatCode="₹#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="168" formatCode="mmm yyyy"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -227,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -288,7 +286,7 @@
     <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -300,7 +298,7 @@
     <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -336,30 +334,6 @@
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2410,343 +2384,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" s="18" t="inlineStr">
-        <is>
-          <t>Total Orders</t>
-        </is>
-      </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>Delivered Orders</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Share (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>TOPS</t>
-        </is>
-      </c>
-      <c r="B2" s="39" t="n">
-        <v>216</v>
-      </c>
-      <c r="C2" s="40" t="n">
-        <v>390201.34</v>
-      </c>
-      <c r="D2" s="39" t="n">
-        <v>195</v>
-      </c>
-      <c r="E2" s="41" t="n">
-        <v>0.5490653264340458</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>CHUDIDHAR</t>
-        </is>
-      </c>
-      <c r="B3" s="42" t="n">
-        <v>67</v>
-      </c>
-      <c r="C3" s="43" t="n">
-        <v>159679.35</v>
-      </c>
-      <c r="D3" s="42" t="n">
-        <v>49</v>
-      </c>
-      <c r="E3" s="44" t="n">
-        <v>0.2246901418445315</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>ANARKALI</t>
-        </is>
-      </c>
-      <c r="B4" s="39" t="n">
-        <v>39</v>
-      </c>
-      <c r="C4" s="40" t="n">
-        <v>168321</v>
-      </c>
-      <c r="D4" s="39" t="n">
-        <v>35</v>
-      </c>
-      <c r="E4" s="41" t="n">
-        <v>0.2368500959292068</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>LEHENGA</t>
-        </is>
-      </c>
-      <c r="B5" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="43" t="n">
-        <v>13829</v>
-      </c>
-      <c r="D5" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="44" t="n">
-        <v>0.01945924737023307</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>CO-ORD SET</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="C6" s="40" t="n">
-        <v>22490</v>
-      </c>
-      <c r="D6" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="41" t="n">
-        <v>0.03164642948561297</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>HALF SAREE LEHENGA</t>
-        </is>
-      </c>
-      <c r="B7" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="43" t="n">
-        <v>2950</v>
-      </c>
-      <c r="D7" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="44" t="n">
-        <v>0.004151043440754036</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>LONG GOWN</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="40" t="n">
-        <v>11182</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="41" t="n">
-        <v>0.01573456534051242</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>SHARARA</t>
-        </is>
-      </c>
-      <c r="B9" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="43" t="n">
-        <v>1940</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="44" t="n">
-        <v>0.002729838737309434</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>DRESS</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>KURTI</t>
-        </is>
-      </c>
-      <c r="B11" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>SAREE</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>2950</v>
-      </c>
-      <c r="D12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="41" t="n">
-        <v>0.004151043440754036</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="B13" s="42" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="43" t="n">
-        <v>22490</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" s="44" t="n">
-        <v>0.03164642948561297</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>SUIT</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>OTHERS</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="n">
-        <v>15</v>
-      </c>
-      <c r="C15" s="43" t="n">
-        <v>22490</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="44" t="n">
-        <v>0.03164642948561297</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="45">
-        <f>SUM(B2:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="38">
-        <f>SUM(C2:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="45">
-        <f>SUM(D2:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="46">
-        <f>SUM(E2:E15)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
